--- a/report.xlsx
+++ b/report.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>google data analytics apprenticeship</t>
+          <t>Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
+          <t>https://github.com/sealandseacat/dbmask</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt biocare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -493,16 +493,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.368987975951904</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The EPA is planning to scrap public review rules for data center pollution</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.368987975951904</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://capitalbnews.org/data-centers-permit-rules-epa/</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "google data analytics apprenticeship" (and what it should mean for your 2026 content plan)</t>
+          <t>What Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases means for analytics people (a quick take)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>google data analytics apprenticeship</t>
+          <t>Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -796,11 +796,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
+          <t>https://github.com/sealandseacat/dbmask</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Data Pipeline, explained in plain English (a 2026 beginner's guide)</t>
+          <t>Why everyone's suddenly talking about "dbt biocare" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt biocare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -824,11 +824,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.368987975951904</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What The EPA is planning to scrap public review rules for data center pollution means for analytics people (a quick take)</t>
+          <t>Data Pipeline, explained in plain English (a 2026 beginner's guide)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The EPA is planning to scrap public review rules for data center pollution</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -852,11 +852,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.2</v>
+        <v>1.368987975951904</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://capitalbnews.org/data-centers-permit-rules-epa/</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "power bi dashboard" (and what it should mean for your 2026 content plan)</t>
+          <t>dbt, explained in plain English (a 2026 beginner's guide)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F430"/>
+  <dimension ref="A1:F418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>google data analytics apprenticeship</t>
+          <t>Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
+          <t>https://github.com/sealandseacat/dbmask</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt biocare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.368987975951904</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The EPA is planning to scrap public review rules for data center pollution</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1173,16 +1173,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.368987975951904</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://capitalbnews.org/data-centers-permit-rules-epa/</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7301338792878506</v>
+        <v>0.7301045701784317</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data engineering projects</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.6625751503006012</v>
+        <v>0.6776052104208418</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+projects</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.658817635270541</v>
+        <v>0.6625751503006012</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>what is a data pipeline</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1677,16 +1677,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.6583166332665331</v>
+        <v>0.658817635270541</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+a+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dbt labs</t>
+          <t>what is a data pipeline</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.655060120240481</v>
+        <v>0.6583166332665331</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+labs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+a+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>dbt labs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6437875751503006</v>
+        <v>0.655060120240481</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+labs</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6400300601202404</v>
+        <v>0.6437875751503006</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.6362725450901803</v>
+        <v>0.6400300601202404</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>data engineering zoomcamp</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.6287575150300601</v>
+        <v>0.6362725450901803</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+zoomcamp</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>what is dbt in data engineering</t>
+          <t>data engineering zoomcamp</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.625</v>
+        <v>0.6287575150300601</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt+in+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>what is dbt in data engineering</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1929,16 +1929,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5539511450994561</v>
+        <v>0.625</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>We rebuilt the old Google Analytics on top of GA4's data</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1957,16 +1957,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+management</t>
+          <t>https://github.com/adacahq/adaca-analytics</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.5539289083355077</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=etl+vs+data+pipeline</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+data+analytics+work</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>how to dbt</t>
+          <t>how to data analytics</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+dbt</t>
+          <t>https://www.google.com/search?q=how+to+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=etl+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+snowflake</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+delete+data+analytics+from+iphone</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+dashboard</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+sql</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dbt vs sqlmesh</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+sqlmesh</t>
+          <t>https://www.google.com/search?q=how+to+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dbt vs spark</t>
+          <t>how to dbt</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+spark</t>
+          <t>https://www.google.com/search?q=how+to+dbt</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+design+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+delete+data+analytics+from+iphone</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+do+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+design+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+get+into+data+engineering</t>
+          <t>https://www.google.com/search?q=visual+studio+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>vs data analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+analytics+engineering</t>
+          <t>https://www.google.com/search?q=vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>vs dbt</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+analytics</t>
+          <t>https://www.google.com/search?q=vs+dbt</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>vs power bi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+analytics+for+free</t>
+          <t>https://www.google.com/search?q=vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is ai in analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+pro</t>
+          <t>https://www.google.com/search?q=what+is+ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+analytics+for+free</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=exabeam+ai+agent+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+accounting</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+desktop</t>
+          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline+fabric</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+and+tableau</t>
+          <t>https://www.google.com/search?q=dataops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+master+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+healthcare</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=mlops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+simple+words</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+analytics+work</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+job</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+sql</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+salary</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+training</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+used+for</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+vs+tableau</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=excel+vs+power+bi</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+all+about</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+python</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+and+analytics</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+optimize+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+and+data+science</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>what is dbt labs</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+labs</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>what is dbt models</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+models</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+in+simple+words</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>what is dbt in snowflake</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+in+snowflake</t>
+          <t>https://www.google.com/search?q=etl+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+llm+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+role</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>what is dbt fusion</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+fusion</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=fabric+vs+power+bi</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering+dbt</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+and+how+does+it+work</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>what is dbt data</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+data</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+and+visualization</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=grafana+vs+power+bi</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+big+data+analytics</t>
+          <t>https://www.google.com/search?q=etl+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+testing</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+databricks</t>
+          <t>https://www.google.com/search?q=exabeam+ai+agent+analytics</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=devops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=excel+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+analytics</t>
+          <t>https://www.google.com/search?q=fabric+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+orchestration</t>
+          <t>https://www.google.com/search?q=glue+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>dbt vs databricks</t>
+          <t>dbt vs sqlmesh</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+databricks</t>
+          <t>https://www.google.com/search?q=dbt+vs+sqlmesh</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>dbt vs snowflake</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+snowflake</t>
+          <t>https://www.google.com/search?q=devops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+benchmark</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>workflow vs data pipeline</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+comparison</t>
+          <t>https://www.google.com/search?q=workflow+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=glue+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=why+power+bi+over+tableau</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>why dbt is used</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+is+used</t>
+          <t>https://www.google.com/search?q=why+power+bi+over+excel</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>why dbt app is not working</t>
+          <t>why power bi is used</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+app+is+not+working</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+used</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>why dbt</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+not+available+for+mac</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why power bi is important</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+pipeline</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+important</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+reddit</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+better+than+tableau</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+reddit</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+better+than+excel</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+master+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data analytics</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+interview+questions</t>
+          <t>https://www.google.com/search?q=why+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+bas</t>
+          <t>https://www.google.com/search?q=top+data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard servicenow</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard+servicenow</t>
+          <t>https://www.google.com/search?q=tableau+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard</t>
+          <t>https://www.google.com/search?q=statistics+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ai agent analytics</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics</t>
+          <t>https://www.google.com/search?q=software+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+courses</t>
+          <t>https://www.google.com/search?q=or+power+bi+symbol</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>or power bi measure</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+certification</t>
+          <t>https://www.google.com/search?q=or+power+bi+measure</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>or power bi dax</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=software+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=or+power+bi+dax</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering+reddit</t>
+          <t>https://www.google.com/search?q=why+power+bi+gateway+went+offline</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering+dbt</t>
+          <t>https://www.google.com/search?q=why+data+engineering+interview+questions</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ai agent analytics platform</t>
+          <t>why dbt app is not working</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+platform</t>
+          <t>https://www.google.com/search?q=why+dbt+app+is+not+working</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ai in analytics course</t>
+          <t>why dbt</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+in+analytics+course</t>
+          <t>https://www.google.com/search?q=why+dbt</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ai in analytics</t>
+          <t>why data pipeline</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+in+analytics</t>
+          <t>https://www.google.com/search?q=why+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>ai vs data engineering</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+used</t>
+          <t>https://www.google.com/search?q=ai+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>ai vs data analytics</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+ai</t>
+          <t>https://www.google.com/search?q=ai+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>ai in analytics course</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+development</t>
+          <t>https://www.google.com/search?q=ai+in+analytics+course</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>ai in analytics</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+architecture</t>
+          <t>https://www.google.com/search?q=ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>analytics engineering vs data engineering</t>
+          <t>power bi</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=power+bi</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>analytics engineering salary</t>
+          <t>ai agent analytics servicenow</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+salary</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+servicenow</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>why dbt is used in data engineering</t>
+          <t>ai agent analytics platform</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+is+used+in+data+engineering</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>ai agent analytics dashboard servicenow</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+blogs</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard+servicenow</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>ai agent analytics dashboard</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+tools</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>ai agent analytics</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+software</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+programs</t>
+          <t>https://www.google.com/search?q=why+data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ai agent analytics vidhya</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+vidhya</t>
+          <t>https://www.google.com/search?q=why+data+engineering+is+important</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>power bi courses</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+the+future</t>
+          <t>https://www.google.com/search?q=power+bi+courses</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>power bi certification</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+gateway+went+offline</t>
+          <t>https://www.google.com/search?q=power+bi+certification</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>ai agent analytics vidhya</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+vidhya</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>llm analytics</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+books</t>
+          <t>https://www.google.com/search?q=llm+analytics</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+engineering</t>
+          <t>https://www.google.com/search?q=integration+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>use of ai in analytics</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+analytics</t>
+          <t>https://www.google.com/search?q=use+of+ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+login</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+python</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+download</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+databricks</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+desktop+download</t>
+          <t>https://www.google.com/search?q=how+to+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics</t>
+          <t>https://www.google.com/search?q=grafana+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+sql</t>
+          <t>https://www.google.com/search?q=how+to+study+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>or power bi</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+snowflake</t>
+          <t>https://www.google.com/search?q=or+power+bi</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+youtube</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=integration+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+study+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+bas</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>how to power bi</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+start+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+power+bi</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+youtube</t>
+          <t>https://www.google.com/search?q=how+to+optimize+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+dashboard</t>
+          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+master+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+dax</t>
+          <t>https://www.google.com/search?q=how+to+learn+python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+start+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+python</t>
+          <t>https://www.google.com/search?q=mlops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+ai+in+analytics</t>
+          <t>https://www.google.com/search?q=looker+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+power+bi</t>
+          <t>https://www.google.com/search?q=llm+analytics+vidhya</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>vs dbt</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+dbt</t>
+          <t>https://www.google.com/search?q=power+bi+vs+tableau</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>power bi training</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+data+analytics</t>
+          <t>https://www.google.com/search?q=power+bi+training</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>power bi login</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=visual+studio+data+pipeline</t>
+          <t>https://www.google.com/search?q=power+bi+login</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi</t>
+          <t>https://www.google.com/search?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+symbol</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+analytics</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+master+data+analytics</t>
+          <t>https://www.google.com/search?q=llm+analytics+benchmark</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+etl</t>
+          <t>https://www.google.com/search?q=how+to+get+into+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=looker+vs+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+do+data+analytics</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+vidhya</t>
+          <t>https://www.google.com/search?q=llm+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+tools</t>
+          <t>https://www.google.com/search?q=llm+analytics+posthog</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+posthog</t>
+          <t>https://www.google.com/search?q=llm+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+platform</t>
+          <t>https://www.google.com/search?q=llm+analytics+meaning</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+meaning</t>
+          <t>https://www.google.com/search?q=llm+analytics+leaderboard</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+leaderboard</t>
+          <t>https://www.google.com/search?q=llm+analytics+dashboard</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+machine+learning</t>
+          <t>https://www.google.com/search?q=llm+analytics+comparison</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+python+for+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+learn+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>backend vs data engineering</t>
+          <t>api vs data pipeline</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=backend+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=api+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>best ai agent analytics tools</t>
+          <t>backend vs data engineering</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+ai+agent+analytics+tools</t>
+          <t>https://www.google.com/search?q=backend+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>best analytics engineering books</t>
+          <t>best ai agent analytics tools</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+analytics+engineering+books</t>
+          <t>https://www.google.com/search?q=best+ai+agent+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>best analytics engineering books</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+better+than+tableau</t>
+          <t>https://www.google.com/search?q=best+analytics+engineering+books</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>best analytics engineering course</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+important</t>
+          <t>https://www.google.com/search?q=best+analytics+engineering+course</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>best data analytics books</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+not+available+for+mac</t>
+          <t>https://www.google.com/search?q=best+data+analytics+books</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+used</t>
+          <t>https://www.google.com/search?q=best+data+analytics+bootcamp</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ai agent analytics servicenow</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+servicenow</t>
+          <t>https://www.google.com/search?q=best+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+and+visualization</t>
+          <t>https://www.google.com/search?q=best+data+analytics+certification+reddit</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+courses+reddit</t>
+          <t>https://www.google.com/search?q=best+data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+courses</t>
+          <t>https://www.google.com/search?q=best+data+analytics+courses+reddit</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>analytics engineering</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+dashboards</t>
+          <t>https://www.google.com/search?q=analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>best dbt training for therapists</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+training</t>
+          <t>https://www.google.com/search?q=best+dbt+training+for+therapists</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>best power bi books</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+tutorial+on+youtube</t>
+          <t>https://www.google.com/search?q=best+power+bi+books</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>best power bi certification</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+visuals</t>
+          <t>https://www.google.com/search?q=best+power+bi+certification</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>why dbt is used</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=tableau+vs+power+bi</t>
+          <t>https://www.google.com/search?q=why+dbt+is+used</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>best dbt apps</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+apps</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+development+services</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics</t>
+          <t>https://www.google.com/search?q=cloud+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cybersecurity+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=business+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cybersecurity+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=best+power+bi+visuals</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cloud+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=best+data+engineering+podcasts</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline</t>
+          <t>https://www.google.com/search?q=best+data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+development+services</t>
+          <t>https://www.google.com/search?q=best+data+engineering+course+reddit</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+bootcamp</t>
+          <t>https://www.google.com/search?q=best+power+bi+course+for+beginners</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>api vs data pipeline</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=api+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=best+data+engineering+certifications</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>and data analytics</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=and+data+analytics</t>
+          <t>https://www.google.com/search?q=best+data+engineering+bootcamp</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>analytics vs data engineering</t>
+          <t>best data engineering books</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=best+data+engineering+books</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt pdf</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt+pdf</t>
+          <t>https://www.google.com/search?q=best+data+engineering+blogs</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt</t>
+          <t>https://www.google.com/search?q=best+data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>analytics engineering vs data science</t>
+          <t>best data analytics software</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+vs+data+science</t>
+          <t>https://www.google.com/search?q=best+data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+certifications+2026</t>
+          <t>https://www.google.com/search?q=best+data+analytics+programs</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+certifications</t>
+          <t>https://www.google.com/search?q=best+data+analytics+masters+programs</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+architecture</t>
+          <t>https://www.google.com/search?q=best+data+engineering+certifications+2026</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why data engineering</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+over+tableau</t>
+          <t>https://www.google.com/search?q=why+data+engineering</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>analytics engineering manager</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+manager</t>
+          <t>https://www.google.com/search?q=why+data+analytics+reddit</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>analytics engineering jobs</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+jobs</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+used</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>analytics engineering course</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+course</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+the+future+of+everything</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>analytics engineering best practices</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+best+practices</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+the+future</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>analytics engineering</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+important</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ai vs data engineering</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+a+good+career</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>why data analytics course</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+measure</t>
+          <t>https://www.google.com/search?q=why+data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+masters+programs</t>
+          <t>https://www.google.com/search?q=why+data+analytics+as+a+career</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+better+than+excel</t>
+          <t>https://www.google.com/search?q=power+bi+desktop+download</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>analytics engineering podcast</t>
+          <t>analytics engineering best practices</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+podcast</t>
+          <t>https://www.google.com/search?q=analytics+engineering+best+practices</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ai vs data analytics</t>
+          <t>why dbt is used in data engineering</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=why+dbt+is+used+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>workflow vs data pipeline</t>
+          <t>why power bi</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=workflow+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=why+power+bi</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>analytics engineering roundup</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+roundup</t>
+          <t>https://www.google.com/search?q=why+data+engineering+is+hard</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>analytics engineering course</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+is+hard</t>
+          <t>https://www.google.com/search?q=analytics+engineering+course</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+tools</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best data pipeline</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+software+for+integration+platforms</t>
+          <t>https://www.google.com/search?q=best+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+orchestration+tools</t>
+          <t>https://www.google.com/search?q=best+data+engineering+projects+for+resume</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+framework</t>
+          <t>https://www.google.com/search?q=best+data+engineering+projects</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>accounting vs data analytics</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+for+small+business</t>
+          <t>https://www.google.com/search?q=accounting+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+the+future+of+everything</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+used+for</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+over+excel</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+stand+for</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>and data analytics</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+important</t>
+          <t>https://www.google.com/search?q=and+data+analytics</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>analytics engineering jobs</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+is+important</t>
+          <t>https://www.google.com/search?q=analytics+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>analytics engineering with sql and dbt pdf</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+course</t>
+          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>analytics engineering with sql and dbt</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+as+a+career</t>
+          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>analytics engineering vs data science</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics</t>
+          <t>https://www.google.com/search?q=analytics+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>analytics engineering vs data engineering</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+used+for</t>
+          <t>https://www.google.com/search?q=analytics+engineering+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>analytics engineering salary</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+stand+for</t>
+          <t>https://www.google.com/search?q=analytics+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>analytics engineering roundup</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+software</t>
+          <t>https://www.google.com/search?q=analytics+engineering+roundup</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>analytics engineering podcast</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+service</t>
+          <t>https://www.google.com/search?q=analytics+engineering+podcast</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>analytics engineering manager</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+report+builder</t>
+          <t>https://www.google.com/search?q=analytics+engineering+manager</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>analytics vs data engineering</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+a+good+career</t>
+          <t>https://www.google.com/search?q=analytics+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>data engineering system design</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+icon</t>
+          <t>https://www.google.com/search?q=data+engineering+system+design</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>data engineering things</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+vs+data+science</t>
+          <t>https://www.google.com/search?q=data+engineering+things</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+degree</t>
+          <t>https://www.google.com/search?q=data+engineering+vs+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>data pipeline architecture diagram</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+engineering</t>
+          <t>https://www.google.com/search?q=data+pipeline+architecture+diagram</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+accounting</t>
+          <t>https://www.google.com/search?q=data+pipeline+diagram</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+healthcare</t>
+          <t>https://www.google.com/search?q=data+pipeline+icon</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>data analytics vs data science</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+simple+words</t>
+          <t>https://www.google.com/search?q=data+analytics+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>data engineering academy</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+job</t>
+          <t>https://www.google.com/search?q=data+engineering+academy</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+salary</t>
+          <t>https://www.google.com/search?q=data+engineering+interview+questions</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>data engineering manager</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+used+for</t>
+          <t>https://www.google.com/search?q=data+engineering+manager</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+vs+data+science</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>dbt vs act</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+act</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+skills</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>dbt vs airflow</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+airflow</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>dbt vs code extension</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+code+extension</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+all+about</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>best dbt books</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+books</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+for+small+business</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+vs+data+science</t>
+          <t>https://www.google.com/search?q=database+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>dbt vs spark</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+skills</t>
+          <t>https://www.google.com/search?q=dbt+vs+spark</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>dbt vs snowflake</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+salary</t>
+          <t>https://www.google.com/search?q=dbt+vs+snowflake</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>dbt vs databricks</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+role</t>
+          <t>https://www.google.com/search?q=dbt+vs+databricks</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>dbt vs code extension</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+reddit</t>
+          <t>https://www.google.com/search?q=dbt+vs+code+extension</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>dbt vs airflow</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+in+simple+words</t>
+          <t>https://www.google.com/search?q=dbt+vs+airflow</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>accounting vs data analytics</t>
+          <t>dbt vs act</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=accounting+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=dbt+vs+act</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+and+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+ai</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+orchestration</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline+fabric</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+management</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+sql</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=database+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+python</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=use+of+ai+in+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+machine+learning</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=top+data+pipeline+solutions</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+etl</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+course</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+and+data+science</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=statistics+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+testing</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>best dbt books for therapists</t>
+          <t>data analytics apprenticeship google</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+books+for+therapists</t>
+          <t>https://www.google.com/search?q=data+analytics+apprenticeship+google</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>best analytics engineering course</t>
+          <t>data analytics apprenticeship</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+analytics+engineering+course</t>
+          <t>https://www.google.com/search?q=data+analytics+apprenticeship</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+books</t>
+          <t>https://www.google.com/search?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+bootcamp</t>
+          <t>https://www.google.com/search?q=cybersecurity+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+certification</t>
+          <t>https://www.google.com/search?q=cybersecurity+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>what is power bi software</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+certification+reddit</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+software</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best dbt therapist near me</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+courses</t>
+          <t>https://www.google.com/search?q=best+dbt+therapist+near+me</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>what is power bi service</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+course+for+beginners</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+service</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>best dbt training for therapists</t>
+          <t>best dbt podcast</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+training+for+therapists</t>
+          <t>https://www.google.com/search?q=best+dbt+podcast</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>best dbt books for therapists</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+books</t>
+          <t>https://www.google.com/search?q=best+dbt+books+for+therapists</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>best dbt books</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+certification</t>
+          <t>https://www.google.com/search?q=best+dbt+books</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>data analytics google certification</t>
+          <t>best dbt apps</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+google+certification</t>
+          <t>https://www.google.com/search?q=best+dbt+apps</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+internships</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+salary</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+software+for+integration+platforms</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=business+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+orchestration+tools</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+diagram</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+framework</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>best dbt skills</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+architecture+diagram</t>
+          <t>https://www.google.com/search?q=best+dbt+skills</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>best dbt therapist near me</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+therapist+near+me</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+report+builder</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>best dbt skills</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+skills</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>best dbt podcast</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+podcast</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+vs+analytics+engineering</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+and+tableau</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+things</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+and+how+does+it+work</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+system+design</t>
+          <t>https://www.google.com/search?q=what+is+llm+analytics</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>what is dbt models</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+course+reddit</t>
+          <t>https://www.google.com/search?q=what+is+dbt+models</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>data analytics internships</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+projects</t>
+          <t>https://www.google.com/search?q=data+analytics+internships</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>what is dbt in snowflake</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+manager</t>
+          <t>https://www.google.com/search?q=what+is+dbt+in+snowflake</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>what is dbt fusion</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+interview+questions</t>
+          <t>https://www.google.com/search?q=what+is+dbt+fusion</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>what is dbt data</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+academy</t>
+          <t>https://www.google.com/search?q=what+is+dbt+data</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+projects+for+resume</t>
+          <t>https://www.google.com/search?q=best+power+bi+tutorial+on+youtube</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>best power bi training</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+projects</t>
+          <t>https://www.google.com/search?q=best+power+bi+training</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+podcasts</t>
+          <t>https://www.google.com/search?q=best+power+bi+dashboards</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best power bi courses</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+courses</t>
+          <t>https://www.google.com/search?q=best+power+bi+courses</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship google</t>
+          <t>data analytics salary</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+apprenticeship+google</t>
+          <t>https://www.google.com/search?q=data+analytics+salary</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>dbt mp</t>
+          <t>what is dbt labs</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9069,16 +9069,16 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>0.4178356713426854</v>
+        <v>0.5</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+mp</t>
+          <t>https://www.google.com/search?q=what+is+dbt+labs</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>dbt 2.0</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9097,16 +9097,16 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>0.3537785271271151</v>
+        <v>0.4478957915831664</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+2.0</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>dbt mp</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.4178356713426854</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+mp</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>data and analytics</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9153,16 +9153,16 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.3537643257130241</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>data and analytics</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9209,16 +9209,16 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.2828044398948235</v>
+        <v>0.2975951903807615</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Apparently CodePen 2.0 sends data to their servers as you type</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9237,16 +9237,16 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.2769230769230769</v>
+        <v>0.2975951903807615</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49596976</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>The Dataflow Model Revisited</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9265,16 +9265,16 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0.2744939271255061</v>
+        <v>0.2827930875298557</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>https://www.vldb.org/pvldb/volumes/19/paper/The%20Dataflow%20Model%20Revisited</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>software engineering</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.2214487866562293</v>
+        <v>0.2735470941883767</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=software+engineering</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9321,16 +9321,16 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.1803607214428858</v>
+        <v>0.2214398972362162</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>engineering data management</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.1743486973947896</v>
+        <v>0.1803607214428858</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ai data analytics</t>
+          <t>power bi que es y para que sirve</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.1623246492985972</v>
+        <v>0.1773547094188377</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+que+es+y+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>engineering data management</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0.156312625250501</v>
+        <v>0.1743486973947896</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>power bi report</t>
+          <t>ai data analytics</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0.1292585170340682</v>
+        <v>0.1623246492985972</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
+          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9461,16 +9461,16 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0.1267738503843761</v>
+        <v>0.156312625250501</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>power bi report</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0.1172344689378757</v>
+        <v>0.1292585170340682</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>business data analytics</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9517,16 +9517,16 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.1267687614154106</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>social engineering</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.1172344689378757</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>business data analytics</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.1142284569138277</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>social engineering</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.1142284569138277</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=excel</t>
+          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>download power bi</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -9685,16 +9685,16 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0.1110535717869974</v>
+        <v>0.1112224448897796</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://trends.google.com/trends/explore?q=excel</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -9713,16 +9713,16 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0.1099295477810562</v>
+        <v>0.1112224448897796</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>dbt pdf</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9741,16 +9741,16 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0.1082164328657315</v>
+        <v>0.1110491138630753</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9769,16 +9769,16 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0.1022044088176353</v>
+        <v>0.1099251349778215</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Knap – Turn Data into Markdown</t>
+          <t>dbt pdf</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9797,16 +9797,16 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>0.09959514170040486</v>
+        <v>0.1082164328657315</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>https://knap.md/</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0.09823969811926697</v>
+        <v>0.098235754571182</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>power bi price</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0.09619238476953906</v>
+        <v>0.09318637274549098</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+price</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>power bi free</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Revolut confirms customer data breach, falling for fake government requests</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9993,16 +9993,16 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0.0874493927125506</v>
+        <v>0.08416833667334669</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/revolut-confirms-sensitive-customer-data-breach-falling-fake-government-requests-2026-09-12/</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0.08416833667334669</v>
+        <v>0.0811623246492986</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10049,7 +10049,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>0.0811623246492986</v>
+        <v>0.07214428857715431</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Show HN: Filament – Fast data movement engine in Go</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10077,16 +10077,16 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>0.0728744939271255</v>
+        <v>0.06913827655310621</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>https://github.com/galaxy-io/filament</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0.07214428857715431</v>
+        <v>0.06312625250501003</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0.06913827655310621</v>
+        <v>0.06312625250501003</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10189,16 +10189,16 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.06228448708427835</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.06012024048096192</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10245,16 +10245,16 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>0.06228698741494551</v>
+        <v>0.06012024048096192</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>snowflake dbt</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10301,7 +10301,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.05711422845691383</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.05711422845691383</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10357,16 +10357,16 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>0.05711422845691383</v>
+        <v>0.05645585372217651</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>snowflake dbt</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10385,16 +10385,16 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>0.05711422845691383</v>
+        <v>0.05415972542801517</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>data engineering tools</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10413,16 +10413,16 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>0.05645812006985006</v>
+        <v>0.05410821643286573</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+tools</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Apple wants to train AI on your private personal data</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -10441,16 +10441,16 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>0.05587044534412956</v>
+        <v>0.05244164341769866</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://machinelearning.apple.com/research/introducing-third-generation-of-apple-foundation-models</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>microsoft learn</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10469,16 +10469,16 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>0.05416189960057004</v>
+        <v>0.05110220440881763</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+learn</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>OpenAI: "We use ... de-identified data to improve ChatGPT"</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -10497,16 +10497,16 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>0.0534412955465587</v>
+        <v>0.04919816149168055</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://twitter.com/markchen90/status/2097400166554993041</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -10525,16 +10525,16 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>0.05244374862005982</v>
+        <v>0.04809619238476953</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>microsoft learn</t>
+          <t>data analytics services</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>0.05110220440881763</v>
+        <v>0.04809619238476953</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+learn</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Secret DHS Unit Pulling People over Based on Their Financial Data</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10581,16 +10581,16 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0.05101214574898785</v>
+        <v>0.04809619238476953</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://newrepublic.com/post/215177/secret-dhs-unit-predictive-policiing-people-based-financial-data</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>learn microsoft power bi</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10609,16 +10609,16 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>0.0492001364886293</v>
+        <v>0.04809619238476953</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://trends.google.com/trends/explore?q=learn+microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10637,7 +10637,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.04509018036072144</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>data analytics software</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.04509018036072144</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>learn microsoft power bi</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10693,16 +10693,16 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.04107339983541738</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+microsoft+power+bi</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>data analytics services</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.03907815631262525</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>data analytics platform</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.03907815631262525</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+platform</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10777,16 +10777,16 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>0.04509018036072144</v>
+        <v>0.03869698733516649</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>data analytics software</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10805,16 +10805,16 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>0.04509018036072144</v>
+        <v>0.03835979366959035</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>dbt training</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10833,16 +10833,16 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>0.04107504867425383</v>
+        <v>0.03607214428857716</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>power bi web</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0.03907815631262525</v>
+        <v>0.03607214428857716</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>data analytics tools</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0.03907815631262525</v>
+        <v>0.03006012024048096</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -10917,7 +10917,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>0.03869854077597801</v>
+        <v>0.02960881520582863</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>0.03836133357419563</v>
+        <v>0.02862934789153604</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>dbt training</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -10973,16 +10973,16 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>0.03607214428857716</v>
+        <v>0.02742508480019269</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>0.03006012024048096</v>
+        <v>0.02705410821643287</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>analytics engineer</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -11029,16 +11029,16 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>0.02961000381365288</v>
+        <v>0.02705410821643287</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=analytics+engineer</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Massachusetts hits data centers with new clean power rules</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -11057,16 +11057,16 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0.0291497975708502</v>
+        <v>0.02659012905686129</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/09/massachusetts-hits-data-centers-with-new-clean-power-rules/</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0.02863049717990406</v>
+        <v>0.025193183870903</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>healthcare data analytics</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -11113,16 +11113,16 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>0.02742618574496698</v>
+        <v>0.02404809619238477</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://trends.google.com/trends/explore?q=healthcare+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>financial data analytics</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -11141,16 +11141,16 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0.02705410821643287</v>
+        <v>0.0214037693434759</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=financial+data+analytics</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -11169,16 +11169,16 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>0.02705410821643287</v>
+        <v>0.01994259679264597</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>LG accused of 'egregious invasion of privacy' over TV data collection</t>
+          <t>google data analytics certificate</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -11197,16 +11197,16 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>0.02672064777327935</v>
+        <v>0.01803607214428858</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/09/08/lg-accused-of-egregious-invasion-of-privacy-over-tv-data-collection/5294956</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -11225,16 +11225,16 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0.02659119648341061</v>
+        <v>0.01803607214428858</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -11253,16 +11253,16 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0.0251941952188836</v>
+        <v>0.01503006012024048</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>data analytics healthcare</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>0.02404809619238477</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+healthcare</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>big data and analytics</t>
+          <t>data analytics masters</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>0.02404809619238477</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+and+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Show HN: Forget Rigid Stock Screeners – A Universal Query API for Financial Data</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -11337,16 +11337,16 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>0.02186234817813765</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://financialdata.net/universal-query</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -11365,16 +11365,16 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0.02140462857028161</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>data analytics solutions</t>
+          <t>data analytics consulting</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>0.02104208416833667</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11421,7 +11421,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>0.01994339736255796</v>
+        <v>0.0112558456937559</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11449,16 +11449,16 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>0.0194331983805668</v>
+        <v>0.01005158260241254</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://github.com/sealandseacat/dbmask</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>machine learning data analytics</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -11477,16 +11477,16 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.009409308953696086</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=machine+learning+data+analytics</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>coursera</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.009018036072144289</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=coursera</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>google data analytics certificate</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.009018036072144289</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11561,16 +11561,16 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>0.01503006012024048</v>
+        <v>0.007337976436585513</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>data pipeline development</t>
+          <t>data pipeline solutions</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>0.01503006012024048</v>
+        <v>0.006012024048096191</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Show HN: I licensed $50k of stock market data to do analysis Claude can't</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11617,16 +11617,16 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>0.0145748987854251</v>
+        <v>0.006012024048096191</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://www.athenic.com:443/</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Show HN: AI Brand Visibility for Free Forever</t>
+          <t>masters in data analytics</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11645,16 +11645,16 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>0.0145748987854251</v>
+        <v>0.006012024048096191</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://app.geosurge.ai/login</t>
+          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>data analytics consulting</t>
+          <t>etl data pipeline</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.006012024048096191</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>data analytics class</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -11701,16 +11701,16 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.005459326014089879</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+class</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>data pipeline software</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>data engineering bootcamp</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+bootcamp</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -11785,16 +11785,16 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>0.01125629754521186</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>dbt in data engineering</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -11813,16 +11813,16 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>0.01005198611027478</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Ada: An open-source data analyst that tells you when its own forecast is useless</t>
+          <t>data pipeline examples</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11841,16 +11841,16 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>0.009716599190283401</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://github.com/saineshnakra/automated-data-analyst</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+examples</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>what is big data analytics</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11869,16 +11869,16 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>0.009409686678308344</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11897,16 +11897,16 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>0.009018036072144289</v>
+        <v>0.002713606165827028</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0.007338271010216575</v>
+        <v>0.002488810388776268</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11953,16 +11953,16 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.002039218834674749</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>data pipeline solutions</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11981,16 +11981,16 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.001974991469803103</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>etl data pipeline</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -12009,16 +12009,16 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.001621740963009052</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>0.005459545171714739</v>
+        <v>0.001605684121791141</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>We rebuilt the old Google Analytics on top of GA4's data</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -12065,16 +12065,16 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>0.004858299595141701</v>
+        <v>0.001525399915701584</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>https://github.com/adacahq/adaca-analytics</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>An Analysis of Two Architectures for Agentic Data Analysis</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -12093,16 +12093,16 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>0.004858299595141701</v>
+        <v>0.00147722939204785</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>https://www.starburst.io/blog/an-analysis-of-two-architectures-for-agentic-data-analysis/</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -12121,16 +12121,16 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.001268490456215001</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>data engineering bootcamp</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -12149,16 +12149,16 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.00125243361499709</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+bootcamp</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>data pipeline examples</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -12177,16 +12177,16 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.001188206250125444</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+examples</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>0.002713715100058208</v>
+        <v>0.001188206250125444</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>0.002488910298869955</v>
+        <v>0.001043694679164242</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Summation: AI Data Analyst</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -12261,16 +12261,16 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>0.00242914979757085</v>
+        <v>0.0009794673142925958</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>https://www.summation.com/</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>0.002039300696493447</v>
+        <v>0.0009152399494209503</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>0.001975070753296803</v>
+        <v>0.0007707283784597475</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>dataforgelabs/dataforge-core</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>0.001621806065715261</v>
+        <v>0.000706501013588102</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/dataforgelabs/dataforge-core</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MUJTBA4F/attrition-insights-engineering</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>0.0016057485799161</v>
+        <v>0.0005780462838448106</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>0.001525461150920295</v>
+        <v>0.0004495915541015194</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>0.001477288693522812</v>
+        <v>0.000433534712883608</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>0.001268541378133719</v>
+        <v>0.0003693073480119624</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>0.001252483892334558</v>
+        <v>0.0003211368243582281</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0.001188253949137914</v>
+        <v>0.0002569094594865825</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>Tony405-spec/feature-engineering-healthcare</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>0.001188253949137914</v>
+        <v>0.0001284547297432913</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/Tony405-spec/feature-engineering-healthcare</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>exmergo/dex</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>0.001043736576945465</v>
+        <v>0.0001123978885253799</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://github.com/exmergo/dex</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>0.0009795066337488208</v>
+        <v>0.0001123978885253799</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>0.0009152766905521769</v>
+        <v>9.634104730746844e-05</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
     </row>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>A list of articles on how data teams built their analytics agents</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12653,16 +12653,16 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>0.0007707593183597279</v>
+        <v>0</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/GetCassis/analytics-agent-articles</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>dataforgelabs/dataforge-core</t>
+          <t>Show HN: The Analyst (A data science analytics simulator)</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12681,16 +12681,16 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>0.0007065293751630839</v>
+        <v>0</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>https://github.com/dataforgelabs/dataforge-core</t>
+          <t>https://theanalyst.dev</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>Designing a Dbt Pipeline for Consent Withdrawal</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -12709,16 +12709,16 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>0.0005780694887697959</v>
+        <v>0</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://kore-nordmann.de/blog/designing-a-dbt-pipeline-for-consent-withdrawal.html</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>Dreamerol/ALLSTATS</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>0.000449609602376508</v>
+        <v>0</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>Assembling context for analytics agents from existing data stacks</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -12765,352 +12765,16 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>0.0004335521165773469</v>
+        <v>0</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="n">
-        <v>418</v>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D419" t="n">
-        <v>0.0003693221733807029</v>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="n">
-        <v>419</v>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Dreamerol/Dreamerol</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D420" t="n">
-        <v>0.0003211497159832199</v>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="n">
-        <v>420</v>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>nirholas/bnbchain-mcp</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D421" t="n">
-        <v>0.000256919772786576</v>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="n">
-        <v>421</v>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Tony405-spec/feature-engineering-healthcare</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D422" t="n">
-        <v>0.000128459886393288</v>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>https://github.com/Tony405-spec/feature-engineering-healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="n">
-        <v>422</v>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>exmergo/dex</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D423" t="n">
-        <v>0.000112402400594127</v>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>https://github.com/exmergo/dex</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="n">
-        <v>423</v>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D424" t="n">
-        <v>0.000112402400594127</v>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="n">
-        <v>424</v>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D425" t="n">
-        <v>9.634491479496599e-05</v>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="n">
-        <v>425</v>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Show HN: The Analyst (A data science analytics simulator)</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D426" t="n">
-        <v>0</v>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>https://theanalyst.dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="n">
-        <v>426</v>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Designing a Dbt Pipeline for Consent Withdrawal</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D427" t="n">
-        <v>0</v>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>https://kore-nordmann.de/blog/designing-a-dbt-pipeline-for-consent-withdrawal.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="n">
-        <v>427</v>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Dreamerol/ALLSTATS</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D428" t="n">
-        <v>0</v>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="n">
-        <v>428</v>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Assembling context for analytics agents from existing data stacks</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D429" t="n">
-        <v>0</v>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
           <t>https://blog.getcassis.com/a-blank-beats-a-guess/</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="n">
-        <v>429</v>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>A list of articles on how data teams built their analytics agents</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D430" t="n">
-        <v>0</v>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>https://github.com/GetCassis/analytics-agent-articles</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dbt biocare</t>
+          <t>google data analytics apprenticeship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.368987975951904</v>
+        <v>1.375</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.996993987975952</v>
+        <v>0.98875</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9443887775551102</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8654809619238477</v>
+        <v>0.9775</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8166332665330661</v>
+        <v>0.8875</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -661,16 +661,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.81625</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dbt data</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7715430861723447</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>dbt data</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7565130260521041</v>
+        <v>0.79375</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "dbt biocare" (and what it should mean for your 2026 content plan)</t>
+          <t>Why everyone's suddenly talking about "google data analytics apprenticeship" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dbt biocare</t>
+          <t>google data analytics apprenticeship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.368987975951904</v>
+        <v>1.375</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -866,12 +866,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "data engineering" (and what it should mean for your 2026 content plan)</t>
+          <t>Why everyone's suddenly talking about "data analytics" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -880,11 +880,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.996993987975952</v>
+        <v>0.98875</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Data Engineering, explained in plain English (a 2026 beginner's guide)</t>
+          <t>Why everyone's suddenly talking about "data engineering" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -908,11 +908,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9443887775551102</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "data engineering jobs" (and what it should mean for your 2026 content plan)</t>
+          <t>Data Engineering, explained in plain English (a 2026 beginner's guide)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -936,11 +936,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8654809619238477</v>
+        <v>0.9775</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "power bi desktop" (and what it should mean for your 2026 content plan)</t>
+          <t>Why everyone's suddenly talking about "data engineering jobs" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -964,11 +964,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8166332665330661</v>
+        <v>0.8875</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I tried marketingskills so you don't have to — first impressions</t>
+          <t>Why everyone's suddenly talking about "power bi desktop" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -992,11 +992,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8</v>
+        <v>0.81625</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "dbt data" (and what it should mean for your 2026 content plan)</t>
+          <t>I tried marketingskills so you don't have to — first impressions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dbt data</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7715430861723447</v>
+        <v>0.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dbt, explained in plain English (a 2026 beginner's guide)</t>
+          <t>Why everyone's suddenly talking about "dbt data" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>dbt data</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.7565130260521041</v>
+        <v>0.79375</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F418"/>
+  <dimension ref="A1:F432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dbt biocare</t>
+          <t>google data analytics apprenticeship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.368987975951904</v>
+        <v>1.375</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.996993987975952</v>
+        <v>0.98875</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9443887775551102</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8654809619238477</v>
+        <v>0.9775</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8166332665330661</v>
+        <v>0.8875</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.81625</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dbt data</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7715430861723447</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>dbt data</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7565130260521041</v>
+        <v>0.79375</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7565130260521041</v>
+        <v>0.77125</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7527555110220441</v>
+        <v>0.7675</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7339679358717435</v>
+        <v>0.76</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7301045701784317</v>
+        <v>0.74125</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dbt skills</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7226953907815631</v>
+        <v>0.7374999999999999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+skills</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.718937875751503</v>
+        <v>0.7301045701784317</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>dbt skills</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.7001503006012023</v>
+        <v>0.73</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+skills</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dbt meaning</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.6813627254509018</v>
+        <v>0.7075</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.6776052104208418</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+projects</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>dbt meaning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6625751503006012</v>
+        <v>0.6887500000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+meaning</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>power bi training</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.658817635270541</v>
+        <v>0.6775</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+training</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>what is a data pipeline</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.6583166332665331</v>
+        <v>0.67</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+a+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dbt labs</t>
+          <t>data analytics tools</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.655060120240481</v>
+        <v>0.66625</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+labs</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6437875751503006</v>
+        <v>0.6475</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6437875751503006</v>
+        <v>0.64375</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6400300601202404</v>
+        <v>0.64</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>data pipeline examples</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.6400300601202404</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+examples</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>what is dbt in data engineering</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.6362725450901803</v>
+        <v>0.62875</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>data engineering zoomcamp</t>
+          <t>We rebuilt the old Google Analytics on top of GA4's data</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1901,16 +1901,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.6287575150300601</v>
+        <v>0.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+zoomcamp</t>
+          <t>https://github.com/adacahq/adaca-analytics</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>what is dbt in data engineering</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1929,16 +1929,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.625</v>
+        <v>0.5539449651767256</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt+in+data+engineering</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>We rebuilt the old Google Analytics on top of GA4's data</t>
+          <t>what is a data pipeline</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1957,16 +1957,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.6</v>
+        <v>0.549</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/adacahq/adaca-analytics</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+a+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.5539289083355077</v>
+        <v>0.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://www.google.com/search?q=excel+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+engineering</t>
+          <t>https://www.google.com/search?q=exabeam+ai+agent+analytics</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+analytics+work</t>
+          <t>https://www.google.com/search?q=how+to+design+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+analytics</t>
+          <t>https://www.google.com/search?q=fabric+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>dbt vs spark</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+snowflake</t>
+          <t>https://www.google.com/search?q=dbt+vs+spark</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+engineering</t>
+          <t>https://www.google.com/search?q=glue+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>dbt vs snowflake</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+sql</t>
+          <t>https://www.google.com/search?q=dbt+vs+snowflake</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+pipeline</t>
+          <t>https://www.google.com/search?q=grafana+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>how to dbt</t>
+          <t>dbt vs databricks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+dbt</t>
+          <t>https://www.google.com/search?q=dbt+vs+databricks</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>dbt vs code extension</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+delete+data+analytics+from+iphone</t>
+          <t>https://www.google.com/search?q=dbt+vs+code+extension</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+design+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=visual+studio+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+bas</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>vs dbt</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+dbt</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+youtube</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+start+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+ai+in+analytics</t>
+          <t>https://www.google.com/search?q=how+to+study+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+analytics+for+free</t>
+          <t>https://www.google.com/search?q=how+to+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+accounting</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+databricks</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline+fabric</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+snowflake</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+python</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+healthcare</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+and+visualization</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+simple+words</t>
+          <t>https://www.google.com/search?q=power+bi+vs+tableau</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>or power bi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+job</t>
+          <t>https://www.google.com/search?q=or+power+bi</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>or power bi dax</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+salary</t>
+          <t>https://www.google.com/search?q=or+power+bi+dax</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>or power bi measure</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+used+for</t>
+          <t>https://www.google.com/search?q=or+power+bi+measure</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+vs+data+science</t>
+          <t>https://www.google.com/search?q=or+power+bi+symbol</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>power bi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+all+about</t>
+          <t>https://www.google.com/search?q=power+bi</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>power bi certification</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+and+analytics</t>
+          <t>https://www.google.com/search?q=power+bi+certification</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+and+data+science</t>
+          <t>https://www.google.com/search?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+course</t>
+          <t>https://www.google.com/search?q=power+bi+desktop+download</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+in+simple+words</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=etl+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+accounting</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+role</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+healthcare</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering</t>
+          <t>https://www.google.com/search?q=devops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering+dbt</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+job</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering+reddit</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+salary</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+and+visualization</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+used+for</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+degree</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>data pipeline station</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=etl+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=data+pipeline+station</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+all+about</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=exabeam+ai+agent+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+and+analytics</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>dbt vs sqlmesh</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=excel+vs+power+bi</t>
+          <t>https://www.google.com/search?q=dbt+vs+sqlmesh</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=fabric+vs+power+bi</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+and+data+science</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=glue+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>dbt vs sqlmesh</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+sqlmesh</t>
+          <t>https://www.google.com/search?q=etl+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=devops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+delete+data+analytics+from+iphone</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+reddit</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+simple+words</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>workflow vs data pipeline</t>
+          <t>what is power bi software</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=workflow+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+software</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>what is power bi service</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+over+tableau</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+service</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>best analytics engineering course</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+over+excel</t>
+          <t>https://www.google.com/search?q=best+analytics+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>best analytics engineering books</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+used</t>
+          <t>https://www.google.com/search?q=best+analytics+engineering+books</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>best ai agent analytics tools</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+not+available+for+mac</t>
+          <t>https://www.google.com/search?q=best+ai+agent+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>backend vs data engineering</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+important</t>
+          <t>https://www.google.com/search?q=backend+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>api vs data pipeline</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+better+than+tableau</t>
+          <t>https://www.google.com/search?q=api+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>and data analytics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+better+than+excel</t>
+          <t>https://www.google.com/search?q=and+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+master+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+data+analytics+work</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>ai in analytics</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics</t>
+          <t>https://www.google.com/search?q=ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>why power bi is used</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=top+data+pipeline+solutions</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+used</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>ai in analytics course</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=tableau+vs+power+bi</t>
+          <t>https://www.google.com/search?q=ai+in+analytics+course</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>use of ai in analytics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=statistics+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=use+of+ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=software+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=top+data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+symbol</t>
+          <t>https://www.google.com/search?q=mlops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+measure</t>
+          <t>https://www.google.com/search?q=looker+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+dax</t>
+          <t>https://www.google.com/search?q=llm+analytics+vidhya</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>analytics vs data engineering</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+gateway+went+offline</t>
+          <t>https://www.google.com/search?q=analytics+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>analytics engineering vs data science</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+interview+questions</t>
+          <t>https://www.google.com/search?q=analytics+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>why dbt app is not working</t>
+          <t>analytics engineering vs data engineering</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+app+is+not+working</t>
+          <t>https://www.google.com/search?q=analytics+engineering+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>why dbt</t>
+          <t>analytics engineering salary</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt</t>
+          <t>https://www.google.com/search?q=analytics+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>analytics engineering roundup</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+pipeline</t>
+          <t>https://www.google.com/search?q=analytics+engineering+roundup</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ai vs data engineering</t>
+          <t>analytics engineering podcast</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=analytics+engineering+podcast</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ai vs data analytics</t>
+          <t>analytics engineering manager</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=analytics+engineering+manager</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ai in analytics course</t>
+          <t>analytics engineering jobs</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+in+analytics+course</t>
+          <t>https://www.google.com/search?q=analytics+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ai in analytics</t>
+          <t>analytics engineering course</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+in+analytics</t>
+          <t>https://www.google.com/search?q=analytics+engineering+course</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+stand+for</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ai agent analytics servicenow</t>
+          <t>analytics engineering</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+servicenow</t>
+          <t>https://www.google.com/search?q=analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ai agent analytics platform</t>
+          <t>ai vs data engineering</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+platform</t>
+          <t>https://www.google.com/search?q=ai+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard servicenow</t>
+          <t>ai vs data analytics</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard+servicenow</t>
+          <t>https://www.google.com/search?q=ai+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard</t>
+          <t>https://www.google.com/search?q=why+power+bi+over+tableau</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ai agent analytics</t>
+          <t>vs data analytics</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics</t>
+          <t>https://www.google.com/search?q=vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+reddit</t>
+          <t>https://www.google.com/search?q=why+data+engineering+is+important</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+is+important</t>
+          <t>https://www.google.com/search?q=why+data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>why data analytics</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+courses</t>
+          <t>https://www.google.com/search?q=why+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+certification</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+used+for</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ai agent analytics vidhya</t>
+          <t>analytics engineering best practices</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+vidhya</t>
+          <t>https://www.google.com/search?q=analytics+engineering+best+practices</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=integration+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+analytics+for+free</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=use+of+ai+in+analytics</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+python</t>
+          <t>https://www.google.com/search?q=how+to+learn+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+databricks</t>
+          <t>https://www.google.com/search?q=how+to+get+into+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+big+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+do+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=grafana+vs+power+bi</t>
+          <t>https://www.google.com/search?q=llm+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+study+data+analytics</t>
+          <t>https://www.google.com/search?q=llm+analytics+posthog</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi</t>
+          <t>https://www.google.com/search?q=tableau+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+youtube</t>
+          <t>https://www.google.com/search?q=llm+analytics+meaning</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+dashboard</t>
+          <t>https://www.google.com/search?q=llm+analytics+leaderboard</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to dbt</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+bas</t>
+          <t>https://www.google.com/search?q=how+to+dbt</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to data engineering</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+optimize+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>dbt vs airflow</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=dbt+vs+airflow</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to data analytics</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+master+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+python+for+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+sql</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+start+data+engineering</t>
+          <t>https://www.google.com/search?q=llm+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=mlops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=statistics+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=looker+vs+power+bi</t>
+          <t>https://www.google.com/search?q=software+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>power bi login</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+vidhya</t>
+          <t>https://www.google.com/search?q=power+bi+login</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+vs+tableau</t>
+          <t>https://www.google.com/search?q=llm+analytics+dashboard</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+training</t>
+          <t>https://www.google.com/search?q=llm+analytics+comparison</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+login</t>
+          <t>https://www.google.com/search?q=llm+analytics+benchmark</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>llm analytics</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+download</t>
+          <t>https://www.google.com/search?q=llm+analytics</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+analytics</t>
+          <t>https://www.google.com/search?q=integration+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+benchmark</t>
+          <t>https://www.google.com/search?q=how+to+learn+python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+get+into+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering+dbt</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+do+data+analytics</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>what is ai in analytics</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+tools</t>
+          <t>https://www.google.com/search?q=what+is+ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>vs power bi</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+posthog</t>
+          <t>https://www.google.com/search?q=vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>vs dbt</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+platform</t>
+          <t>https://www.google.com/search?q=vs+dbt</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>how to power bi</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+meaning</t>
+          <t>https://www.google.com/search?q=how+to+power+bi</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+leaderboard</t>
+          <t>https://www.google.com/search?q=how+to+optimize+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+dashboard</t>
+          <t>https://www.google.com/search?q=how+to+master+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+comparison</t>
+          <t>https://www.google.com/search?q=how+to+master+data+analytics</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+analytics+engineering</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>api vs data pipeline</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=api+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=best+data+analytics+certification+reddit</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>backend vs data engineering</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=backend+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=best+data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>best ai agent analytics tools</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+ai+agent+analytics+tools</t>
+          <t>https://www.google.com/search?q=best+data+analytics+courses+reddit</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>best analytics engineering books</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+analytics+engineering+books</t>
+          <t>https://www.google.com/search?q=best+data+analytics+masters+programs</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>best analytics engineering course</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+analytics+engineering+course</t>
+          <t>https://www.google.com/search?q=best+data+analytics+programs</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>best data analytics software</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+books</t>
+          <t>https://www.google.com/search?q=best+data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+bootcamp</t>
+          <t>https://www.google.com/search?q=best+data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+certification</t>
+          <t>https://www.google.com/search?q=best+data+engineering+blogs</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>best data engineering books</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+certification+reddit</t>
+          <t>https://www.google.com/search?q=best+data+engineering+books</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+courses</t>
+          <t>https://www.google.com/search?q=best+data+engineering+bootcamp</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+courses+reddit</t>
+          <t>https://www.google.com/search?q=best+data+engineering+certifications</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>analytics engineering</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering</t>
+          <t>https://www.google.com/search?q=best+data+engineering+certifications+2026</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>best dbt training for therapists</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+training+for+therapists</t>
+          <t>https://www.google.com/search?q=best+data+engineering+course+reddit</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>analytics engineering with sql and dbt pdf</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+books</t>
+          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+certification</t>
+          <t>https://www.google.com/search?q=best+data+engineering+podcasts</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>why dbt is used</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+is+used</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best dbt therapist near me</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+development+services</t>
+          <t>https://www.google.com/search?q=best+dbt+therapist+near+me</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>best dbt skills</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cloud+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=best+dbt+skills</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>best data analytics books</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=business+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=best+data+analytics+books</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>best dbt podcast</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+visuals</t>
+          <t>https://www.google.com/search?q=best+dbt+podcast</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best dbt books for therapists</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+podcasts</t>
+          <t>https://www.google.com/search?q=best+dbt+books+for+therapists</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best dbt books</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+courses</t>
+          <t>https://www.google.com/search?q=best+dbt+books</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>best dbt apps</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+course+reddit</t>
+          <t>https://www.google.com/search?q=best+dbt+apps</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+course+for+beginners</t>
+          <t>https://www.google.com/search?q=best+data+engineering+projects</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+certifications</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+software+for+integration+platforms</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+bootcamp</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+orchestration+tools</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+books</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+framework</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+blogs</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+for+small+business</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+tools</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+development+services</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+software</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>best data pipeline</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+programs</t>
+          <t>https://www.google.com/search?q=best+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+masters+programs</t>
+          <t>https://www.google.com/search?q=best+data+engineering+projects+for+resume</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+certifications+2026</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+important</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data pipeline</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+reddit</t>
+          <t>https://www.google.com/search?q=why+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>accounting vs data analytics</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+used</t>
+          <t>https://www.google.com/search?q=accounting+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+the+future+of+everything</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+not+available+for+mac</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>analytics engineering with sql and dbt</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+the+future</t>
+          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+important</t>
+          <t>https://www.google.com/search?q=why+data+engineering+is+hard</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+a+good+career</t>
+          <t>https://www.google.com/search?q=why+data+analytics+as+a+career</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+course</t>
+          <t>https://www.google.com/search?q=best+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why power bi is important</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+as+a+career</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+important</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+desktop+download</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+better+than+tableau</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>analytics engineering best practices</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+best+practices</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+better+than+excel</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>why dbt is used in data engineering</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+is+used+in+data+engineering</t>
+          <t>https://www.google.com/search?q=why+power+bi+gateway+went+offline</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why dbt is used in data engineering</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+is+hard</t>
+          <t>https://www.google.com/search?q=why+dbt+is+used+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>analytics engineering course</t>
+          <t>why dbt is used</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+course</t>
+          <t>https://www.google.com/search?q=why+dbt+is+used</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>why dbt app is not working</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+architecture</t>
+          <t>https://www.google.com/search?q=why+dbt+app+is+not+working</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline</t>
+          <t>https://www.google.com/search?q=visual+studio+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+projects+for+resume</t>
+          <t>https://www.google.com/search?q=best+data+analytics+bootcamp</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+projects</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+a+good+career</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>accounting vs data analytics</t>
+          <t>why data analytics course</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=accounting+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=why+data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>workflow vs data pipeline</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+used+for</t>
+          <t>https://www.google.com/search?q=workflow+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+stand+for</t>
+          <t>https://www.google.com/search?q=why+power+bi+over+excel</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>and data analytics</t>
+          <t>ai agent analytics</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=and+data+analytics</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>analytics engineering jobs</t>
+          <t>ai agent analytics dashboard</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+jobs</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt pdf</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt+pdf</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+the+future</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt</t>
+          <t>ai agent analytics platform</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>analytics engineering vs data science</t>
+          <t>ai agent analytics servicenow</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+vs+data+science</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+servicenow</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>analytics engineering vs data engineering</t>
+          <t>ai agent analytics vidhya</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+vidhya</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>analytics engineering salary</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+salary</t>
+          <t>https://www.google.com/search?q=why+data+engineering+interview+questions</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>analytics engineering roundup</t>
+          <t>why data engineering</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+roundup</t>
+          <t>https://www.google.com/search?q=why+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>analytics engineering podcast</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+podcast</t>
+          <t>https://www.google.com/search?q=why+data+analytics+reddit</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>analytics engineering manager</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+manager</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+used</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>analytics vs data engineering</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+the+future+of+everything</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>ai agent analytics dashboard servicenow</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+system+design</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard+servicenow</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>data engineering certification</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+things</t>
+          <t>https://www.google.com/search?q=data+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering internship</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+vs+analytics+engineering</t>
+          <t>https://www.google.com/search?q=data+engineering+internship</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+architecture+diagram</t>
+          <t>https://www.google.com/search?q=data+engineering+interview+questions</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>data engineering reddit</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+diagram</t>
+          <t>https://www.google.com/search?q=data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>data engineering salary</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+icon</t>
+          <t>https://www.google.com/search?q=data+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+vs+data+science</t>
+          <t>https://www.google.com/search?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+academy</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+interview+questions</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+manager</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+ai</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+salary</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+skills</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+vs+data+science</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+etl</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+architecture</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+machine+learning</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+development</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+python</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+for+small+business</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+sql</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>best dbt training for therapists</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=database+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=best+dbt+training+for+therapists</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>dbt vs spark</t>
+          <t>dbt vs act</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+spark</t>
+          <t>https://www.google.com/search?q=dbt+vs+act</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>dbt vs snowflake</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+snowflake</t>
+          <t>https://www.google.com/search?q=etl+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>dbt vs databricks</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+databricks</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>dbt vs code extension</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+code+extension</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+skills</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>dbt vs airflow</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+airflow</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>dbt vs act</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+act</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+role</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>why dbt</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+ai</t>
+          <t>https://www.google.com/search?q=why+dbt</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+orchestration</t>
+          <t>https://www.google.com/search?q=data+engineering+vs+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+management</t>
+          <t>https://www.google.com/search?q=dataops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+sql</t>
+          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline+fabric</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+python</t>
+          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+machine+learning</t>
+          <t>https://www.google.com/search?q=database+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+etl</t>
+          <t>https://www.google.com/search?q=data+pipeline+engineer</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+engineering</t>
+          <t>https://www.google.com/search?q=data+pipeline+diagram</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>data pipeline</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+analytics</t>
+          <t>https://www.google.com/search?q=data+pipeline</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+testing</t>
+          <t>https://www.google.com/search?q=data+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship google</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+apprenticeship+google</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+in+simple+words</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+apprenticeship</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+report+builder</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cybersecurity+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>what is power bi dashboard</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cybersecurity+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+software</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+and+how+does+it+work</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>best dbt therapist near me</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+therapist+near+me</t>
+          <t>https://www.google.com/search?q=what+is+llm+analytics</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is dbt used for</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+service</t>
+          <t>https://www.google.com/search?q=what+is+dbt+used+for</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>best dbt podcast</t>
+          <t>data engineering academy</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+podcast</t>
+          <t>https://www.google.com/search?q=data+engineering+academy</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>best dbt books for therapists</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+books+for+therapists</t>
+          <t>https://www.google.com/search?q=best+power+bi+visuals</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>best dbt books</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+books</t>
+          <t>https://www.google.com/search?q=best+power+bi+tutorial+on+youtube</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>best dbt apps</t>
+          <t>best power bi training</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+apps</t>
+          <t>https://www.google.com/search?q=best+power+bi+training</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+tools</t>
+          <t>https://www.google.com/search?q=best+power+bi+dashboards</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best power bi courses</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+software+for+integration+platforms</t>
+          <t>https://www.google.com/search?q=best+power+bi+courses</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+orchestration+tools</t>
+          <t>https://www.google.com/search?q=best+power+bi+course+for+beginners</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best power bi certification</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+framework</t>
+          <t>https://www.google.com/search?q=best+power+bi+certification</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>best dbt skills</t>
+          <t>best power bi books</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+skills</t>
+          <t>https://www.google.com/search?q=best+power+bi+books</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+report+builder</t>
+          <t>https://www.google.com/search?q=best+data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>data pipeline orchestration</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+pro</t>
+          <t>https://www.google.com/search?q=data+pipeline+orchestration</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+desktop</t>
+          <t>https://www.google.com/search?q=data+pipeline+icon</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>what is dbt treatment</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+and+tableau</t>
+          <t>https://www.google.com/search?q=what+is+dbt+treatment</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is dbt labs</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+and+how+does+it+work</t>
+          <t>https://www.google.com/search?q=what+is+dbt+labs</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is dbt data</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+llm+analytics</t>
+          <t>https://www.google.com/search?q=what+is+dbt+data</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>what is dbt models</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+models</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+testing</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+internships</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+orchestration</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>what is dbt in snowflake</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+in+snowflake</t>
+          <t>https://www.google.com/search?q=business+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>what is dbt fusion</t>
+          <t>data analytics salary</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+fusion</t>
+          <t>https://www.google.com/search?q=data+analytics+salary</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>what is dbt data</t>
+          <t>data analytics professional certificate</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+data</t>
+          <t>https://www.google.com/search?q=data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>data analytics masters</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+tutorial+on+youtube</t>
+          <t>https://www.google.com/search?q=data+analytics+masters</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>data analytics jobs entry level</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+training</t>
+          <t>https://www.google.com/search?q=data+analytics+jobs+entry+level</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>data analytics internships</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+dashboards</t>
+          <t>https://www.google.com/search?q=data+analytics+internships</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+courses</t>
+          <t>https://www.google.com/search?q=cybersecurity+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+salary</t>
+          <t>https://www.google.com/search?q=cybersecurity+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>what is dbt labs</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+labs</t>
+          <t>https://www.google.com/search?q=cloud+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>dbt 2.0</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9097,16 +9097,16 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>0.4478957915831664</v>
+        <v>0.5</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+2.0</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+management</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>dbt mp</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0.4178356713426854</v>
+        <v>0.489</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+mp</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>banglarbhumi</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9153,16 +9153,16 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.3537643257130241</v>
+        <v>0.48</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://trends.google.com/trends/explore?q=banglarbhumi</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>social registry wb gov in</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.45</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://trends.google.com/trends/explore?q=social+registry+wb+gov+in</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>data and analytics</t>
+          <t>dbt mp</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.42</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+mp</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>fathom analytics</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.39</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=fathom+analytics</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0.2827930875298557</v>
+        <v>0.3537643257130241</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>software engineering</t>
+          <t>social security.wb.gov.in</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.2735470941883767</v>
+        <v>0.33</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=software+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=social+security.wb.gov.in</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>heap analytics</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9321,16 +9321,16 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.2214398972362162</v>
+        <v>0.33</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=heap+analytics</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.1803607214428858</v>
+        <v>0.3</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>power bi que es y para que sirve</t>
+          <t>data analytics engineering</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.1773547094188377</v>
+        <v>0.3</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+que+es+y+para+que+sirve</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>engineering data management</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0.1743486973947896</v>
+        <v>0.3</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ai data analytics</t>
+          <t>data and analytics</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0.1623246492985972</v>
+        <v>0.3</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9461,16 +9461,16 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0.156312625250501</v>
+        <v>0.2827930875298557</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>power bi report</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9489,16 +9489,16 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0.1292585170340682</v>
+        <v>0.2214398972362162</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>engineering data management</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9517,16 +9517,16 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0.1267687614154106</v>
+        <v>0.183</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
         </is>
       </c>
     </row>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.1172344689378757</v>
+        <v>0.174</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>dbt check</t>
+          <t>ai data analytics</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.159</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+check</t>
+          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>business data analytics</t>
+          <t>power bi report</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.135</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>social engineering</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -9629,16 +9629,16 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.1267687614154106</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>dbt check</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.126</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+check</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.123</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=excel</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.12</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>business data analytics</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9741,16 +9741,16 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0.1110491138630753</v>
+        <v>0.12</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>dbt pdf</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9769,16 +9769,16 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0.1099251349778215</v>
+        <v>0.12</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>dbt pdf</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>0.1082164328657315</v>
+        <v>0.117</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0.09919839679358719</v>
+        <v>0.117</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>dbt status</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0.09919839679358716</v>
+        <v>0.117</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>dbt status</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -9881,16 +9881,16 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0.098235754571182</v>
+        <v>0.114</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9909,16 +9909,16 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0.09318637274549098</v>
+        <v>0.1110491138630753</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9937,16 +9937,16 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>0.09318637274549098</v>
+        <v>0.1099251349778215</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>power bi free</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>0.09318637274549098</v>
+        <v>0.108</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0.08416833667334669</v>
+        <v>0.108</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>power bi price</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0.0811623246492986</v>
+        <v>0.099</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+price</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10049,16 +10049,16 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>0.07214428857715431</v>
+        <v>0.098235754571182</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>0.06913827655310621</v>
+        <v>0.096</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.093</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>business analytics</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.09</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10161,7 +10161,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.078</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10189,16 +10189,16 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>0.06228448708427835</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=travel</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10273,7 +10273,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>snowflake dbt</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10301,7 +10301,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>0.05711422845691383</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>0.05711422845691383</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10357,16 +10357,16 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>0.05645585372217651</v>
+        <v>0.066</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10385,16 +10385,16 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>0.05415972542801517</v>
+        <v>0.063</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>data engineering tools</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>0.05410821643286573</v>
+        <v>0.063</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+tools</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>software engineering</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -10441,16 +10441,16 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>0.05244164341769866</v>
+        <v>0.063</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=software+engineering</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>microsoft learn</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10469,16 +10469,16 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>0.05110220440881763</v>
+        <v>0.06228448708427835</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+learn</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>snowflake dbt</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -10497,16 +10497,16 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>0.04919816149168055</v>
+        <v>0.06</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.06</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>data analytics services</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10553,16 +10553,16 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.05645585372217651</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10581,16 +10581,16 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.05415972542801517</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>learn microsoft power bi</t>
+          <t>data analytics services</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+microsoft+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10637,7 +10637,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>0.04509018036072144</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>data analytics software</t>
+          <t>data analytics platform</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>0.04509018036072144</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>microsoft learn power bi</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10693,16 +10693,16 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>0.04107339983541738</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0.03907815631262525</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10749,16 +10749,16 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>0.03907815631262525</v>
+        <v>0.05244164341769866</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10777,16 +10777,16 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>0.03869698733516649</v>
+        <v>0.051</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>microsoft learn</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10805,16 +10805,16 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>0.03835979366959035</v>
+        <v>0.051</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+learn</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>dbt training</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>0.03607214428857716</v>
+        <v>0.051</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>power bi web</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -10861,16 +10861,16 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0.03607214428857716</v>
+        <v>0.04919816149168055</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>data analytics software</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0.03006012024048096</v>
+        <v>0.048</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -10917,16 +10917,16 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>0.02960881520582863</v>
+        <v>0.045</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>dbt training</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -10945,16 +10945,16 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>0.02862934789153604</v>
+        <v>0.045</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>0.02742508480019269</v>
+        <v>0.04107339983541738</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>study engineering</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>0.02705410821643287</v>
+        <v>0.039</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=study+engineering</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>analytics engineer</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -11029,7 +11029,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>0.02705410821643287</v>
+        <v>0.039</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=analytics+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0.02659012905686129</v>
+        <v>0.03869698733516649</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0.025193183870903</v>
+        <v>0.03835979366959035</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>healthcare data analytics</t>
+          <t>financial data analytics</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>0.02404809619238477</v>
+        <v>0.036</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=healthcare+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=financial+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -11141,16 +11141,16 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0.0214037693434759</v>
+        <v>0.033</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>engineering analytics systems</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -11169,16 +11169,16 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>0.01994259679264597</v>
+        <v>0.033</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+analytics+systems</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>google data analytics certificate</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -11197,7 +11197,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.03</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=exercise</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>prompt engineering</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.03</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=prompt+engineering</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -11253,16 +11253,16 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0.01503006012024048</v>
+        <v>0.02960881520582863</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -11281,16 +11281,16 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.02862934789153604</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>data analytics masters</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11309,16 +11309,16 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.02742508480019269</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>data pipeline software</t>
+          <t>healthcare data analytics</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -11337,7 +11337,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.027</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
+          <t>https://trends.google.com/trends/explore?q=healthcare+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>what is social engineering</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.027</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+social+engineering</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>data analytics consulting</t>
+          <t>big data and analytics</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.027</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+and+analytics</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>data analytics solutions</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11421,16 +11421,16 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>0.0112558456937559</v>
+        <v>0.027</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+solutions</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>0.01005158260241254</v>
+        <v>0.02659012905686129</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>0.009409308953696086</v>
+        <v>0.025193183870903</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>coursera</t>
+          <t>data engineering vs data analytics</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>0.009018036072144289</v>
+        <v>0.024</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=coursera</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11533,16 +11533,16 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>0.009018036072144289</v>
+        <v>0.0214037693434759</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>machine learning data analytics</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11561,16 +11561,16 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>0.007337976436585513</v>
+        <v>0.021</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=machine+learning+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>data pipeline solutions</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.021</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>google data analytics certificate</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.021</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>masters in data analytics</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.021</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>etl data pipeline</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11673,16 +11673,16 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.01994259679264597</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -11701,16 +11701,16 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>0.005459326014089879</v>
+        <v>0.018</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>data analytics consulting</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.018</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>data engineering bootcamp</t>
+          <t>data pipeline development</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.018</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+bootcamp</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.015</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>dbt in data engineering</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -11813,7 +11813,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.015</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+in+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>data pipeline examples</t>
+          <t>data analytics class</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.015</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+examples</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+class</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>what is big data analytics</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.015</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11897,16 +11897,16 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>0.002713606165827028</v>
+        <v>0.015</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>aws data pipeline</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11925,16 +11925,16 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0.002488810388776268</v>
+        <v>0.012</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=aws+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>0.002039218834674749</v>
+        <v>0.0112558456937559</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>0.001974991469803103</v>
+        <v>0.01005158260241254</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>0.001621740963009052</v>
+        <v>0.009409308953696086</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>MUJTBA4F/attrition-insights-engineering</t>
+          <t>etl data pipeline</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -12037,16 +12037,16 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>0.001605684121791141</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>data pipeline solutions</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -12065,16 +12065,16 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>0.001525399915701584</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -12093,16 +12093,16 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>0.00147722939204785</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -12121,7 +12121,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>0.001268490456215001</v>
+        <v>0.007337976436585513</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -12149,16 +12149,16 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0.00125243361499709</v>
+        <v>0.006</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>data engineering zoomcamp</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -12177,16 +12177,16 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>0.001188206250125444</v>
+        <v>0.006</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+zoomcamp</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>0.001188206250125444</v>
+        <v>0.005459326014089879</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>0.001043694679164242</v>
+        <v>0.002713606165827028</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -12261,7 +12261,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>0.0009794673142925958</v>
+        <v>0.002488810388776268</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>0.0009152399494209503</v>
+        <v>0.002039218834674749</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>0.0007707283784597475</v>
+        <v>0.001974991469803103</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>dataforgelabs/dataforge-core</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>0.000706501013588102</v>
+        <v>0.001621740963009052</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>https://github.com/dataforgelabs/dataforge-core</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>0.0005780462838448106</v>
+        <v>0.001605684121791141</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>0.0004495915541015194</v>
+        <v>0.001525399915701584</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>0.000433534712883608</v>
+        <v>0.00147722939204785</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>0.0003693073480119624</v>
+        <v>0.001268490456215001</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>0.0003211368243582281</v>
+        <v>0.00125243361499709</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0.0002569094594865825</v>
+        <v>0.001188206250125444</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Tony405-spec/feature-engineering-healthcare</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>0.0001284547297432913</v>
+        <v>0.001188206250125444</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>https://github.com/Tony405-spec/feature-engineering-healthcare</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>0.0001123978885253799</v>
+        <v>0.001059751520382153</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>0.0001123978885253799</v>
+        <v>0.0009794673142925958</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>9.634104730746844e-05</v>
+        <v>0.0009152399494209503</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>A list of articles on how data teams built their analytics agents</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12653,16 +12653,16 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>0</v>
+        <v>0.0007707283784597475</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>https://github.com/GetCassis/analytics-agent-articles</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Show HN: The Analyst (A data science analytics simulator)</t>
+          <t>dataforgelabs/dataforge-core</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12681,16 +12681,16 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>0</v>
+        <v>0.000706501013588102</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>https://theanalyst.dev</t>
+          <t>https://github.com/dataforgelabs/dataforge-core</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Designing a Dbt Pipeline for Consent Withdrawal</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -12709,16 +12709,16 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>0</v>
+        <v>0.0005780462838448106</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>https://kore-nordmann.de/blog/designing-a-dbt-pipeline-for-consent-withdrawal.html</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>0</v>
+        <v>0.0004495915541015194</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -12756,25 +12756,417 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>0.000433534712883608</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>0.0003693073480119624</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Dreamerol/Dreamerol</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>0.0003211368243582281</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>nirholas/bnbchain-mcp</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>0.0002569094594865825</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Tony405-spec/feature-engineering-healthcare</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>0.0001284547297432913</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>https://github.com/Tony405-spec/feature-engineering-healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>0.0001123978885253799</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>0.0001123978885253799</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>9.634104730746844e-05</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Show HN: The Analyst (A data science analytics simulator)</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>https://theanalyst.dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>machine learning algorithms</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=machine+learning+algorithms</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Designing a Dbt Pipeline for Consent Withdrawal</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>https://kore-nordmann.de/blog/designing-a-dbt-pipeline-for-consent-withdrawal.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>data warehouse design</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+warehouse+design</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
           <t>Assembling context for analytics agents from existing data stacks</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D418" t="n">
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
         <v>0</v>
       </c>
-      <c r="E418" t="inlineStr">
+      <c r="E431" t="inlineStr">
         <is>
           <t>hn</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr">
+      <c r="F431" t="inlineStr">
         <is>
           <t>https://blog.getcassis.com/a-blank-beats-a-guess/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>A list of articles on how data teams built their analytics agents</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>0</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>https://github.com/GetCassis/analytics-agent-articles</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dbt charts</t>
+          <t>meditation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>3.018</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -475,7 +475,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
+          <t>https://trends.google.com/trends/explore?q=meditation</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dbt v2</t>
+          <t>dbt charts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.369565217391304</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
         </is>
       </c>
     </row>
@@ -513,25 +513,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>dbt v2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.369565217391304</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
         </is>
       </c>
     </row>
@@ -541,25 +541,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dbt summit</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9130434782608696</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -569,25 +569,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>dbt summit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7191702488464724</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dbt status tracker</t>
+          <t>data privacy regulations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7173913043478262</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=data+privacy+regulations</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pfms dbt tracker</t>
+          <t>dbt status tracker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
         </is>
       </c>
     </row>
@@ -681,25 +681,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pfms dbt status tracker</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.7191560682243913</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status+tracker</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>pfms dbt tracker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5787878787878787</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
         </is>
       </c>
     </row>
@@ -798,26 +798,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("LightDash Demo: Ultimate Setup Guide for Modern BI Tool on DBT | Charts &amp; Metrics Explained", 4.7k views). Your angle: claim the space — straightforward, solid coverage of "dbt charts" has almost no competition right now.</t>
+          <t>REVISIT — "Flying: Relaxing Sleep Music for Meditation, Stress Relief &amp; Relaxation by Peder B. Helland" has 532.1M views, but it's from 10 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dbt charts</t>
+          <t>meditation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LightDash Demo: Ultimate Setup Guide for Modern BI Tool on DBT | Charts &amp; Metrics Explained</t>
+          <t>Flying: Relaxing Sleep Music for Meditation, Stress Relief &amp; Relaxation by Peder B. Helland</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4709</v>
+        <v>532067862</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>3.018</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
+          <t>https://trends.google.com/trends/explore?q=meditation</t>
         </is>
       </c>
     </row>
@@ -839,26 +839,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PROVEN DEMAND</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PROVEN DEMAND — "Tema El Saxofon 2.0 DBT DjFranyerCarAudio" has 278.1k views from 11 months ago. There's a proven audience for this. Your angle: don't repeat it — bring something only you have (a real client story, a contrarian take, your own data) instead of another generic walkthrough.</t>
+          <t>WHITESPACE — only one relevant video exists ("LightDash Demo: Ultimate Setup Guide for Modern BI Tool on DBT | Charts &amp; Metrics Explained", 4.7k views). Your angle: claim the space — straightforward, solid coverage of "dbt charts" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dbt v2</t>
+          <t>dbt charts</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tema El Saxofon 2.0 DBT DjFranyerCarAudio</t>
+          <t>LightDash Demo: Ultimate Setup Guide for Modern BI Tool on DBT | Charts &amp; Metrics Explained</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>278134</v>
+        <v>4709</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.369565217391304</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
         </is>
       </c>
     </row>
@@ -880,38 +880,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OPPORTUNITY</t>
+          <t>PROVEN DEMAND</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Show HN: Capsule – Single-file web apps that save their data into SQLite #Shorts" at 727 views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
+          <t>PROVEN DEMAND — "Tema El Saxofon 2.0 DBT DjFranyerCarAudio" has 278.1k views from 11 months ago. There's a proven audience for this. Your angle: don't repeat it — bring something only you have (a real client story, a contrarian take, your own data) instead of another generic walkthrough.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>dbt v2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite #Shorts</t>
+          <t>Tema El Saxofon 2.0 DBT DjFranyerCarAudio</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>727</v>
+        <v>278139</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.369565217391304</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
         </is>
       </c>
     </row>
@@ -921,38 +921,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>OPPORTUNITY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REVISIT — "dbt Explained ft. Anders Swanson" has 34.2k views, but it's from 23 months ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Show HN: Capsule – Single-file web apps that save their data into SQLite #Shorts" at 730 views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dbt summit</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dbt Explained ft. Anders Swanson</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite #Shorts</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>34210</v>
+        <v>730</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9130434782608696</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -962,32 +962,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "dbt Explained ft. Anders Swanson" has 34.2k views, but it's from 23 months ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>dbt summit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dbt Explained ft. Anders Swanson</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>34209</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
         </is>
       </c>
     </row>
@@ -997,38 +1003,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Engineering Course for Beginners</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1131737</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7191702488464724</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1043,27 +1043,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "dbt status tracker" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — only one relevant video exists ("WILL INDIAN GOVERNMENT DESTROY YOUR PRIVACY?? #informative #indiangovernment", 1.6M views). Your angle: claim the space — straightforward, solid coverage of "data privacy regulations" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dbt status tracker</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>data privacy regulations</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WILL INDIAN GOVERNMENT DESTROY YOUR PRIVACY?? #informative #indiangovernment</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1647595</v>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7173913043478262</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=data+privacy+regulations</t>
         </is>
       </c>
     </row>
@@ -1078,33 +1084,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se", 1.6M views). Your angle: claim the space — straightforward, solid coverage of "pfms dbt tracker" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "dbt status tracker" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pfms dbt tracker</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1634759</v>
-      </c>
+          <t>dbt status tracker</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
         </is>
       </c>
     </row>
@@ -1114,38 +1114,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se", 1.6M views). Your angle: claim the space — straightforward, solid coverage of "pfms dbt status tracker" has almost no competition right now.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pfms dbt status tracker</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se</t>
+          <t>Data Engineering Course for Beginners</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1634759</v>
+        <v>1131757</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.7191560682243913</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status+tracker</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineer vs. Data Scientist ft. @eczachly_" has 2.1M views, but it's from 22 months ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se", 1.6M views). Your angle: claim the space — straightforward, solid coverage of "pfms dbt tracker" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>pfms dbt tracker</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Engineer vs. Data Scientist ft. @eczachly_</t>
+          <t>pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2145656</v>
+        <v>1634766</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.5787878787878787</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dbt charts</t>
+          <t>meditation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>3.018</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
+          <t>https://trends.google.com/trends/explore?q=meditation</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dbt v2</t>
+          <t>dbt charts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.369565217391304</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
         </is>
       </c>
     </row>
@@ -1298,25 +1298,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>dbt v2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.369565217391304</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
         </is>
       </c>
     </row>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dbt summit</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9130434782608696</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1354,25 +1354,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>dbt summit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7191702488464724</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dbt status tracker</t>
+          <t>data privacy regulations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7173913043478262</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=data+privacy+regulations</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pfms dbt tracker</t>
+          <t>dbt status tracker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
         </is>
       </c>
     </row>
@@ -1466,25 +1466,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pfms dbt status tracker</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.7191560682243913</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status+tracker</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>pfms dbt tracker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5787878787878787</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
         </is>
       </c>
     </row>
@@ -1522,25 +1522,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.5477461844855464</v>
+        <v>0.597</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pfms dbt</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.5444005270092227</v>
+        <v>0.5477353840086759</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pfms dbt status</t>
+          <t>pfms dbt</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.5435217391304348</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dbt boursorama</t>
+          <t>pfms dbt status tracker</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+boursorama</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status+tracker</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dbt bourse</t>
+          <t>dbt boursorama</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.4565217391304348</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+bourse</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+boursorama</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>dbt bourse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.3545454545454546</v>
+        <v>0.4565217391304348</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+bourse</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>pfms dbt status</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1699,16 +1699,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.3481168907993848</v>
+        <v>0.4565217391304348</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.3232</v>
+        <v>0.357</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1755,16 +1755,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.3</v>
+        <v>0.3481100266193434</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1783,16 +1783,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.3</v>
+        <v>0.3296</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>data and analytics</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -1830,25 +1830,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>data and analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.2778877627479592</v>
+        <v>0.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dbt center of orange county</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+center+of+orange+county</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1886,16 +1886,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.2303030303030303</v>
+        <v>0.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.2212121212121212</v>
+        <v>0.2778822833481219</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1951,16 +1951,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.2183065820089127</v>
+        <v>0.234</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -1970,16 +1970,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.2151515151515151</v>
+        <v>0.231</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2007,16 +2007,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.2</v>
+        <v>0.2183022774327122</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -2026,16 +2026,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dbt vs airflow</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1956521739130435</v>
+        <v>0.213</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+vs+airflow</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2054,16 +2054,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.201</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>data pipeline solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.1757575757575758</v>
+        <v>0.1986521739130435</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -2110,16 +2110,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dbt status</t>
+          <t>dbt vs airflow</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1696969696969697</v>
+        <v>0.1956521739130435</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+vs+airflow</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>dbt center of orange county</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.1575757575757576</v>
+        <v>0.1956521739130435</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+center+of+orange+county</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dbt check</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.195</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+check</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -2194,16 +2194,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.195</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -2222,16 +2222,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.1424242424242424</v>
+        <v>0.189</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2250,16 +2250,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dbt skills</t>
+          <t>dbt status</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.1393939393939394</v>
+        <v>0.171</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+skills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>dbt check</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.159</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+check</t>
         </is>
       </c>
     </row>
@@ -2306,16 +2306,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dbt data</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.159</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2334,16 +2334,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.156</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>data pipeline solutions</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.144</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2390,25 +2390,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>dbt skills</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.1247466182908073</v>
+        <v>0.141</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+skills</t>
         </is>
       </c>
     </row>
@@ -2418,16 +2418,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>dbt data</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.135</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>power bi free</t>
+          <t>power bi gateway download</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.1151515151515151</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway+download</t>
         </is>
       </c>
     </row>
@@ -2474,16 +2474,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.1151515151515151</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.1093189257404267</v>
+        <v>0.1247441585329784</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -2530,25 +2530,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.1088</v>
+        <v>0.12</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2567,16 +2567,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.108198919430532</v>
+        <v>0.12</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>power bi free</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.1060606060606061</v>
+        <v>0.117</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.103030303030303</v>
+        <v>0.114</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dbt pdf</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2651,16 +2651,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.103030303030303</v>
+        <v>0.1093167701863354</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>engineering data management</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2679,16 +2679,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.1088</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2707,16 +2707,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.1081967859607611</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2763,16 +2763,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.09660448791260796</v>
+        <v>0.108</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ai data analytics</t>
+          <t>dbt pdf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.09393939393939395</v>
+        <v>0.108</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>business data analytics</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.09393939393939395</v>
+        <v>0.108</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>engineering data management</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.08787878787878788</v>
+        <v>0.102</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>social engineering</t>
+          <t>data engineering and analytics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.099</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+and+analytics</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>ai data analytics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.099</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.0966025830622104</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>business data analytics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.093</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.09</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.07575757575757576</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.07575757575757576</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=travel</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3071,16 +3071,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.07565563749654929</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.081</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.081</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3202,16 +3202,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>social engineering</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.081</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>power bi gateway download</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.06521739130434782</v>
+        <v>0.081</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway+download</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>power bi app</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3267,16 +3267,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.07565414571625752</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+app</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -3286,16 +3286,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>dbt meaning</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.075</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3323,16 +3323,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.06120597862523169</v>
+        <v>0.075</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>snowflake</t>
+          <t>data science pipeline</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.07421739130434782</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake</t>
+          <t>https://trends.google.com/trends/explore?q=data+science+pipeline</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>snowflake dbt</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>business analytics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.066</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3482,25 +3482,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.05330283550893244</v>
+        <v>0.066</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
         </is>
       </c>
     </row>
@@ -3510,25 +3510,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>dbt meaning</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.05167803762274718</v>
+        <v>0.063</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+meaning</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>snowflake dbt</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.05151515151515151</v>
+        <v>0.063</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>dbt training</t>
+          <t>snowflake</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.063</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3603,16 +3603,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.06120477176377798</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop+download</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.057</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>power bi reports</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.057</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+reports</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>power bi reports</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3687,16 +3687,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.04839689237685846</v>
+        <v>0.057</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+reports</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>data analytics services</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.057</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3743,16 +3743,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.04242424242424242</v>
+        <v>0.05330178448190871</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.04076191978546358</v>
+        <v>0.05167701863354038</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>data analytics services</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3799,16 +3799,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.03803289032614268</v>
+        <v>0.051</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.03778049453799739</v>
+        <v>0.04839593808537909</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.048</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3883,16 +3883,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.02923058721457586</v>
+        <v>0.048</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3911,16 +3911,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.02818945458847655</v>
+        <v>0.045</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>data analytics healthcare</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.02727272727272727</v>
+        <v>0.04076111604061915</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+healthcare</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.02697479985802737</v>
+        <v>0.03803214039238884</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.02615451354655519</v>
+        <v>0.03777974958099182</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4023,16 +4023,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.02490830934258785</v>
+        <v>0.036</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -4042,25 +4042,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.02424242424242424</v>
+        <v>0.02923001084491768</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4079,16 +4079,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.02424242424242424</v>
+        <v>0.02818889874790496</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>data analytics healthcare</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.02121212121212121</v>
+        <v>0.027</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+healthcare</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.02121212121212121</v>
+        <v>0.027</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4163,16 +4163,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.02110659778364949</v>
+        <v>0.027</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.01970264621209133</v>
+        <v>0.02697426796805679</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.02615399783101646</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -4238,25 +4238,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.02490781819974366</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -4266,16 +4266,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>data analytics masters</t>
+          <t>data analytics tools</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.01212121212121212</v>
+        <v>0.024</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4303,16 +4303,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.01212121212121212</v>
+        <v>0.02110618160307601</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.01140513467681508</v>
+        <v>0.01970225771468008</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -4350,25 +4350,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.009953858894979691</v>
+        <v>0.018</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4387,16 +4387,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.009401743108411879</v>
+        <v>0.018</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4406,16 +4406,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.00909090909090909</v>
+        <v>0.015</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>data analytics masters</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.007256378909176953</v>
+        <v>0.015</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>google data analytics certificate</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4471,16 +4471,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.006399999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
         </is>
       </c>
     </row>
@@ -4490,25 +4490,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.006399999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4518,16 +4518,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.012</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>google data analytics certificate</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4555,16 +4555,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.01140490979000296</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>what is big data analytics</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4583,16 +4583,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.009953662624470078</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>masters in data analytics</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4611,16 +4611,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.009401557724539092</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>masters in data analytics</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4639,16 +4639,16 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.005394959971605474</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0032</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>what is big data analytics</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4695,16 +4695,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.003186496825334227</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>aws data pipeline</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4723,16 +4723,16 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.007256235827664399</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=aws+data+pipeline</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -4742,25 +4742,25 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.006399999999999999</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4770,25 +4770,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.006399999999999999</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4798,16 +4798,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>data pipeline software</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.006</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.006</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4863,16 +4863,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.002744804196079978</v>
+        <v>0.006</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4891,16 +4891,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.002034941041921363</v>
+        <v>0.006</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -4910,25 +4910,25 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.001956067358125961</v>
+        <v>0.006</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.001719446306739756</v>
+        <v>0.005394853593611358</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MUJTBA4F/attrition-insights-engineering</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4975,16 +4975,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.001609023149426194</v>
+        <v>0.0032</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.001530149465630792</v>
+        <v>0.003186433993887411</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5031,16 +5031,16 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.001482825255353551</v>
+        <v>0.003</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5059,16 +5059,16 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.001277753677485507</v>
+        <v>0.003</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5087,16 +5087,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.001277753677485507</v>
+        <v>0.003</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>etl data pipeline</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.001261978940726427</v>
+        <v>0.003</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5134,25 +5134,25 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.001198879993690105</v>
+        <v>0.003</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.001198879993690105</v>
+        <v>0.00274475007394262</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.001167330520171945</v>
+        <v>0.002034900916888494</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.001009583152581141</v>
+        <v>0.001956028788326925</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.0007887368379540168</v>
+        <v>0.001719412402642216</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.0005994399968450527</v>
+        <v>0.001608991422656019</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.0004890168395314903</v>
+        <v>0.001530119294094449</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.00047324210277241</v>
+        <v>0.001482796016957508</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.0003943684189770084</v>
+        <v>0.001277728482697427</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.0003470442086997673</v>
+        <v>0.001277728482697427</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.000283945261663446</v>
+        <v>0.001261954056985113</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.000189296841108964</v>
+        <v>0.001198856354135857</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.000141972630831723</v>
+        <v>0.001198856354135857</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.0001261978940726427</v>
+        <v>0.001167307502711229</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3.154947351816067e-05</v>
+        <v>0.00100956324558809</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5563,7 +5563,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1.577473675908033e-05</v>
+        <v>0.0007887212856156956</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Amey-Thakur/OPTIMIZING-STOCK-TRADING-STRATEGY-WITH-K-MEANS-CLUSTERING</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>0.0005994281770679287</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://github.com/Amey-Thakur/OPTIMIZING-STOCK-TRADING-STRATEGY-WITH-K-MEANS-CLUSTERING</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5619,16 +5619,16 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>0.0004890071970817312</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5647,16 +5647,16 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>0.0004732327713694173</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -5666,25 +5666,25 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>0.0003943606428078478</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>etl data pipeline</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5703,16 +5703,16 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>0.0003470373656709061</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5731,16 +5731,16 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>0.0002839396628216504</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5759,16 +5759,16 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>0.0001892931085477669</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -5778,23 +5778,219 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.0001419698314108252</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.0001261954056985113</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>3.154885142462782e-05</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1.577442571231391e-05</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Amey-Thakur/OPTIMIZING-STOCK-TRADING-STRATEGY-WITH-K-MEANS-CLUSTERING</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://github.com/Amey-Thakur/OPTIMIZING-STOCK-TRADING-STRATEGY-WITH-K-MEANS-CLUSTERING</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://etlfunnel.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
           <t>what does dbt stand for</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
         <v>0</v>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=what+does+dbt+stand+for</t>
         </is>
@@ -5811,7 +6007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A278"/>
+  <dimension ref="A1:A279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6370,7 +6566,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship</t>
+          <t>data analytics apprenticeship google</t>
         </is>
       </c>
     </row>
@@ -6412,21 +6608,21 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>data analytics meaning</t>
+          <t>data analytics jobs remote</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>data analytics wsu</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
@@ -7056,21 +7252,21 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi app</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>power bi dashboard examples</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
@@ -7217,544 +7413,551 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>what is dbt data</t>
+          <t>what is dbt</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>what is dbt in data engineering</t>
+          <t>what is dbt data</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>what is dbt treatment</t>
+          <t>what is dbt in data engineering</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>what is dbt used for</t>
+          <t>what is dbt treatment</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is dbt used for</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>what is power bi dashboard</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>why dbt</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>why dbt app is not working</t>
+          <t>why dbt</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>why dbt is used</t>
+          <t>why dbt app is not working</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>why dbt is used in data engineering</t>
+          <t>why dbt is used</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why dbt is used in data engineering</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/report.xlsx
+++ b/report.xlsx
@@ -457,25 +457,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -494,16 +494,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7174576970697483</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5470746614782933</v>
+        <v>0.7174593192359091</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.5909090909090908</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -597,16 +597,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3470864532358549</v>
+        <v>0.547063910069963</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2769962462905096</v>
+        <v>0.4946808510638298</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -653,25 +653,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2265957446808511</v>
+        <v>0.3470953541388256</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -681,25 +681,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2178173456753729</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -709,25 +709,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1243794587583279</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -798,38 +798,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OPPORTUNITY</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
+          <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1114</v>
+        <v>41873</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -839,32 +839,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>OPPORTUNITY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1114</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -874,38 +880,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Data Engineering Course for Beginners</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1133434</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7174576970697483</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -915,26 +915,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
+          <t>Data Engineering Course for Beginners</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79875</v>
+        <v>1133477</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -942,11 +942,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5470746614782933</v>
+        <v>0.7174593192359091</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -961,21 +961,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data", 30 views). Your angle: claim the space — straightforward, solid coverage of "Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("What is Data Pipeline | How to design Data Pipeline ? - ETL vs Data pipeline (2025)", 1.3M views). Your angle: claim the space — straightforward, solid coverage of "what is data pipeline" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>What is Data Pipeline | How to design Data Pipeline ? - ETL vs Data pipeline (2025)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>1260783</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.5909090909090908</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1002,33 +1002,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
+          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>619941</v>
+        <v>79875</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3470864532358549</v>
+        <v>0.547063910069963</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1038,26 +1038,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data", 30 views). Your angle: claim the space — straightforward, solid coverage of "Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>16539261</v>
+        <v>30</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1065,11 +1065,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.2769962462905096</v>
+        <v>0.4946808510638298</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1084,27 +1084,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "Open-sourced jev architecture last year with model,paper and dataset" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>airbytehq/airbyte</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Airbyte 2.0: Enterprise Flex</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>619941</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.2265957446808511</v>
+        <v>0.3470953541388256</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1119,33 +1125,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>7655693</v>
-      </c>
+          <t>data engineering</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.2178173456753729</v>
+        <v>0.3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1155,38 +1155,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — no real YouTube coverage of "what is data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>John Cooper Clarke - Evidently Chickentown</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2001363</v>
-      </c>
+          <t>what is data engineering</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.1243794587583279</v>
+        <v>0.3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,25 +1236,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1264,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1279,16 +1273,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1292,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,7 +1301,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7174576970697483</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1316,7 +1310,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1320,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1335,7 +1329,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5470746614782933</v>
+        <v>0.7174593192359091</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1344,7 +1338,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1348,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1363,16 +1357,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.5909090909090908</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1382,16 +1376,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3470864532358549</v>
+        <v>0.547063910069963</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1400,7 +1394,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1404,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1419,16 +1413,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2769962462905096</v>
+        <v>0.4946808510638298</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1438,25 +1432,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2265957446808511</v>
+        <v>0.3470953541388256</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1466,25 +1460,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2178173456753729</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1494,25 +1488,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1243794587583279</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1522,25 +1516,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1090187292415935</v>
+        <v>0.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1544,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1559,16 +1553,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1078552758288623</v>
+        <v>0.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -1578,16 +1572,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.09634652044887292</v>
+        <v>0.2769908026098577</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1596,7 +1590,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1606,25 +1600,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.07556158245386475</v>
+        <v>0.2696969696969697</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -1634,25 +1628,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06100269245130988</v>
+        <v>0.2393939393939394</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -1662,25 +1656,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.05312579840025156</v>
+        <v>0.2363636363636363</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1684,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1699,16 +1693,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.05153784171530767</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1712,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1727,16 +1721,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.0482361495980976</v>
+        <v>0.2297872340425532</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1746,16 +1740,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.0406894247587603</v>
+        <v>0.2178130650106124</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1764,7 +1758,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1768,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1783,16 +1777,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.03789084763083938</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1796,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1811,16 +1805,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.0376392901361948</v>
+        <v>0.2060606060606061</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -1830,25 +1824,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.02914922469194034</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -1858,25 +1852,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>download power bi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.02808010533970089</v>
+        <v>0.1575757575757576</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
         </is>
       </c>
     </row>
@@ -1886,25 +1880,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.02690092958355443</v>
+        <v>0.1545454545454545</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -1914,25 +1908,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.02606764538254427</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -1942,25 +1936,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.02485702493956725</v>
+        <v>0.1454545454545454</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -1970,25 +1964,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.02103649548965273</v>
+        <v>0.1424242424242424</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1992,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2007,7 +2001,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.01962148458227699</v>
+        <v>0.1243770143856615</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2016,7 +2010,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2020,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2035,16 +2029,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.01132008725900596</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2048,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2063,16 +2057,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.009967965725291355</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2082,25 +2076,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.009401961362341059</v>
+        <v>0.1121212121212121</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2104,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2119,7 +2113,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.007216555627616296</v>
+        <v>0.109016586746325</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2128,7 +2122,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2132,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2147,16 +2141,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.1078531561984121</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2160,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2175,16 +2169,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.103030303030303</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2188,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2203,16 +2197,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.09696969696969697</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2216,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2231,7 +2225,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.005377041448027829</v>
+        <v>0.09634462699473312</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2240,7 +2234,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2244,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2259,16 +2253,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.003411748521117072</v>
+        <v>0.09393939393939395</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2272,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2287,16 +2281,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.003191489361702127</v>
+        <v>0.09393939393939395</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2300,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2315,16 +2309,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.002735687754259773</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2328,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2343,16 +2337,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.002012459957156614</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2356,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2371,16 +2365,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.001933848240080184</v>
+        <v>0.0818181818181818</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2384,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2399,16 +2393,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.001729457775681465</v>
+        <v>0.07575757575757576</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2412,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2427,7 +2421,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.001650846058605035</v>
+        <v>0.07557581951104474</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2436,7 +2430,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2440,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2455,16 +2449,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.001525067311282747</v>
+        <v>0.07272727272727272</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2468,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2483,16 +2477,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.001509344967867461</v>
+        <v>0.06969696969696969</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2496,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2511,16 +2505,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.001462177937621603</v>
+        <v>0.06969696969696969</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -2530,25 +2524,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.001257787473222884</v>
+        <v>0.06969696969696969</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2552,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2567,16 +2561,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.001257787473222884</v>
+        <v>0.06969696969696969</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2580,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2595,16 +2589,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.001242065129807598</v>
+        <v>0.06363636363636363</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2608,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2623,16 +2617,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.00119489809956174</v>
+        <v>0.06363636363636363</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2636,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2651,16 +2645,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.001163453412731168</v>
+        <v>0.06363636363636363</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2664,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2679,7 +2673,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.001021952321993593</v>
+        <v>0.06100149359327098</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2688,7 +2682,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2692,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2707,16 +2701,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0007703948273490164</v>
+        <v>0.0606060606060606</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -2726,25 +2720,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.0005817267063655838</v>
+        <v>0.05454545454545454</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2748,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2763,16 +2757,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.0004716703024585814</v>
+        <v>0.05454545454545454</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2776,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2791,7 +2785,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.0004559479590432955</v>
+        <v>0.05312475434321201</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2800,7 +2794,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2804,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2819,7 +2813,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.0003773362419668652</v>
+        <v>0.05153682886565522</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2828,7 +2822,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2832,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>power bi download desktop</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2847,16 +2841,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.000330169211721007</v>
+        <v>0.05151515151515151</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2860,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2875,16 +2869,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0002830021814751489</v>
+        <v>0.04848484848484848</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2888,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2903,16 +2897,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0001729457775681465</v>
+        <v>0.04848484848484848</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2916,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2931,7 +2925,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.0001257787473222884</v>
+        <v>0.04823520163509158</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2940,7 +2934,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2944,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>power bi web</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2959,16 +2953,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0001100564039070023</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
         </is>
       </c>
     </row>
@@ -2978,25 +2972,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.572234341528605e-05</v>
+        <v>0.04242424242424242</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3000,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3015,7 +3009,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>0.04068862510808899</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3024,7 +3018,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3028,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3043,7 +3037,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.03789010297932553</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3052,7 +3046,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3056,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3071,16 +3065,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>0.03763855042842544</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -3090,25 +3084,1873 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>data engineering consulting</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>data engineering courses</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>data scientist</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>dbt</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>EVERGREEN</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>google analytics</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.02914865183554752</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>dbt-labs/dbt-utils</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.02807955349422216</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>google data analytics professional certificate</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.02727272727272727</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hiflylabs/awesome-dbt</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.026900400911878</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Multiwoven/multiwoven</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.02606713308702146</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://github.com/Multiwoven/multiwoven</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kaelio/ktx</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.0248565364358148</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://github.com/Kaelio/ktx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>duckdb/dbt-duckdb</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.02103608206901973</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>astronomer/astronomer-cosmos</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01962109897020674</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>snowflake data engineering</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>python for data engineering</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>dbt data engineering</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>google data analytics certification</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01212121212121212</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>mikehasa/agentacct</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01131986479050389</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://github.com/mikehasa/agentacct</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>zhongyu09/openchatbi</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.009967769829415926</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://github.com/zhongyu09/openchatbi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TimeCopilot/timecopilot</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.009401776589890732</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>data pipeline development</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.00909090909090909</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.007216413803946231</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.006382978723404255</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.006382978723404255</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://sentralis.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.006382978723404255</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>data pipeline tools</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.006060606060606061</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>upgini/upgini</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.005376935775489349</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://github.com/upgini/upgini</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AngusKit/AngusKit</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.003411681471582423</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://github.com/AngusKit/AngusKit</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>We Benchmark Analytics Agents, this explains how</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.003191489361702127</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>dbt analytics engineering certification</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>big data pipeline</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>data pipeline architecture</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>data pipeline platform</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>data pipeline aws</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>data pipeline meaning</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>data pipeline monitoring</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cesarjoquin/Marketing-Skills</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.00273563399103844</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>colossus-lab/openarg_backend</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.002012420407200692</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.001933810235044415</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>surfalytics/data-projects</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.001729423787438095</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://github.com/surfalytics/data-projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Chrisinho8/DACH-data-job-market</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.001650813615281818</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>decisionbox-io/decisionbox-platform</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.001525037339831774</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>docwire/docwire</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.001509315305400519</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://github.com/docwire/docwire</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Shaf2665/Hermes-router</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.001462149202106753</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ellie886/Datalume</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.001257762754500433</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://github.com/ellie886/Datalume</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>marieai/marie-ai</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.001257762754500433</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://github.com/marieai/marie-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ESIPFed/Geoweaver</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.001242040720069177</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ServiceNow/SyGra</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.001194874616775411</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://github.com/ServiceNow/SyGra</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>social-media-skills/skills</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0.0011634305479129</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://github.com/social-media-skills/skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>agentscope-ai/QwenPaw-Data</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.001021932238031601</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.0007703796871315148</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Priyanshu-byte-coder/contextrot</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0.00058171527395645</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.0004716610329376621</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>pella-labs/pellametric</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.0004559389985064068</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://github.com/pella-labs/pellametric</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0.0003773288263501297</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Dreamerol/Dreamerol</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0.0003301627230563635</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>nirholas/bnbchain-mcp</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0.0002829966197625973</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0.0001729423787438095</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.0001257762754500433</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0.0001100542410187878</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1.572203443125541e-05</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>etl data pipeline</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>power bi para que sirve</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
         <v>0</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>hn</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -3123,7 +4965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A247"/>
+  <dimension ref="A1:A249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3633,63 +5475,63 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship google</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data analytics entry level jobs</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>data analytics google certification</t>
+          <t>data analytics internship</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data analytics jobs remote</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
@@ -3710,56 +5552,56 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data engineering certification</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
     </row>
@@ -3780,14 +5622,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
     </row>
@@ -3808,1048 +5650,1062 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>data pipeline station</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi course</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>use of ai in analytics</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is ai in analytics</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
+        <is>
+          <t>why power bi over excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/report.xlsx
+++ b/report.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,16 +466,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -485,25 +485,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7174593192359091</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5909090909090908</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -597,16 +597,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.547063910069963</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -625,25 +625,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -653,16 +653,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3470953541388256</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -709,25 +709,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -803,21 +803,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Avoiding circular dependency errors in DAX</t>
+          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>41873</v>
+        <v>16539891</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -839,38 +839,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OPPORTUNITY</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
+          <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1114</v>
+        <v>619941</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "Fast wavedash on pad (Lightdash handcam)" has 48.8k views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>lightdash/lightdash</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fast wavedash on pad (Lightdash handcam)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>48791</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -905,7 +911,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -915,38 +921,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Engineering Course for Beginners</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1133477</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7174593192359091</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -961,21 +961,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("What is Data Pipeline | How to design Data Pipeline ? - ETL vs Data pipeline (2025)", 1.3M views). Your angle: claim the space — straightforward, solid coverage of "what is data pipeline" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>What is Data Pipeline | How to design Data Pipeline ? - ETL vs Data pipeline (2025)</t>
+          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1260783</v>
+        <v>7656650</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.5909090909090908</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1002,33 +1002,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("ClearML Introduction", 319.8k views). Your angle: claim the space — straightforward, solid coverage of "clearml/clearml" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
+          <t>ClearML Introduction</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>79875</v>
+        <v>319846</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.547063910069963</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1038,38 +1038,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data", 30 views). Your angle: claim the space — straightforward, solid coverage of "Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data" has almost no competition right now.</t>
+          <t>REVISIT — "I suspect someone is playing tricks, but I have no evidence" has 364.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>I suspect someone is playing tricks, but I have no evidence</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>364126461</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1079,38 +1079,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
+          <t>John Cooper Clarke - Evidently Chickentown</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>619941</v>
+        <v>2001414</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.3470953541388256</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1125,27 +1125,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>data engineering</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>langfuse/langfuse</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>79875</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1155,32 +1161,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "what is data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Engineering Course for Beginners</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1133490</v>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,7 +1248,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1245,16 +1257,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1264,25 +1276,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1304,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1310,7 +1322,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1332,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1329,7 +1341,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7174593192359091</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1338,7 +1350,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1360,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1357,16 +1369,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5909090909090908</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1376,16 +1388,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.547063910069963</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1394,7 +1406,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1404,25 +1416,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1432,16 +1444,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3470953541388256</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1450,7 +1462,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1472,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1469,16 +1481,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1488,25 +1500,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1516,25 +1528,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3</v>
+        <v>0.772</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1556,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1553,16 +1565,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.3</v>
+        <v>0.62336</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1584,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2769908026098577</v>
+        <v>0.5655</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1600,25 +1612,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2696969696969697</v>
+        <v>0.5432</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1628,25 +1640,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2393939393939394</v>
+        <v>0.5270400000000001</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1656,25 +1668,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2363636363636363</v>
+        <v>0.49344</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1696,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1693,16 +1705,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.4192</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1724,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1721,16 +1733,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.2297872340425532</v>
+        <v>0.3881600000000001</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1740,16 +1752,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.2178130650106124</v>
+        <v>0.3856</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1758,7 +1770,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1768,16 +1780,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.36</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1786,7 +1798,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1808,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1805,16 +1817,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2060606060606061</v>
+        <v>0.2992</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -1824,25 +1836,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.28832</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1864,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1575757575757576</v>
+        <v>0.27632</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -1880,25 +1892,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1545454545454545</v>
+        <v>0.26784</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -1908,25 +1920,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.25552</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1948,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>data pipeline solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1945,7 +1957,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.2412</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1954,7 +1966,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1976,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1973,16 +1985,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1424242424242424</v>
+        <v>0.234</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1992,7 +2004,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2001,7 +2013,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.1243770143856615</v>
+        <v>0.21664</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2010,7 +2022,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2032,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2029,16 +2041,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.20224</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2048,16 +2060,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.1182</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2066,7 +2078,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2076,25 +2088,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.1121212121212121</v>
+        <v>0.11776</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2116,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2113,16 +2125,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.109016586746325</v>
+        <v>0.1095</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2144,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2141,7 +2153,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.1078531561984121</v>
+        <v>0.104</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2150,7 +2162,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2172,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2169,16 +2181,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.103030303030303</v>
+        <v>0.09824000000000001</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2200,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2197,16 +2209,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.09696969696969697</v>
+        <v>0.07600000000000001</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -2216,25 +2228,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.09634462699473312</v>
+        <v>0.06</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2256,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2253,7 +2265,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.09393939393939395</v>
+        <v>0.06</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2262,7 +2274,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2272,16 +2284,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.09393939393939395</v>
+        <v>0.06</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2290,7 +2302,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2312,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2309,16 +2321,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.05728</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -2328,16 +2340,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.054</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2346,7 +2358,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2356,16 +2368,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.048</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2374,7 +2386,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2396,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.07575757575757576</v>
+        <v>0.0474</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2402,7 +2414,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2412,25 +2424,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.07557581951104474</v>
+        <v>0.0474</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2452,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2449,7 +2461,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.0456</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2458,7 +2470,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2480,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2477,7 +2489,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2486,7 +2498,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2508,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2505,7 +2517,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.0414</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2514,7 +2526,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2524,25 +2536,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.03728</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2564,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>power bi report</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2561,7 +2573,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.0336</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2570,7 +2582,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
         </is>
       </c>
     </row>
@@ -2580,16 +2592,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.0336</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2598,7 +2610,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2608,16 +2620,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>download power bi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.03179999999999999</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2626,7 +2638,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
         </is>
       </c>
     </row>
@@ -2636,16 +2648,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.0312</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2654,7 +2666,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2676,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2673,7 +2685,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.06100149359327098</v>
+        <v>0.0304</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2682,7 +2694,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -2692,16 +2704,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.0294</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2710,7 +2722,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2732,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2729,7 +2741,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.0288</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2738,7 +2750,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2760,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>engineering data management</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2757,7 +2769,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.0276</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2766,7 +2778,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2788,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2785,16 +2797,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.05312475434321201</v>
+        <v>0.0246</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2816,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2813,16 +2825,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.05153682886565522</v>
+        <v>0.0246</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2844,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>power bi download desktop</t>
+          <t>data analytics software</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2841,7 +2853,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.05151515151515151</v>
+        <v>0.024</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2850,7 +2862,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2872,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>power bi curso</t>
+          <t>power bi free</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2869,7 +2881,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.0234</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2878,7 +2890,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2900,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>data science and engineering</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2897,7 +2909,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.0234</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2906,7 +2918,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=data+science+and+engineering</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2928,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2925,7 +2937,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.04823520163509158</v>
+        <v>0.02304</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2934,7 +2946,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -2944,16 +2956,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power bi web</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.0228</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2962,7 +2974,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2972,25 +2984,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.04242424242424242</v>
+        <v>0.02224</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3012,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>social engineering</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3009,16 +3021,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.04068862510808899</v>
+        <v>0.021</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3040,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3037,7 +3049,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.03789010297932553</v>
+        <v>0.02016</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3046,7 +3058,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3068,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3065,16 +3077,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.03763855042842544</v>
+        <v>0.0198</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3093,16 +3105,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.01936</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -3112,16 +3124,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.0192</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3130,7 +3142,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3152,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3149,7 +3161,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.0192</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3158,7 +3170,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -3168,16 +3180,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.0186</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3186,7 +3198,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3208,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3205,7 +3217,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.0186</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3214,7 +3226,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3236,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3233,7 +3245,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.02914865183554752</v>
+        <v>0.01808</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3242,7 +3254,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3264,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3261,7 +3273,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.02807955349422216</v>
+        <v>0.01792</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3270,7 +3282,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3292,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3289,16 +3301,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.02727272727272727</v>
+        <v>0.01744</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3320,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3317,16 +3329,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.026900400911878</v>
+        <v>0.0168</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3345,16 +3357,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.02606713308702146</v>
+        <v>0.0156</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3364,25 +3376,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>data analytics tools</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0248565364358148</v>
+        <v>0.0156</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3404,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3401,7 +3413,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.02103608206901973</v>
+        <v>0.01536</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3410,7 +3422,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3432,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3429,7 +3441,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.01962109897020674</v>
+        <v>0.01536</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3438,7 +3450,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3460,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3457,16 +3469,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.01818181818181818</v>
+        <v>0.0152</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3488,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>python for data engineering</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3485,7 +3497,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.015</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3494,7 +3506,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3516,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3513,16 +3525,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.01472</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3544,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3541,7 +3553,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.01212121212121212</v>
+        <v>0.0144</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3550,7 +3562,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3572,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3569,16 +3581,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.01131986479050389</v>
+        <v>0.0144</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3600,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3597,7 +3609,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.009967769829415926</v>
+        <v>0.0144</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3606,7 +3618,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3628,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3625,16 +3637,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.009401776589890732</v>
+        <v>0.0132</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3656,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>data pipeline development</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3653,7 +3665,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.00909090909090909</v>
+        <v>0.0132</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3662,7 +3674,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3684,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3681,7 +3693,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.007216413803946231</v>
+        <v>0.01296</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3690,7 +3702,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3712,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3709,16 +3721,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.0126</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3740,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3737,16 +3749,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.0114</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3768,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>download power bi desktop</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3765,16 +3777,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.006382978723404255</v>
+        <v>0.0108</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -3784,25 +3796,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.0104</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3824,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3821,16 +3833,16 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.005376935775489349</v>
+        <v>0.0102</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3852,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3849,16 +3861,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.003411681471582423</v>
+        <v>0.0102</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3880,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>data analytics consulting</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3877,16 +3889,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.003191489361702127</v>
+        <v>0.0102</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3908,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>data engineering tools</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3905,7 +3917,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3914,7 +3926,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+tools</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3936,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>data analytics masters</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3933,7 +3945,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3942,7 +3954,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
         </is>
       </c>
     </row>
@@ -3952,16 +3964,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>feature engineering</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3970,7 +3982,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://trends.google.com/trends/explore?q=feature+engineering</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3992,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3989,16 +4001,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.00848</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4020,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4017,16 +4029,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.00736</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4036,16 +4048,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.0072</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4054,7 +4066,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4076,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4073,16 +4085,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.0072</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -4092,25 +4104,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.00273563399103844</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4132,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4129,7 +4141,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.002012420407200692</v>
+        <v>0.0064</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4138,7 +4150,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4160,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4157,16 +4169,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.001933810235044415</v>
+        <v>0.006</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4188,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4185,16 +4197,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.001729423787438095</v>
+        <v>0.006</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4216,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4213,7 +4225,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.001650813615281818</v>
+        <v>0.005920000000000001</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4222,7 +4234,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4244,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4241,7 +4253,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.001525037339831774</v>
+        <v>0.00544</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4250,7 +4262,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4272,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>what is big data analytics</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4269,16 +4281,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.001509315305400519</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4300,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>masters in data analytics</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4297,16 +4309,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.001462149202106753</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4328,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>coursera</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,16 +4337,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.001257762754500433</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=coursera</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4356,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4353,16 +4365,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.001257762754500433</v>
+        <v>0.0045</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4384,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4381,16 +4393,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.001242040720069177</v>
+        <v>0.0045</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4409,7 +4421,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.001194874616775411</v>
+        <v>0.00432</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4418,7 +4430,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4440,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>exmergo/dex</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4437,7 +4449,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.0011634305479129</v>
+        <v>0.00384</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/exmergo/dex</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4468,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4465,7 +4477,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.001021932238031601</v>
+        <v>0.00368</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4474,7 +4486,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4493,16 +4505,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.0007703796871315148</v>
+        <v>0.0036</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4524,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4521,16 +4533,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.00058171527395645</v>
+        <v>0.003</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4552,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4549,16 +4561,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.0004716610329376621</v>
+        <v>0.003</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4580,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>Dreamerol/ALLSTATS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4577,7 +4589,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.0004559389985064068</v>
+        <v>0.00272</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4586,7 +4598,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4608,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>Codpal-Limited/deckgauge</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4605,7 +4617,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.0003773288263501297</v>
+        <v>0.00256</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4636,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>errajeshcs-pixel/DS4Earth</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4633,7 +4645,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.0003301627230563635</v>
+        <v>0.00256</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4642,7 +4654,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4664,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4661,16 +4673,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0002829966197625973</v>
+        <v>0.0024</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -4680,25 +4692,25 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0001729423787438095</v>
+        <v>0.0018</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4720,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4717,16 +4729,16 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0001257762754500433</v>
+        <v>0.0015</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4748,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4745,16 +4757,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.0001100542410187878</v>
+        <v>0.0015</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4776,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4773,16 +4785,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1.572203443125541e-05</v>
+        <v>0.0012</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4804,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4801,16 +4813,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4820,25 +4832,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4860,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>etl data pipeline</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4857,7 +4869,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4866,91 +4878,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>power bi para que sirve</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A249"/>
+  <dimension ref="A1:A246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5475,63 +5403,63 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data analytics apprenticeship google</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>data analytics entry level jobs</t>
+          <t>data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>data analytics internship</t>
+          <t>data analytics google certification</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data analytics internships</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>data analytics jobs remote</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>data analytics meaning</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics vs data science</t>
         </is>
       </c>
     </row>
@@ -5552,56 +5480,56 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>data engineering bootcamp</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>data engineering certification</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data engineering manager</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>data engineering salary</t>
+          <t>data engineering system design</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering things</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>data engineering vs data science</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
@@ -5622,14 +5550,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>data pipeline architecture diagram</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>data pipeline engineer</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
@@ -5650,1062 +5578,1041 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>data pipeline orchestration</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>data pipeline station</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>power bi courses</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>power bi report builder</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>use of ai in analytics</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>what is ai in analytics</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is power bi dashboard</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
-        <is>
-          <t>why power bi is used</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>why power bi over excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>why power bi over tableau</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/report.xlsx
+++ b/report.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -475,7 +475,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -485,12 +485,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -503,7 +503,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -597,25 +597,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -625,25 +625,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.5655</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -653,16 +653,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -709,16 +709,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>0.31708</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -798,26 +798,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+          <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16539891</v>
+        <v>619941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -839,30 +839,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
+          <t>Data Engineering Course for Beginners</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>619941</v>
+        <v>1133491</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -880,30 +880,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>REVISIT — "Fast wavedash on pad (Lightdash handcam)" has 48.8k views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fast wavedash on pad (Lightdash handcam)</t>
+          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>48791</v>
+        <v>79875</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -956,26 +956,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
+          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7656650</v>
+        <v>16540035</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -997,38 +997,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("ClearML Introduction", 319.8k views). Your angle: claim the space — straightforward, solid coverage of "clearml/clearml" has almost no competition right now.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ClearML Introduction</t>
+          <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>319846</v>
+        <v>41873</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1038,38 +1038,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>OPPORTUNITY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REVISIT — "I suspect someone is playing tricks, but I have no evidence" has 364.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I suspect someone is playing tricks, but I have no evidence</t>
+          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>364126461</v>
+        <v>1114</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0.5655</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1079,38 +1079,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>John Cooper Clarke - Evidently Chickentown</t>
+          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2001414</v>
+        <v>7656832</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1125,33 +1125,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>79875</v>
-      </c>
+          <t>data engineering</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1166,33 +1160,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Engineering Course for Beginners</t>
+          <t>John Cooper Clarke - Evidently Chickentown</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1133490</v>
+        <v>2001417</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8</v>
+        <v>0.31708</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,7 +1242,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1257,7 +1251,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1266,7 +1260,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1270,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1294,7 +1288,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1298,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1322,7 +1316,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1354,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1369,7 +1363,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1378,7 +1372,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1388,25 +1382,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1416,25 +1410,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.5655</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1444,16 +1438,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1462,7 +1456,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1466,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1481,16 +1475,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1500,16 +1494,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>0.31708</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1518,7 +1512,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1522,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1537,16 +1531,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.772</v>
+        <v>0.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1550,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1565,7 +1559,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.62336</v>
+        <v>0.278</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1574,7 +1568,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1584,25 +1578,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5655</v>
+        <v>0.27504</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1606,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1621,7 +1615,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5432</v>
+        <v>0.24576</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1630,7 +1624,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1640,25 +1634,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5270400000000001</v>
+        <v>0.234</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1662,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1677,7 +1671,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.49344</v>
+        <v>0.19304</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1690,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1705,7 +1699,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4192</v>
+        <v>0.15584</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1714,7 +1708,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1718,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1733,7 +1727,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.3881600000000001</v>
+        <v>0.1358</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1742,7 +1736,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1746,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1761,7 +1755,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.3856</v>
+        <v>0.13176</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1770,7 +1764,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1780,25 +1774,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.36</v>
+        <v>0.12336</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1808,25 +1802,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2992</v>
+        <v>0.1182</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1830,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1845,16 +1839,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.28832</v>
+        <v>0.1095</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1858,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1873,7 +1867,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.27632</v>
+        <v>0.1048</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1882,7 +1876,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1886,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1901,7 +1895,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.26784</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1910,7 +1904,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1914,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1929,7 +1923,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.25552</v>
+        <v>0.0964</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1938,7 +1932,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1948,25 +1942,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>data pipeline solutions</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.2412</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -1976,25 +1970,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.234</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -2004,7 +1998,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2013,7 +2007,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.21664</v>
+        <v>0.06908</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2022,7 +2016,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2026,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2041,7 +2035,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.20224</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2050,7 +2044,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2060,25 +2054,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1182</v>
+        <v>0.06388000000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2082,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2097,16 +2091,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.11776</v>
+        <v>0.06</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2116,25 +2110,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1095</v>
+        <v>0.06</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -2144,25 +2138,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.104</v>
+        <v>0.06</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2166,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2181,7 +2175,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.09824000000000001</v>
+        <v>0.05416</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2190,7 +2184,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2200,25 +2194,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.07600000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2228,25 +2222,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.06</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2256,16 +2250,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.06</v>
+        <v>0.048</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2274,7 +2268,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2284,16 +2278,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.06</v>
+        <v>0.0474</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2302,7 +2296,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2306,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2321,16 +2315,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.05728</v>
+        <v>0.0468</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2340,16 +2334,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.054</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2358,7 +2352,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2368,16 +2362,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.048</v>
+        <v>0.0414</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2386,7 +2380,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2396,16 +2390,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.0474</v>
+        <v>0.0336</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2414,7 +2408,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2418,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>download power bi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2433,7 +2427,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.0474</v>
+        <v>0.03179999999999999</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2442,7 +2436,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
         </is>
       </c>
     </row>
@@ -2452,16 +2446,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.0456</v>
+        <v>0.0312</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2470,7 +2464,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2480,16 +2474,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.0306</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2498,7 +2492,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2502,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2517,16 +2511,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.0414</v>
+        <v>0.02944</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2536,25 +2530,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.03728</v>
+        <v>0.0294</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2564,16 +2558,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>power bi report</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.0336</v>
+        <v>0.0288</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2582,7 +2576,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2592,25 +2586,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.0336</v>
+        <v>0.026</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2620,16 +2614,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.03179999999999999</v>
+        <v>0.0246</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2638,7 +2632,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2648,16 +2642,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.0312</v>
+        <v>0.0246</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2666,7 +2660,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2670,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2685,7 +2679,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.0304</v>
+        <v>0.02456</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2694,7 +2688,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2704,16 +2698,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0294</v>
+        <v>0.0228</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2722,7 +2716,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2732,16 +2726,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.0288</v>
+        <v>0.021</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2750,7 +2744,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2754,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>engineering data management</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2769,7 +2763,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.0276</v>
+        <v>0.0198</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2778,7 +2772,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2782,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2797,7 +2791,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.0246</v>
+        <v>0.0192</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2806,7 +2800,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2810,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2825,7 +2819,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.0246</v>
+        <v>0.0192</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2834,7 +2828,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2838,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>data analytics software</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2853,16 +2847,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2866,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>power bi free</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2881,7 +2875,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0234</v>
+        <v>0.0186</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2890,7 +2884,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2894,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>data science and engineering</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2909,7 +2903,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0234</v>
+        <v>0.0186</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2918,7 +2912,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science+and+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2922,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2937,16 +2931,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.02304</v>
+        <v>0.0168</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -2956,16 +2950,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0228</v>
+        <v>0.0156</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2974,7 +2968,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2978,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2993,16 +2987,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.02224</v>
+        <v>0.015</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3006,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>social engineering</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3021,7 +3015,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.021</v>
+        <v>0.0144</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3030,7 +3024,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3040,25 +3034,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.02016</v>
+        <v>0.0144</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3062,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3077,7 +3071,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.0198</v>
+        <v>0.0144</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3086,7 +3080,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3090,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3105,16 +3099,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.01936</v>
+        <v>0.0144</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3118,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3133,16 +3127,16 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0192</v>
+        <v>0.01432</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3146,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3161,7 +3155,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0192</v>
+        <v>0.0132</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3170,7 +3164,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3174,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3189,7 +3183,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0186</v>
+        <v>0.0132</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3198,7 +3192,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3202,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3217,7 +3211,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0186</v>
+        <v>0.0132</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3226,7 +3220,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3230,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3245,16 +3239,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.01808</v>
+        <v>0.0126</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3258,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3273,16 +3267,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.01792</v>
+        <v>0.0114</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3292,25 +3286,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.01744</v>
+        <v>0.0114</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3314,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>power bi download desktop</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3329,7 +3323,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0168</v>
+        <v>0.0108</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3338,7 +3332,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3342,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3357,7 +3351,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0156</v>
+        <v>0.0102</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3366,7 +3360,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3376,16 +3370,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0156</v>
+        <v>0.0102</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3394,7 +3388,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3398,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>power bi web</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3413,16 +3407,16 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.01536</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3426,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3441,7 +3435,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.01536</v>
+        <v>0.00932</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3450,7 +3444,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3460,25 +3454,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0152</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3482,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3497,16 +3491,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.015</v>
+        <v>0.0076</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -3516,25 +3510,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.01472</v>
+        <v>0.0072</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3538,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3553,7 +3547,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0144</v>
+        <v>0.0072</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3562,7 +3556,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -3572,16 +3566,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.0144</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3590,7 +3584,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3594,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3609,16 +3603,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0144</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3622,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data scientist</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3637,7 +3631,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.0132</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3646,7 +3640,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3650,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3665,7 +3659,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.0132</v>
+        <v>0.006</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3674,7 +3668,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3678,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3693,16 +3687,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.01296</v>
+        <v>0.006</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3706,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3721,16 +3715,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.0126</v>
+        <v>0.00576</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3734,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3749,16 +3743,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.0114</v>
+        <v>0.00556</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3762,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>download power bi desktop</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3777,16 +3771,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.0108</v>
+        <v>0.00504</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3790,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3805,7 +3799,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.0104</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3814,7 +3808,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3818,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3833,16 +3827,16 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.0102</v>
+        <v>0.00452</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3846,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>power bi curso</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3861,16 +3855,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0102</v>
+        <v>0.0045</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3874,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>data analytics consulting</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3889,16 +3883,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.0102</v>
+        <v>0.0045</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3902,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>data engineering tools</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3917,16 +3911,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.00448</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+tools</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3930,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>data analytics masters</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3945,16 +3939,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.00436</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3958,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>feature engineering</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3973,7 +3967,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0042</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3982,7 +3976,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=feature+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3986,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4001,7 +3995,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.00848</v>
+        <v>0.00384</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4010,7 +4004,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4014,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4029,7 +4023,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.00736</v>
+        <v>0.00384</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4038,7 +4032,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -4048,25 +4042,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0072</v>
+        <v>0.0038</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4070,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4085,7 +4079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.0072</v>
+        <v>0.00368</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4094,7 +4088,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4104,16 +4098,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0036</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4122,7 +4116,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4126,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4141,7 +4135,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.0064</v>
+        <v>0.0036</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4150,7 +4144,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4154,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>python for data engineering</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4169,16 +4163,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.006</v>
+        <v>0.0036</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4182,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4197,16 +4191,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.006</v>
+        <v>0.00324</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4210,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4225,16 +4219,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.005920000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4238,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4253,16 +4247,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.00544</v>
+        <v>0.003</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4266,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>what is big data analytics</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4281,16 +4275,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.005399999999999999</v>
+        <v>0.0026</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4294,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>masters in data analytics</t>
+          <t>data pipeline development</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4309,7 +4303,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.005399999999999999</v>
+        <v>0.0024</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4318,7 +4312,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4322,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>coursera</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4337,16 +4331,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.005399999999999999</v>
+        <v>0.00212</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=coursera</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4350,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4365,16 +4359,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.0045</v>
+        <v>0.00184</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4384,25 +4378,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.0045</v>
+        <v>0.0018</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4406,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4421,7 +4415,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.00432</v>
+        <v>0.0018</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4430,7 +4424,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4434,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4449,7 +4443,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.00384</v>
+        <v>0.0016</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4458,7 +4452,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4462,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4477,16 +4471,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.00368</v>
+        <v>0.0015</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4490,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4505,16 +4499,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.0036</v>
+        <v>0.0015</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4533,16 +4527,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.003</v>
+        <v>0.00148</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4546,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4561,16 +4555,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.003</v>
+        <v>0.00136</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4574,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4589,16 +4583,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.00272</v>
+        <v>0.0012</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4602,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4617,16 +4611,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.00256</v>
+        <v>0.0012</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -4636,25 +4630,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.00256</v>
+        <v>0.0012</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4658,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>data pipeline software</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4673,7 +4667,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0024</v>
+        <v>0.0012</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4682,7 +4676,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4692,16 +4686,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0018</v>
+        <v>0.0012</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4710,7 +4704,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -4720,25 +4714,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0015</v>
+        <v>0.0012</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4742,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4757,16 +4751,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.0015</v>
+        <v>0.0012</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4770,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4785,16 +4779,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.0012</v>
+        <v>0.00108</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4798,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>exmergo/dex</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4813,16 +4807,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0012</v>
+        <v>0.0009599999999999999</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/exmergo/dex</t>
         </is>
       </c>
     </row>
@@ -4832,25 +4826,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.0012</v>
+        <v>0.00092</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4854,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>Dreamerol/ALLSTATS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4869,16 +4863,100 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.0012</v>
+        <v>0.00068</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>etl data pipeline</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>trends</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A246"/>
+  <dimension ref="A1:A247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6138,481 +6216,488 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/report.xlsx
+++ b/report.xlsx
@@ -457,12 +457,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -475,7 +475,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -569,25 +569,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.706</v>
+        <v>0.4482</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -597,16 +597,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -625,25 +625,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5655</v>
+        <v>0.24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5548000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -681,16 +681,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -709,25 +709,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.31708</v>
+        <v>0.0486</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -803,25 +803,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>619941</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -829,7 +823,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -858,7 +852,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1133491</v>
+        <v>1133552</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -885,25 +879,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
+          <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>79875</v>
+        <v>619941</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -911,7 +905,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -921,32 +915,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>mage-ai/mage-ai</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>16541265</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -961,33 +961,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Disturbed  - The Sound Of Silence (Official Music Video) [4K UPGRADE]" has 1199.6M views, but it's from 10 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>music</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+          <t>Disturbed  - The Sound Of Silence (Official Music Video) [4K UPGRADE]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16540035</v>
+        <v>1199563052</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.706</v>
+        <v>0.4482</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -1002,33 +1002,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Avoiding circular dependency errors in DAX</t>
+          <t>Cómo usar Power BI (Tutorial desde cero)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>41873</v>
+        <v>2873963</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1038,38 +1038,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OPPORTUNITY</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Capsule Explained: Single-File Web Apps That Save Into SQLite" at 1.1k views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Capsule Explained: Single-File Web Apps That Save Into SQLite</t>
+          <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1114</v>
+        <v>41873</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.5655</v>
+        <v>0.24</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1079,26 +1079,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT", 7.7M views). Your angle: claim the space — straightforward, solid coverage of "dbt-labs/dbt" has almost no competition right now.</t>
+          <t>REVISIT — "Google Analytics in real life - online checkout" has 1.6M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Khaoge Kache Pake Khatte Aam? 🤤🥭 Wait For The End! #shorts #Ghadidetergentpowder #DBT</t>
+          <t>Google Analytics in real life - online checkout</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7656832</v>
+        <v>1627722</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1106,11 +1106,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.5548000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -1120,32 +1120,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "data engineering" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "How to use Microsoft Power BI - Tutorial for Beginners" has 4.6M views, but it's from 6 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>data engineering</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>microsoft power bi</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>How to use Microsoft Power BI - Tutorial for Beginners</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>4635033</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.36</v>
+        <v>0.06</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -1160,33 +1166,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "John Cooper Clarke - Evidently Chickentown" has 2M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Jobs Career &amp; Professions Song | Wendy &amp; Friends Pretend Play Nursery Rhymes Kids Songs" has 360.3M views, but it's from 7 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>John Cooper Clarke - Evidently Chickentown</t>
+          <t>Jobs Career &amp; Professions Song | Wendy &amp; Friends Pretend Play Nursery Rhymes Kids Songs</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2001417</v>
+        <v>360326670</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.31708</v>
+        <v>0.0486</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,7 +1304,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1316,7 +1322,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1326,16 +1332,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1344,7 +1350,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1354,25 +1360,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>what is a social engineering attack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.706</v>
+        <v>0.6636000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+a+social+engineering+attack</t>
         </is>
       </c>
     </row>
@@ -1382,25 +1388,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5655</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1410,25 +1416,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5655</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1438,25 +1444,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>what is prompt engineering</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5548000000000001</v>
+        <v>0.5442</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+prompt+engineering</t>
         </is>
       </c>
     </row>
@@ -1466,16 +1472,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.36</v>
+        <v>0.4482</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1484,7 +1490,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -1494,25 +1500,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.31708</v>
+        <v>0.36</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1537,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1550,25 +1556,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>data analytics engineering</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.278</v>
+        <v>0.3594000000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -1578,25 +1584,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.27504</v>
+        <v>0.3594000000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1612,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1615,7 +1621,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.24576</v>
+        <v>0.31712</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1624,7 +1630,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1634,25 +1640,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.234</v>
+        <v>0.278</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1668,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1671,7 +1677,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.19304</v>
+        <v>0.27504</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1680,7 +1686,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1696,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1699,7 +1705,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.15584</v>
+        <v>0.2458</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1708,7 +1714,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1718,25 +1724,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1358</v>
+        <v>0.24</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1746,25 +1752,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.13176</v>
+        <v>0.234</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1780,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1783,7 +1789,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.12336</v>
+        <v>0.15584</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1792,7 +1798,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1802,25 +1808,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1182</v>
+        <v>0.1358</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1836,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1839,16 +1845,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1095</v>
+        <v>0.13176</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1858,25 +1864,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1048</v>
+        <v>0.1182</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1892,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1895,16 +1901,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.09704000000000002</v>
+        <v>0.1095</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1920,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1923,7 +1929,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.0964</v>
+        <v>0.1048</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1932,7 +1938,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1948,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1951,7 +1957,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1960,7 +1966,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1976,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1979,7 +1985,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.07208000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1988,7 +1994,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1998,7 +2004,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2007,7 +2013,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.06908</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2016,7 +2022,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2032,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2035,7 +2041,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.06908</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2044,7 +2050,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2054,25 +2060,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.06388000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2088,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2091,16 +2097,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.06</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2116,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2128,7 +2134,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2144,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>dashboard design ui</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2156,7 +2162,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+ui</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2172,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2175,16 +2181,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.05416</v>
+        <v>0.06</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2194,16 +2200,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.054</v>
+        <v>0.06</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2212,7 +2218,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2228,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2231,7 +2237,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.05056000000000001</v>
+        <v>0.05416</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2240,7 +2246,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2256,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2259,7 +2265,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.048</v>
+        <v>0.05279999999999999</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2268,7 +2274,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2278,25 +2284,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.0474</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2312,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>best dashboard design</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2315,7 +2321,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.0468</v>
+        <v>0.0504</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2324,7 +2330,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2334,16 +2340,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.0486</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2352,7 +2358,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2368,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2371,7 +2377,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.0414</v>
+        <v>0.048</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2380,7 +2386,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2390,16 +2396,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.0336</v>
+        <v>0.0474</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2408,7 +2414,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2418,16 +2424,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.03179999999999999</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2436,7 +2442,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2446,16 +2452,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.0312</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2464,7 +2470,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2474,16 +2480,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.0306</v>
+        <v>0.042</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2492,7 +2498,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2502,25 +2508,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.02944</v>
+        <v>0.0336</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2536,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2539,7 +2545,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.0294</v>
+        <v>0.0312</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2548,7 +2554,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2564,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2567,7 +2573,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.0288</v>
+        <v>0.0306</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2576,7 +2582,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2586,25 +2592,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.026</v>
+        <v>0.0306</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2614,16 +2620,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.0246</v>
+        <v>0.0288</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2632,7 +2638,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2642,16 +2648,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.0246</v>
+        <v>0.0288</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2660,7 +2666,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2676,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2679,16 +2685,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.02456</v>
+        <v>0.024</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2698,16 +2704,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0228</v>
+        <v>0.024</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2716,7 +2722,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2732,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>ai dashboard design</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2735,7 +2741,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.021</v>
+        <v>0.0228</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2744,7 +2750,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2754,16 +2760,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.0198</v>
+        <v>0.0222</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2772,7 +2778,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2788,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2791,7 +2797,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.0192</v>
+        <v>0.0216</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2800,7 +2806,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2816,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2828,7 +2834,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2872,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2884,7 +2890,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2900,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2912,7 +2918,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2928,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2931,7 +2937,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.0168</v>
+        <v>0.018</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2940,7 +2946,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2956,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2959,7 +2965,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0156</v>
+        <v>0.018</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2968,7 +2974,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2984,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2987,7 +2993,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.015</v>
+        <v>0.0168</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2996,7 +3002,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3012,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>business analytics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3015,7 +3021,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.0144</v>
+        <v>0.0156</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3024,7 +3030,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
         </is>
       </c>
     </row>
@@ -3034,16 +3040,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.0144</v>
+        <v>0.0156</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3052,7 +3058,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3068,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3080,7 +3086,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3108,7 +3114,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3124,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3127,16 +3133,16 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.01432</v>
+        <v>0.0144</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3152,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3155,16 +3161,16 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0132</v>
+        <v>0.01432</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3180,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>modern dashboard design</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3183,7 +3189,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3192,7 +3198,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3202,16 +3208,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3220,7 +3226,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3236,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3239,7 +3245,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.0126</v>
+        <v>0.0138</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3248,7 +3254,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3264,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3267,7 +3273,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.0114</v>
+        <v>0.0132</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3276,7 +3282,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3286,16 +3292,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0114</v>
+        <v>0.0132</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3304,7 +3310,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3320,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>power bi download desktop</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3323,7 +3329,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0108</v>
+        <v>0.0132</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3332,7 +3338,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=travel</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3351,7 +3357,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0102</v>
+        <v>0.0126</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3360,7 +3366,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3376,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>power bi curso</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3379,7 +3385,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0102</v>
+        <v>0.0126</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3388,7 +3394,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3404,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>power bi web</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3407,7 +3413,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3416,7 +3422,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3432,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3435,16 +3441,16 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.00932</v>
+        <v>0.012</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3454,16 +3460,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>analytics dashboard design</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0114</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3472,7 +3478,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3488,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3491,16 +3497,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0076</v>
+        <v>0.0108</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=exercise</t>
         </is>
       </c>
     </row>
@@ -3510,16 +3516,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>bi dashboard design</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.0072</v>
+        <v>0.0108</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3528,7 +3534,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3544,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>download power bi desktop</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3547,7 +3553,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0072</v>
+        <v>0.0108</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3556,7 +3562,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3572,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3575,7 +3581,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0108</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3584,7 +3590,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3600,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>admin dashboard design</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3603,7 +3609,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3612,7 +3618,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3628,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>dashboard design template</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3631,7 +3637,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3640,7 +3646,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3656,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>curso power bi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3659,7 +3665,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.006</v>
+        <v>0.0102</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3668,7 +3674,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=curso+power+bi</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3684,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3687,16 +3693,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.006</v>
+        <v>0.0102</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3706,25 +3712,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.00576</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3740,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>power bi login</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3743,16 +3749,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.00556</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+login</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3768,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3771,7 +3777,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.00504</v>
+        <v>0.00932</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3780,7 +3786,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3796,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>information dashboard design</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3799,16 +3805,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.004840000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3818,25 +3824,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.00452</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3852,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3855,16 +3861,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3880,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>excel dashboard design</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3883,16 +3889,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3908,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>dashboard design figma</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3911,16 +3917,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.00448</v>
+        <v>0.0078</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+figma</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3936,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3939,7 +3945,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.00436</v>
+        <v>0.0076</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3948,7 +3954,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3964,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3967,7 +3973,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0042</v>
+        <v>0.0072</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3976,7 +3982,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -3986,25 +3992,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.00384</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4020,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>data scientist</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4023,16 +4029,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.00384</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4048,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4051,16 +4057,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0038</v>
+        <v>0.006</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4076,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4079,16 +4085,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.00368</v>
+        <v>0.006</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4104,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4107,16 +4113,16 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.0036</v>
+        <v>0.00576</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4132,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4135,7 +4141,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.0036</v>
+        <v>0.00556</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4144,7 +4150,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4160,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>python for data engineering</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4163,16 +4169,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.0036</v>
+        <v>0.00504</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4188,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4191,7 +4197,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.00324</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4200,7 +4206,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4216,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4219,16 +4225,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.003</v>
+        <v>0.0045</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4244,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4247,7 +4253,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.003</v>
+        <v>0.0045</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4256,7 +4262,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4272,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4275,7 +4281,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.0026</v>
+        <v>0.00448</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4284,7 +4290,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4300,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>data pipeline development</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4303,7 +4309,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.0024</v>
+        <v>0.0042</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4312,7 +4318,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4328,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4331,7 +4337,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.00212</v>
+        <v>0.00384</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4340,7 +4346,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4356,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4359,7 +4365,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.00184</v>
+        <v>0.0038</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4368,7 +4374,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4378,25 +4384,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.0018</v>
+        <v>0.00368</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4406,25 +4412,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.0018</v>
+        <v>0.0036</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4440,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>python for data engineering</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4443,16 +4449,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.0016</v>
+        <v>0.0036</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4468,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4471,16 +4477,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.0015</v>
+        <v>0.0036</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4499,16 +4505,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.0015</v>
+        <v>0.003</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4524,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>data engineering vs data analytics</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4527,16 +4533,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.00148</v>
+        <v>0.003</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4552,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4555,16 +4561,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.00136</v>
+        <v>0.003</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4580,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4583,16 +4589,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.0012</v>
+        <v>0.0026</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4608,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4611,16 +4617,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.0012</v>
+        <v>0.00184</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4636,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4639,7 +4645,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.0012</v>
+        <v>0.0018</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4648,7 +4654,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4664,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4667,16 +4673,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0012</v>
+        <v>0.0018</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4692,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4695,16 +4701,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0012</v>
+        <v>0.0016</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -4714,25 +4720,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4748,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4751,16 +4757,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4776,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4779,7 +4785,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.00108</v>
+        <v>0.00148</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4788,7 +4794,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4804,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4807,16 +4813,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0009599999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4832,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4835,16 +4841,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.00092</v>
+        <v>0.0012</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4854,25 +4860,25 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.00068</v>
+        <v>0.0012</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4888,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4891,16 +4897,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4916,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4919,16 +4925,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -4938,23 +4944,247 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
+          <t>data pipeline meaning</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0.00068</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>etl pipeline</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=etl+pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>etl data pipeline</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
@@ -4971,7 +5201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A247"/>
+  <dimension ref="A1:A390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5173,1531 +5403,2532 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>best ai agent analytics tools</t>
+          <t>balanced scorecard vs kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>best analytics engineering books</t>
+          <t>best ai agent analytics tools</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>best analytics engineering course</t>
+          <t>best ai for power bi dax</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>best ai tool for power bi dax</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>best analytics engineering books</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>best analytics engineering course</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best dashboard design home assistant</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>best dashboard design in excel</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>best dashboard design in power bi</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>best dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>best dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>best dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>best dashboard design ui</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best data analytics books</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>best data analytics software</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>best data engineering books</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>best data pipeline</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>best free kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship google</t>
+          <t>best kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>best kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>best kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>best kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>data analytics google certification</t>
+          <t>best power bi books</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>best power bi certification</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>best power bi courses</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>best power bi dax book</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>best power bi dax course</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>best power bi training</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>better than chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>budget vs actual dashboard design</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>business intelligence trends</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>business intelligence trends 2024</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>business intelligence trends 2025</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>data engineering zoomcamp</t>
+          <t>business intelligence trends 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>chatgpt for data analysis course</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>chatgpt for data analysis free</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>chatgpt for data analysis pdf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>chatgpt for data analysis udemy</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>claude ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>claude vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>claude vs chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>copilot vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>dashboard design</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>dashboard design ideas</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>dashboard design meaning</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>dashboard design rules</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>dashboard design skill</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>dashboard design skill claude code</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>dashboard design standards</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>dashboard design tips</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>data analytics</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>data analytics course</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>data analytics internship</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>data analytics jobs near me</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>data analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>data analytics vs data analysis</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>data engineering</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>data engineering academy</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>data engineering certification</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>data engineering zoomcamp</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>data pipeline station</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>deepseek vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>gemini vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>good kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>good vs bad dashboard design</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>grok vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>how good is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>how reliable is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>how to comment power bi dax</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>how to concatenate in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>how to create a kpi dashboard in excel from scratch</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>how to create a kpi dashboard in google sheets</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>how to create kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>how to create kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>how to create kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>how to create kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>how to dashboard design</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>how to design kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>how to divide in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>how to learn power bi dax</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>how to multiply in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>how to open power bi dax</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>how to power bi dax</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>how to practice power bi dax</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>how to use chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>how to use chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>how to use power bi dax</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>how to write power bi dax</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>if or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>julius ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>julius vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>kpi dashboard examples</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>kpi dashboard ideas</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>kpi dashboard meaning</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>kpi dashboard power bi</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>kpi dashboard template</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>kpi dashboard template excel</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>llm for bi</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
+        <is>
+          <t>perplexity vs chatgpt for data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>power bi app</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>power bi certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>power bi dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>power bi dax best practices</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>power bi dax cheat sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>power bi dax filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>power bi dax functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>power bi dax functions list</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>power bi dax if statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>power bi dax queries</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>power bi dax query view</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>power bi dax switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>power bi dax tutorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>power bi dax vs power query</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>power bi desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>power bi desktop download</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>power bi download</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>power bi login</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>power bi report builder</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>power bi training</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>power bi vs power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>software vs data engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>stakeholder reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>stakeholder reporting forvis mazars</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>stakeholder reporting gmbh</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>stakeholder reporting gmbh &amp; co kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>stakeholder reporting hamburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>stakeholder reporting meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>stakeholder reporting template</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>statistics vs data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>tableau vs power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>top 10 power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>top 5 power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>top data pipeline solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>top kpi dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>top n power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>top power bi dax functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>top power bi dax interview questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>types of dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>use of ai in analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>using chatgpt for data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>visual studio data pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>vs data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>vs power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>what is a floating element in tableau dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>what is a good dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>what is ai in analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>what is analytics engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>what is analytics engineering dbt</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>what is analytics engineering reddit</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>what is bi dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>what is dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>what is data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>what is data analytics and visualization</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>what is data analytics degree</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>what is data analytics engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>what is data analytics in accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>what is data analytics in healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>what is data analytics in simple words</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>what is data analytics job</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>what is data analytics salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>what is data analytics used for</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>what is data analytics vs data science</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>what is data engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>what is data engineering all about</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>what is data engineering and analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>what is data engineering and data science</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>what is data engineering course</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>what is data engineering in simple words</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>what is data engineering reddit</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>what is data engineering role</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>what is data engineering salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>what is data engineering skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>what is data engineering vs data science</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>what is data pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>what is data pipeline architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>what is data pipeline development</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>what is data pipeline in ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>what is data pipeline in data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>what is data pipeline in data engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>what is data pipeline in etl</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>what is data pipeline in machine learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>what is data pipeline in python</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>what is data pipeline in sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>what is data pipeline management</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>what is data pipeline orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>what is data pipeline testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard development</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard in excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard in power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>what is kpi dashboard in tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>what is llm analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>what is power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>what is power bi and how does it work</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>what is power bi dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>what is power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>what is power bi dax code</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>what is power bi dax function</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>what is power bi dax measures</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>what is power bi dax query</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>what is power bi dax studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>what is power bi dax used for</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>what is power bi desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>what is power bi pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>what is power bi report builder</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>what is power bi service</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>what is power bi software</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>what is power bi stand for</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>what is power bi used for</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>what is saas dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>what is stakeholder reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>what is the best chatgpt for data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>what is the best version of chatgpt for data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>what is the fundamental challenge of dashboard design</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>what language is power bi dax</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>why data analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>why data analytics as a career</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>why data analytics course</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>why data analytics is a good career</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>why data analytics is important</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>why data analytics is the future</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>why data analytics is the future of everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>why data analytics is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>why data analytics reddit</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>why data engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>why data engineering interview questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>why data engineering is hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>why data engineering is important</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>why data engineering reddit</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>why data pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>why power bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>why power bi gateway went offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>why power bi is better than excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>why power bi is better than tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>why power bi is important</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>why power bi is not available for mac</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>why power bi is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>why power bi over excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/report.xlsx
+++ b/report.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.706</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -569,25 +569,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4482</v>
+        <v>0.706</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=music</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -653,25 +653,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0672</v>
+        <v>0.19324</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -681,25 +681,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06</v>
+        <v>0.1234</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.0486</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=jobs</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -798,21 +798,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Data Engineering Course for Beginners</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1133570</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
@@ -823,7 +829,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -833,26 +839,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Engineering Course for Beginners</t>
+          <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1133552</v>
+        <v>79908</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -864,7 +870,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -879,25 +885,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Airbyte 2.0: Enterprise Flex</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>619941</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -915,26 +915,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
+          <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>16541265</v>
+        <v>619941</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -942,11 +942,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.706</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -961,33 +961,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REVISIT — "Disturbed  - The Sound Of Silence (Official Music Video) [4K UPGRADE]" has 1199.6M views, but it's from 10 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Disturbed  - The Sound Of Silence (Official Music Video) [4K UPGRADE]</t>
+          <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1199563052</v>
+        <v>16541568</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.4482</v>
+        <v>0.706</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=music</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2873963</v>
+        <v>2873994</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1079,38 +1079,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>REVISIT — "Google Analytics in real life - online checkout" has 1.6M views, but it's from 14 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("LangWatch LLM Optimization Studio", 89.1k views). Your angle: claim the space — straightforward, solid coverage of "langwatch/langwatch" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Google Analytics in real life - online checkout</t>
+          <t>LangWatch LLM Optimization Studio</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1627722</v>
+        <v>89121</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.0672</v>
+        <v>0.19324</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1120,38 +1120,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>REVISIT — "How to use Microsoft Power BI - Tutorial for Beginners" has 4.6M views, but it's from 6 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("मनिहारी का भेष बनाया श्याम चूड़ी बेचने आया🚩🙏😯😯🥀 #shortvideo #reels #spiceai#video #viral #trending", 1.2k views). Your angle: claim the space — straightforward, solid coverage of "spiceai/spiceai" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>How to use Microsoft Power BI - Tutorial for Beginners</t>
+          <t>मनिहारी का भेष बनाया श्याम चूड़ी बेचने आया🚩🙏😯😯🥀 #shortvideo #reels #spiceai#video #viral #trending</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4635033</v>
+        <v>1215</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.06</v>
+        <v>0.1234</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1166,21 +1166,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "Jobs Career &amp; Professions Song | Wendy &amp; Friends Pretend Play Nursery Rhymes Kids Songs" has 360.3M views, but it's from 7 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "How to use Microsoft Power BI - Tutorial for Beginners" has 4.6M views, but it's from 6 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jobs Career &amp; Professions Song | Wendy &amp; Friends Pretend Play Nursery Rhymes Kids Songs</t>
+          <t>How to use Microsoft Power BI - Tutorial for Beginners</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>360326670</v>
+        <v>4635045</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1188,11 +1188,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.0486</v>
+        <v>0.06</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=jobs</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1332,16 +1332,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.706</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is a social engineering attack</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6636000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+a+social+engineering+attack</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1388,25 +1388,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>what is a social engineering attack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5655</v>
+        <v>0.6636000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+a+social+engineering+attack</t>
         </is>
       </c>
     </row>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5548000000000001</v>
+        <v>0.5655</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1444,25 +1444,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>what is prompt engineering</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5442</v>
+        <v>0.5548000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+prompt+engineering</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -1472,16 +1472,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4482</v>
+        <v>0.36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=music</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1528,16 +1528,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>power bi para que sirve</t>
+          <t>data analytics engineering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.36</v>
+        <v>0.3594000000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>data analytics engineering</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3594000000000001</v>
+        <v>0.3171600000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.31712</v>
+        <v>0.278</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.278</v>
+        <v>0.27504</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.27504</v>
+        <v>0.2458</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1696,25 +1696,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.2458</v>
+        <v>0.24</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1733,16 +1733,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.24</v>
+        <v>0.234</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.234</v>
+        <v>0.19324</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1864,25 +1864,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1182</v>
+        <v>0.1234</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1892,25 +1892,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1095</v>
+        <v>0.1182</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1929,16 +1929,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1048</v>
+        <v>0.1095</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.09704000000000002</v>
+        <v>0.1048</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.0964</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.07208000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.06908</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -2060,25 +2060,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.0672</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.06908</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2116,25 +2116,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.06</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>dashboard design ui</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.06</v>
+        <v>0.06392</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+ui</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2237,16 +2237,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.05416</v>
+        <v>0.06</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2256,16 +2256,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>dashboard design ui</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.05279999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+ui</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.05056000000000001</v>
+        <v>0.05416</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2312,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>best dashboard design</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.0504</v>
+        <v>0.05279999999999999</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2340,25 +2340,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.0486</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=jobs</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>best dashboard design</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.048</v>
+        <v>0.0504</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2396,16 +2396,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.0474</v>
+        <v>0.048</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.0474</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2452,16 +2452,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.042</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2508,16 +2508,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.0336</v>
+        <v>0.042</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.0312</v>
+        <v>0.0336</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.0306</v>
+        <v>0.0312</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.0288</v>
+        <v>0.0306</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2648,25 +2648,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.0288</v>
+        <v>0.02944</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2676,16 +2676,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.024</v>
+        <v>0.0288</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2704,16 +2704,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.024</v>
+        <v>0.0288</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ai dashboard design</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2741,16 +2741,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.0228</v>
+        <v>0.026</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2760,25 +2760,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.0222</v>
+        <v>0.02456</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.0216</v>
+        <v>0.024</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.0192</v>
+        <v>0.024</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>ai dashboard design</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2853,16 +2853,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.019</v>
+        <v>0.0228</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2872,16 +2872,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0186</v>
+        <v>0.0222</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0186</v>
+        <v>0.0216</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.018</v>
+        <v>0.0192</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2965,16 +2965,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0168</v>
+        <v>0.0186</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>business analytics</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.0156</v>
+        <v>0.0186</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.0156</v>
+        <v>0.018</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.0144</v>
+        <v>0.018</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.0144</v>
+        <v>0.0168</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>business analytics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0144</v>
+        <v>0.0156</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3161,16 +3161,16 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.01432</v>
+        <v>0.0156</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>modern dashboard design</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3208,16 +3208,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3273,16 +3273,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.0132</v>
+        <v>0.01432</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>modern dashboard design</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>travel</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=travel</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3348,16 +3348,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0126</v>
+        <v>0.0138</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>dashboard design best practices</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0126</v>
+        <v>0.0132</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.012</v>
+        <v>0.0132</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.012</v>
+        <v>0.0126</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>analytics dashboard design</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0114</v>
+        <v>0.0126</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>exercise</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0108</v>
+        <v>0.012</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=exercise</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>bi dashboard design</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.0108</v>
+        <v>0.012</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>download power bi desktop</t>
+          <t>analytics dashboard design</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0108</v>
+        <v>0.0114</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>download power bi desktop</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>admin dashboard design</t>
+          <t>bi dashboard design</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0102</v>
+        <v>0.0108</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3628,16 +3628,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>dashboard design template</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.0102</v>
+        <v>0.0108</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>curso power bi</t>
+          <t>dashboard design template</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=curso+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>admin dashboard design</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3712,16 +3712,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>curso power bi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+login</t>
+          <t>https://trends.google.com/trends/explore?q=curso+power+bi</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>power bi login</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3777,16 +3777,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.00932</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+login</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>information dashboard design</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3805,16 +3805,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.00936</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>information dashboard design</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>user dashboard design</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
+          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3880,16 +3880,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>excel dashboard design</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dashboard design figma</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.0078</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+figma</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>excel dashboard design</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3945,16 +3945,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.0076</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>dashboard design figma</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0072</v>
+        <v>0.0078</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+figma</t>
         </is>
       </c>
     </row>
@@ -3992,25 +3992,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0076</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0072</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -4048,25 +4048,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.006</v>
+        <v>0.0072</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>data scientist</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.006</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
         </is>
       </c>
     </row>
@@ -4104,25 +4104,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.00576</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4141,16 +4141,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.00556</v>
+        <v>0.006</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4169,16 +4169,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.00504</v>
+        <v>0.006</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.004840000000000001</v>
+        <v>0.00576</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4225,16 +4225,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.0045</v>
+        <v>0.00556</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4253,16 +4253,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.0045</v>
+        <v>0.00504</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.00448</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4309,16 +4309,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.0042</v>
+        <v>0.004560000000000001</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4337,16 +4337,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.00384</v>
+        <v>0.0045</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4365,16 +4365,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.0038</v>
+        <v>0.0045</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.00368</v>
+        <v>0.00448</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -4412,25 +4412,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.0036</v>
+        <v>0.00436</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>python for data engineering</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.0036</v>
+        <v>0.0042</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.0036</v>
+        <v>0.00384</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4505,16 +4505,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.003</v>
+        <v>0.00384</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>data engineering vs data analytics</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4533,16 +4533,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.003</v>
+        <v>0.0038</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4561,16 +4561,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.003</v>
+        <v>0.00368</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4589,16 +4589,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.0026</v>
+        <v>0.0036</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4608,25 +4608,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.00184</v>
+        <v>0.0036</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4636,25 +4636,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.0018</v>
+        <v>0.0036</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0018</v>
+        <v>0.00324</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0016</v>
+        <v>0.003</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0015</v>
+        <v>0.003</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>data engineering vs data analytics</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4757,16 +4757,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.0015</v>
+        <v>0.003</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.00148</v>
+        <v>0.0026</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>data pipeline development</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0012</v>
+        <v>0.0024</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4841,16 +4841,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.0012</v>
+        <v>0.00212</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -4860,25 +4860,25 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.0012</v>
+        <v>0.00184</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4888,16 +4888,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.0012</v>
+        <v>0.0018</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4925,16 +4925,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.0012</v>
+        <v>0.0018</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -4944,25 +4944,25 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.0012</v>
+        <v>0.0016</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4981,16 +4981,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.00108</v>
+        <v>0.0015</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5009,16 +5009,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.0009599999999999999</v>
+        <v>0.0015</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.00092</v>
+        <v>0.00148</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.00068</v>
+        <v>0.00136</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5093,16 +5093,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5121,16 +5121,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>etl pipeline</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -5168,23 +5168,275 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
+          <t>data pipeline architecture</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>data pipeline meaning</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>data pipeline aws</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.00068</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t>etl data pipeline</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
@@ -5201,7 +5453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A390"/>
+  <dimension ref="A1:A379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5221,2714 +5473,2637 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ai agent analytics</t>
+          <t>ai vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard</t>
+          <t>ai vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard servicenow</t>
+          <t>analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ai agent analytics platform</t>
+          <t>analytics engineering best practices</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ai agent analytics servicenow</t>
+          <t>analytics engineering course</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ai agent analytics vidhya</t>
+          <t>analytics engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ai in analytics</t>
+          <t>analytics engineering manager</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ai in analytics course</t>
+          <t>analytics engineering podcast</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ai vs data analytics</t>
+          <t>analytics engineering roundup</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ai vs data engineering</t>
+          <t>analytics engineering salary</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>analytics engineering</t>
+          <t>analytics engineering vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>analytics engineering best practices</t>
+          <t>analytics engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>analytics engineering course</t>
+          <t>analytics engineering with sql and dbt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>analytics engineering jobs</t>
+          <t>analytics engineering with sql and dbt pdf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>analytics engineering manager</t>
+          <t>analytics vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>analytics engineering podcast</t>
+          <t>and data analytics</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>analytics engineering roundup</t>
+          <t>api vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>analytics engineering salary</t>
+          <t>backend vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>analytics engineering vs data engineering</t>
+          <t>balanced scorecard vs kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>analytics engineering vs data science</t>
+          <t>best ai for power bi dax</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt</t>
+          <t>best ai tool for power bi dax</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt pdf</t>
+          <t>best analytics engineering books</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>analytics vs data engineering</t>
+          <t>best analytics engineering course</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>and data analytics</t>
+          <t>best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>api vs data pipeline</t>
+          <t>best dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>backend vs data engineering</t>
+          <t>best dashboard design home assistant</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>balanced scorecard vs kpi dashboard</t>
+          <t>best dashboard design in excel</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>best ai agent analytics tools</t>
+          <t>best dashboard design in power bi</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>best ai for power bi dax</t>
+          <t>best dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>best ai tool for power bi dax</t>
+          <t>best dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>best analytics engineering books</t>
+          <t>best dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>best analytics engineering course</t>
+          <t>best dashboard design ui</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>best chatgpt for data analysis</t>
+          <t>best data analytics books</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>best dashboard design examples</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>best dashboard design home assistant</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>best dashboard design in excel</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>best dashboard design in power bi</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>best dashboard design inspiration</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>best dashboard design principles</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>best dashboard design templates</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>best dashboard design ui</t>
+          <t>best data analytics software</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>best data engineering books</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>best data pipeline</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best free kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>best kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>best kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>best kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best power bi books</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best power bi certification</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best power bi courses</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>best free kpi dashboard software</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>best kpi dashboard design</t>
+          <t>best power bi dax book</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>best kpi dashboard excel</t>
+          <t>best power bi dax course</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>best kpi dashboard in power bi</t>
+          <t>best power bi training</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>best kpi dashboard software</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>better than chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>budget vs actual dashboard design</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>business intelligence trends</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>business intelligence trends 2024</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>best power bi dax book</t>
+          <t>business intelligence trends 2025</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>best power bi dax course</t>
+          <t>business intelligence trends 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>chatgpt for data analysis course</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>better than chatgpt for data analysis</t>
+          <t>chatgpt for data analysis free</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>budget vs actual dashboard design</t>
+          <t>chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>business intelligence trends</t>
+          <t>chatgpt for data analysis pdf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>business intelligence trends 2024</t>
+          <t>chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>business intelligence trends 2025</t>
+          <t>chatgpt for data analysis udemy</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>business intelligence trends 2026</t>
+          <t>claude ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>claude vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis</t>
+          <t>claude vs chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis course</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis free</t>
+          <t>copilot vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis in excel</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis pdf</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis reddit</t>
+          <t>dashboard design</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis udemy</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>claude ai vs chatgpt for data analysis</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>claude vs chatgpt for data analysis</t>
+          <t>dashboard design ideas</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>claude vs chatgpt for data analysis reddit</t>
+          <t>dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>dashboard design meaning</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>copilot vs chatgpt for data analysis</t>
+          <t>dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>dashboard design rules</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>dashboard design skill</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dashboard design</t>
+          <t>dashboard design skill claude code</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dashboard design best practices</t>
+          <t>dashboard design standards</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dashboard design ideas</t>
+          <t>dashboard design tips</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>dashboard design inspiration</t>
+          <t>data analytics</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>dashboard design meaning</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>dashboard design principles</t>
+          <t>data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>dashboard design rules</t>
+          <t>data analytics internships</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>dashboard design skill</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>dashboard design skill claude code</t>
+          <t>data analytics jobs entry level</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>dashboard design standards</t>
+          <t>data analytics masters</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>dashboard design templates</t>
+          <t>data analytics professional certificate</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>dashboard design tips</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>data analytics tools</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data engineering</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>data engineering academy</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data engineering certification</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>data analytics internship</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data engineering internship</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>data analytics jobs near me</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>data analytics meaning</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>data analytics vs data analysis</t>
+          <t>data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>data engineering bootcamp</t>
+          <t>data pipeline</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>data engineering certification</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data pipeline examples</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>data engineering salary</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>data engineering vs data science</t>
+          <t>data pipeline station</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>data engineering zoomcamp</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>data pipeline engineer</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>deepseek vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>data pipeline orchestration</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>data pipeline station</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>gemini vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>deepseek vs chatgpt for data analysis</t>
+          <t>good kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>good vs bad dashboard design</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>grok vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>how good is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>how reliable is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>gemini vs chatgpt for data analysis</t>
+          <t>how to comment power bi dax</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>how to concatenate in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>good kpi dashboard</t>
+          <t>how to create a kpi dashboard in excel from scratch</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>good vs bad dashboard design</t>
+          <t>how to create a kpi dashboard in google sheets</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>grok vs chatgpt for data analysis</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>how good is chatgpt for data analysis</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>how reliable is chatgpt for data analysis</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how to create kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>how to comment power bi dax</t>
+          <t>how to create kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>how to concatenate in power bi dax</t>
+          <t>how to create kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in excel from scratch</t>
+          <t>how to create kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in google sheets</t>
+          <t>how to dashboard design</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in excel</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in power bi</t>
+          <t>how to design kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in tableau</t>
+          <t>how to divide in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>how to dashboard design</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to learn power bi dax</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>how to design kpi dashboard</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>how to divide in power bi dax</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to multiply in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to open power bi dax</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>how to learn power bi dax</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to power bi dax</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to practice power bi dax</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>how to multiply in power bi dax</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>how to open power bi dax</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to use chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to use chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to use power bi dax</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to write power bi dax</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>how to power bi dax</t>
+          <t>if or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>how to practice power bi dax</t>
+          <t>julius ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>julius vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis</t>
+          <t>kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis in excel</t>
+          <t>kpi dashboard examples</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>how to use power bi dax</t>
+          <t>kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>how to write power bi dax</t>
+          <t>kpi dashboard ideas</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>if or power bi dax</t>
+          <t>kpi dashboard meaning</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>kpi dashboard power bi</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>julius ai vs chatgpt for data analysis</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>julius vs chatgpt for data analysis</t>
+          <t>kpi dashboard template</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kpi dashboard</t>
+          <t>kpi dashboard template excel</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kpi dashboard design</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kpi dashboard examples</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kpi dashboard excel</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kpi dashboard ideas</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kpi dashboard meaning</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kpi dashboard power bi</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kpi dashboard template</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>kpi dashboard template excel</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>llm for bi</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>perplexity vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>llm for bi</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>power bi dax</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>power bi dax best practices</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>power bi dax cheat sheet</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>power bi dax filter</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>perplexity vs chatgpt for data analysis</t>
+          <t>power bi dax functions list</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>power bi dax if</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>power bi app</t>
+          <t>power bi dax if statement</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi dax queries</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi dax query view</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>power bi dax</t>
+          <t>power bi dax switch</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>power bi dax best practices</t>
+          <t>power bi dax vs power query</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>power bi dax cheat sheet</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>power bi dax filter</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>power bi dax functions</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>power bi dax functions list</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>power bi dax if statement</t>
+          <t>power bi service</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>power bi dax queries</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>power bi dax query view</t>
+          <t>power bi vs power bi dax</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>power bi dax switch</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>power bi dax tutorial</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>power bi dax vs power query</t>
+          <t>stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>stakeholder reporting forvis mazars</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>stakeholder reporting gmbh</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>stakeholder reporting gmbh &amp; co kg</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>stakeholder reporting hamburg</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>power bi report builder</t>
+          <t>stakeholder reporting meaning</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>stakeholder reporting template</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>power bi vs power bi dax</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>stakeholder reporting</t>
+          <t>top 10 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>stakeholder reporting forvis mazars</t>
+          <t>top 5 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh &amp; co kg</t>
+          <t>top kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>stakeholder reporting hamburg</t>
+          <t>top n power bi dax</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>stakeholder reporting meaning</t>
+          <t>top power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>stakeholder reporting template</t>
+          <t>top power bi dax interview questions</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>types of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>using chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>top 10 power bi dax</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>top 5 power bi dax</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>top kpi dashboard</t>
+          <t>what is a floating element in tableau dashboard design</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>top n power bi dax</t>
+          <t>what is a good dashboard design</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>top power bi dax functions</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>top power bi dax interview questions</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>types of dashboard design</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>what is bi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>using chatgpt for data analysis</t>
+          <t>what is dashboard design</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>what is a floating element in tableau dashboard design</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>what is a good dashboard design</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>what is bi dashboard design</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>what is dashboard design</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is kpi dashboard development</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is power bi dax code</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>what is kpi dashboard</t>
+          <t>what is power bi dax function</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>what is kpi dashboard development</t>
+          <t>what is power bi dax measures</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in excel</t>
+          <t>what is power bi dax query</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in power bi</t>
+          <t>what is power bi dax studio</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in tableau</t>
+          <t>what is power bi dax used for</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>what is power bi dashboard</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>what is power bi dax</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>what is power bi dax code</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>what is power bi dax function</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>what is power bi dax measures</t>
+          <t>what is saas dashboard design</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>what is power bi dax query</t>
+          <t>what is stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>what is power bi dax studio</t>
+          <t>what is the best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>what is power bi dax used for</t>
+          <t>what is the best version of chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is the fundamental challenge of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what language is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>what is saas dashboard design</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>what is stakeholder reporting</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>what is the best chatgpt for data analysis</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>what is the best version of chatgpt for data analysis</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>what is the fundamental challenge of dashboard design</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>what language is power bi dax</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
-        <is>
-          <t>why data engineering reddit</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>why data pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>why power bi</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>why power bi gateway went offline</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>why power bi is better than excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>why power bi is better than tableau</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>why power bi is important</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>why power bi is not available for mac</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>why power bi is used</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>why power bi over excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>why power bi over tableau</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/report.xlsx
+++ b/report.xlsx
@@ -597,16 +597,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>power bi para que sirve</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.36</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -625,16 +625,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1133570</v>
+        <v>1133623</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16541568</v>
+        <v>16542114</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1002,33 +1002,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>power bi para que sirve</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cómo usar Power BI (Tutorial desde cero)</t>
+          <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2873994</v>
+        <v>41873</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.36</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1043,33 +1043,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Avoiding circular dependency errors in DAX</t>
+          <t>Cómo usar Power BI (Tutorial desde cero)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>41873</v>
+        <v>2874055</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("मनिहारी का भेष बनाया श्याम चूड़ी बेचने आया🚩🙏😯😯🥀 #shortvideo #reels #spiceai#video #viral #trending", 1.2k views). Your angle: claim the space — straightforward, solid coverage of "spiceai/spiceai" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "spiceai/spiceai" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1133,14 +1133,8 @@
           <t>spiceai/spiceai</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>मनिहारी का भेष बनाया श्याम चूड़ी बेचने आया🚩🙏😯😯🥀 #shortvideo #reels #spiceai#video #viral #trending</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1215</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>NEW / SPIKE</t>
@@ -1166,25 +1160,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "How to use Microsoft Power BI - Tutorial for Beginners" has 4.6M views, but it's from 6 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Power BI Tutorial For Beginners | Create Your First Dashboard Now (Practice Files included)" has 3.1M views, but it's from 4 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>How to use Microsoft Power BI - Tutorial for Beginners</t>
+          <t>Power BI Tutorial For Beginners | Create Your First Dashboard Now (Practice Files included)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4635045</v>
+        <v>3058195</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1192,7 +1186,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,16 +1382,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>what is a social engineering attack</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6636000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1406,7 +1400,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+a+social+engineering+attack</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1494,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>power bi para que sirve</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1509,16 +1503,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.36</v>
+        <v>0.3171600000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -1528,16 +1522,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>data analytics engineering</t>
+          <t>power bi para que sirve</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3594000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1546,7 +1540,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -1556,25 +1550,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.3594000000000001</v>
+        <v>0.278</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1578,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1593,7 +1587,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3171600000000001</v>
+        <v>0.27504</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1602,7 +1596,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1606,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1621,7 +1615,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.278</v>
+        <v>0.2458</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1630,7 +1624,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1649,16 +1643,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.27504</v>
+        <v>0.2412</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -1668,25 +1662,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2458</v>
+        <v>0.234</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1696,25 +1690,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.24</v>
+        <v>0.19324</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1724,25 +1718,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.234</v>
+        <v>0.15584</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1746,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1761,7 +1755,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.19324</v>
+        <v>0.1358</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1770,7 +1764,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1774,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1789,7 +1783,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.15584</v>
+        <v>0.13176</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1798,7 +1792,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1802,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1817,7 +1811,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1358</v>
+        <v>0.1234</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1826,7 +1820,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1836,25 +1830,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.13176</v>
+        <v>0.1164</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1858,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1873,16 +1867,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1234</v>
+        <v>0.1125</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1892,25 +1886,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1182</v>
+        <v>0.1048</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1914,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1929,16 +1923,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1095</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1942,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1957,7 +1951,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1048</v>
+        <v>0.0964</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1966,7 +1960,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1970,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1985,7 +1979,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.09704000000000002</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1994,7 +1988,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -2004,7 +1998,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2013,7 +2007,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.0964</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2022,7 +2016,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2026,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2041,7 +2035,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.06908</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2050,7 +2044,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2054,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2069,7 +2063,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.07208000000000001</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2078,7 +2072,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2082,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2097,7 +2091,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.06908</v>
+        <v>0.06392</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2106,7 +2100,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2110,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2125,16 +2119,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2138,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2153,16 +2147,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.06392</v>
+        <v>0.06</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2166,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2190,7 +2184,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2194,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>dax in power bi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2218,7 +2212,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=dax+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2222,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2246,7 +2240,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2250,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dashboard design ui</t>
+          <t>ui dashboard design</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2274,7 +2268,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+ui</t>
+          <t>https://trends.google.com/trends/explore?q=ui+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2278,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>ui design</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2293,16 +2287,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.05416</v>
+        <v>0.0588</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=ui+design</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2306,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>dashboard ui</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.05279999999999999</v>
+        <v>0.0588</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2330,7 +2324,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+ui</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2334,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2349,7 +2343,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.05056000000000001</v>
+        <v>0.05416</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2358,7 +2352,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2368,16 +2362,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>best dashboard design</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.0504</v>
+        <v>0.0522</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2386,7 +2380,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2390,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>best dashboard design</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2405,7 +2399,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2414,7 +2408,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2424,25 +2418,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.0474</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2455,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.048</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2480,16 +2474,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.0474</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2498,7 +2492,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2502,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2517,7 +2511,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.042</v>
+        <v>0.0474</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2526,7 +2520,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2536,16 +2530,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.0336</v>
+        <v>0.0444</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2554,7 +2548,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2564,16 +2558,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.0312</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2582,7 +2576,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2592,16 +2586,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.0306</v>
+        <v>0.0372</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2610,7 +2604,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2614,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>dashboard power bi</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2629,7 +2623,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.0306</v>
+        <v>0.033</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2638,7 +2632,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2648,25 +2642,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.02944</v>
+        <v>0.03179999999999999</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2670,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2685,7 +2679,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.0288</v>
+        <v>0.0306</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2694,7 +2688,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2704,16 +2698,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0288</v>
+        <v>0.0306</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2722,7 +2716,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -2732,25 +2726,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.026</v>
+        <v>0.03</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2760,25 +2754,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.02456</v>
+        <v>0.03</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2782,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2797,16 +2791,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.024</v>
+        <v>0.02944</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2810,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2825,16 +2819,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2838,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ai dashboard design</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2853,7 +2847,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.0228</v>
+        <v>0.0258</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2862,7 +2856,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2872,25 +2866,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0222</v>
+        <v>0.02456</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2894,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2909,7 +2903,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0216</v>
+        <v>0.024</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2918,7 +2912,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2922,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>ai dashboard design</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2937,7 +2931,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.0192</v>
+        <v>0.0228</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2946,7 +2940,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=ai+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2956,25 +2950,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.019</v>
+        <v>0.0228</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2978,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2993,7 +2987,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0186</v>
+        <v>0.0216</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3002,7 +2996,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3015,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.0186</v>
+        <v>0.0192</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3040,7 +3034,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3049,7 +3043,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.018</v>
+        <v>0.0192</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3058,7 +3052,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3062,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3077,7 +3071,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.018</v>
+        <v>0.0192</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3086,7 +3080,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3090,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3105,16 +3099,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.0168</v>
+        <v>0.019</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3118,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>business analytics</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3133,7 +3127,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0156</v>
+        <v>0.0186</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3142,7 +3136,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3146,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3161,7 +3155,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0156</v>
+        <v>0.0168</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3170,7 +3164,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3174,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3189,7 +3183,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0144</v>
+        <v>0.0162</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3198,7 +3192,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3208,16 +3202,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0144</v>
+        <v>0.015</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3226,7 +3220,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3230,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3245,7 +3239,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.0144</v>
+        <v>0.015</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3254,7 +3248,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3258,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3273,16 +3267,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.01432</v>
+        <v>0.0144</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3286,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>modern dashboard design</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3301,7 +3295,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3310,7 +3304,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3314,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3329,7 +3323,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0138</v>
+        <v>0.0144</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3338,7 +3332,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3348,25 +3342,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0138</v>
+        <v>0.01432</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3370,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>modern dashboard design</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3385,7 +3379,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0132</v>
+        <v>0.0138</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3394,7 +3388,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3398,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3422,7 +3416,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3426,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3441,7 +3435,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.0126</v>
+        <v>0.0132</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3450,7 +3444,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3463,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0126</v>
+        <v>0.0132</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3488,7 +3482,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3497,7 +3491,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.012</v>
+        <v>0.0126</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3506,7 +3500,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3538,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>analytics dashboard design</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3562,7 +3556,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3566,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>download power bi desktop</t>
+          <t>analytics dashboard design</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3581,7 +3575,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.0108</v>
+        <v>0.0114</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3590,7 +3584,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=analytics+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3600,16 +3594,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>bi dashboard design</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0108</v>
+        <v>0.0114</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3618,7 +3612,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3622,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3646,7 +3640,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3650,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>dashboard design template</t>
+          <t>power bi download desktop</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3665,7 +3659,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.0102</v>
+        <v>0.0108</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3674,7 +3668,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download+desktop</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3678,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>admin dashboard design</t>
+          <t>bi dashboard design</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3693,7 +3687,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.0102</v>
+        <v>0.0108</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3702,7 +3696,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3706,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>admin dashboard</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3730,7 +3724,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3734,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>curso power bi</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3758,7 +3752,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=curso+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3762,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>admin dashboard design</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3777,7 +3771,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3786,7 +3780,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+login</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3790,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>power bi web</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3805,16 +3799,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.00936</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
         </is>
       </c>
     </row>
@@ -3824,16 +3818,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>information dashboard design</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3842,7 +3836,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3846,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>user dashboard design</t>
+          <t>dashboard design template</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3861,7 +3855,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3870,7 +3864,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+template</t>
         </is>
       </c>
     </row>
@@ -3880,16 +3874,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>dashboard template</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3898,7 +3892,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+template</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3902,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3917,16 +3911,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0094</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3930,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>excel dashboard design</t>
+          <t>user dashboard design</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3954,7 +3948,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3958,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>dashboard design figma</t>
+          <t>information dashboard design</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3973,7 +3967,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0078</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3982,7 +3976,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+figma</t>
+          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3986,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>excel dashboard design</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4001,16 +3995,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.0076</v>
+        <v>0.0078</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=excel+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4014,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4029,7 +4023,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.0072</v>
+        <v>0.0078</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4038,7 +4032,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
         </is>
       </c>
     </row>
@@ -4048,25 +4042,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0072</v>
+        <v>0.0076</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -4076,16 +4070,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0072</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4094,7 +4088,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4104,16 +4098,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>dax query in power bi</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.0072</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4122,7 +4116,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=dax+query+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4126,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4141,16 +4135,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.006</v>
+        <v>0.0072</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -4160,16 +4154,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.006</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4178,7 +4172,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4182,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>data scientist</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4197,16 +4191,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.00576</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
         </is>
       </c>
     </row>
@@ -4216,25 +4210,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.00556</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4238,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4253,16 +4247,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.00504</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4266,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4281,16 +4275,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.004840000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4294,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4309,7 +4303,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.004560000000000001</v>
+        <v>0.00576</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4318,7 +4312,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4322,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4337,16 +4331,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.0045</v>
+        <v>0.00556</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4350,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>dax functions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4365,16 +4359,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.0045</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=dax+functions</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4378,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>dax function in power bi</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4393,16 +4387,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.00448</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=dax+function+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4406,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4421,7 +4415,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.00436</v>
+        <v>0.00504</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4430,7 +4424,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4434,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4449,16 +4443,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.0042</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4462,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4477,7 +4471,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.00384</v>
+        <v>0.004560000000000001</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4486,7 +4480,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4490,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4505,16 +4499,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.00384</v>
+        <v>0.0045</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4533,16 +4527,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.0038</v>
+        <v>0.0045</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4546,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4561,7 +4555,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.00368</v>
+        <v>0.00448</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4570,7 +4564,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4574,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4589,16 +4583,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.0036</v>
+        <v>0.00436</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -4608,16 +4602,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.0036</v>
+        <v>0.0042</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4626,7 +4620,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4630,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4645,7 +4639,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.0036</v>
+        <v>0.00384</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4654,7 +4648,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4658,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4673,7 +4667,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.00324</v>
+        <v>0.00384</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4682,7 +4676,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4686,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4701,16 +4695,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.003</v>
+        <v>0.0038</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4714,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4729,16 +4723,16 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.003</v>
+        <v>0.00368</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4742,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>data engineering vs data analytics</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4757,16 +4751,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.003</v>
+        <v>0.00364</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4770,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>dax functions in power bi</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4785,16 +4779,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.0026</v>
+        <v>0.0036</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://trends.google.com/trends/explore?q=dax+functions+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4798,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>data pipeline development</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4813,7 +4807,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0024</v>
+        <v>0.0036</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4822,7 +4816,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4826,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>python for data engineering</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4841,16 +4835,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.00212</v>
+        <v>0.0036</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4854,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4869,7 +4863,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.00184</v>
+        <v>0.00324</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4878,7 +4872,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -4888,25 +4882,25 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.0018</v>
+        <v>0.003</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4910,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4925,16 +4919,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.0018</v>
+        <v>0.003</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4938,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4953,7 +4947,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.0016</v>
+        <v>0.0026</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4962,7 +4956,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4966,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4981,16 +4975,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.0015</v>
+        <v>0.00212</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -5000,7 +4994,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5009,16 +5003,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.0015</v>
+        <v>0.00184</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -5028,25 +5022,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.00148</v>
+        <v>0.0018</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5050,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5065,7 +5059,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.00136</v>
+        <v>0.0018</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5074,7 +5068,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5078,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5093,16 +5087,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.0012</v>
+        <v>0.0016</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5106,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5121,16 +5115,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5134,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5149,16 +5143,16 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.0012</v>
+        <v>0.0015</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -5168,25 +5162,25 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.0012</v>
+        <v>0.00148</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -5196,25 +5190,25 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.0012</v>
+        <v>0.00136</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5218,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5242,7 +5236,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5252,25 +5246,25 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.00108</v>
+        <v>0.0012</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5274,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5289,16 +5283,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.0009599999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5302,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5317,16 +5311,16 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.00092</v>
+        <v>0.0012</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5330,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5345,16 +5339,16 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.00068</v>
+        <v>0.0012</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -5364,25 +5358,25 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Codpal-Limited/deckgauge</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://github.com/Codpal-Limited/deckgauge</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5386,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5401,7 +5395,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.00108</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5410,7 +5404,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -5420,23 +5414,163 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.00068</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://github.com/Codpal-Limited/deckgauge</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.0006400000000000001</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>etl data pipeline</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
@@ -5453,7 +5587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A379"/>
+  <dimension ref="A1:A377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5641,686 +5775,686 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>best dashboard design examples</t>
+          <t>best dashboard design</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>best dashboard design home assistant</t>
+          <t>best dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>best dashboard design in excel</t>
+          <t>best dashboard design home assistant</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>best dashboard design in power bi</t>
+          <t>best dashboard design in excel</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>best dashboard design inspiration</t>
+          <t>best dashboard design in power bi</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>best dashboard design principles</t>
+          <t>best dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>best dashboard design templates</t>
+          <t>best dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>best dashboard design ui</t>
+          <t>best dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>best dashboard design ui</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>best data analytics books</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>best data analytics software</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best data engineering books</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>best data pipeline</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>best free kpi dashboard software</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>best kpi dashboard design</t>
+          <t>best free kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>best kpi dashboard excel</t>
+          <t>best kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>best kpi dashboard in power bi</t>
+          <t>best kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>best kpi dashboard software</t>
+          <t>best kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>best kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>best power bi books</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>best power bi certification</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>best power bi courses</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>best power bi dax book</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>best power bi dax course</t>
+          <t>best power bi dax book</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>best power bi dax course</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>best power bi training</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>better than chatgpt for data analysis</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>budget vs actual dashboard design</t>
+          <t>better than chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>business intelligence trends</t>
+          <t>budget vs actual dashboard design</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>business intelligence trends 2024</t>
+          <t>business intelligence trends</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>business intelligence trends 2025</t>
+          <t>business intelligence trends 2024</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>business intelligence trends 2026</t>
+          <t>business intelligence trends 2025</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>business intelligence trends 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis course</t>
+          <t>chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis free</t>
+          <t>chatgpt for data analysis course</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis in excel</t>
+          <t>chatgpt for data analysis free</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis pdf</t>
+          <t>chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis reddit</t>
+          <t>chatgpt for data analysis pdf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>chatgpt for data analysis udemy</t>
+          <t>chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>claude ai vs chatgpt for data analysis</t>
+          <t>chatgpt for data analysis udemy</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>claude vs chatgpt for data analysis</t>
+          <t>claude ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>claude vs chatgpt for data analysis reddit</t>
+          <t>claude vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>claude vs chatgpt for data analysis reddit</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>copilot vs chatgpt for data analysis</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>copilot vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>dashboard design</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dashboard design best practices</t>
+          <t>dashboard design</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dashboard design ideas</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dashboard design inspiration</t>
+          <t>dashboard design ideas</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>dashboard design meaning</t>
+          <t>dashboard design inspiration</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>dashboard design principles</t>
+          <t>dashboard design meaning</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>dashboard design rules</t>
+          <t>dashboard design principles</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>dashboard design skill</t>
+          <t>dashboard design rules</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dashboard design skill claude code</t>
+          <t>dashboard design skill</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dashboard design standards</t>
+          <t>dashboard design skill claude code</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dashboard design templates</t>
+          <t>dashboard design standards</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dashboard design tips</t>
+          <t>dashboard design templates</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>dashboard design tips</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data analytics</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>data analytics apprenticeship google</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>data analytics certification</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data analytics courses</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>data analytics jobs entry level</t>
+          <t>data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>data analytics masters</t>
+          <t>data analytics google certification</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>data analytics professional certificate</t>
+          <t>data analytics internships</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>data engineering</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>data engineering certification</t>
+          <t>data engineering academy</t>
         </is>
       </c>
     </row>
@@ -6334,56 +6468,56 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>data engineering internship</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data engineering manager</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>data engineering reddit</t>
+          <t>data engineering projects</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>data engineering salary</t>
+          <t>data engineering system design</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering things</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>data engineering vs data science</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>data pipeline</t>
+          <t>data engineering zoomcamp</t>
         </is>
       </c>
     </row>
@@ -6397,1713 +6531,1699 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>data pipeline architecture diagram</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>data pipeline engineer</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>data pipeline examples</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>data pipeline orchestration</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>data pipeline station</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>deepseek vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>deepseek vs chatgpt for data analysis</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>gemini vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>gemini vs chatgpt for data analysis</t>
+          <t>good kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>good vs bad dashboard design</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>good kpi dashboard</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>good vs bad dashboard design</t>
+          <t>grok vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>how good is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>grok vs chatgpt for data analysis</t>
+          <t>how reliable is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>how good is chatgpt for data analysis</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>how reliable is chatgpt for data analysis</t>
+          <t>how to comment power bi dax</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how to concatenate in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>how to comment power bi dax</t>
+          <t>how to create a kpi dashboard in excel from scratch</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>how to concatenate in power bi dax</t>
+          <t>how to create a kpi dashboard in google sheets</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in excel from scratch</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in google sheets</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to create kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to create kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard</t>
+          <t>how to create kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in excel</t>
+          <t>how to create kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in power bi</t>
+          <t>how to dashboard design</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in tableau</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>how to dashboard design</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to design kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to divide in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>how to design kpi dashboard</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>how to divide in power bi dax</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to learn power bi dax</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>how to learn power bi dax</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to multiply in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to open power bi dax</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>how to multiply in power bi dax</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>how to open power bi dax</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to power bi dax</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>how to power bi dax</t>
+          <t>how to practice power bi dax</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>how to practice power bi dax</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>how to use chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>how to use chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis</t>
+          <t>how to use power bi dax</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis in excel</t>
+          <t>how to write power bi dax</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>how to use power bi dax</t>
+          <t>if or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>how to write power bi dax</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>if or power bi dax</t>
+          <t>julius ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>julius vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>julius ai vs chatgpt for data analysis</t>
+          <t>kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>julius vs chatgpt for data analysis</t>
+          <t>kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kpi dashboard</t>
+          <t>kpi dashboard examples</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kpi dashboard design</t>
+          <t>kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kpi dashboard examples</t>
+          <t>kpi dashboard ideas</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kpi dashboard excel</t>
+          <t>kpi dashboard meaning</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kpi dashboard ideas</t>
+          <t>kpi dashboard power bi</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kpi dashboard meaning</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kpi dashboard power bi</t>
+          <t>kpi dashboard template</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>kpi dashboard template excel</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kpi dashboard template</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kpi dashboard template excel</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>llm for bi</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>llm for bi</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>perplexity vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>perplexity vs chatgpt for data analysis</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>power bi courses</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi dax</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>power bi dax</t>
+          <t>power bi dax best practices</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>power bi dax best practices</t>
+          <t>power bi dax cheat sheet</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>power bi dax cheat sheet</t>
+          <t>power bi dax filter</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>power bi dax filter</t>
+          <t>power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>power bi dax functions</t>
+          <t>power bi dax functions list</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>power bi dax functions list</t>
+          <t>power bi dax if statement</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>power bi dax if</t>
+          <t>power bi dax queries</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>power bi dax if statement</t>
+          <t>power bi dax query view</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>power bi dax queries</t>
+          <t>power bi dax switch</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>power bi dax query view</t>
+          <t>power bi dax tutorial</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>power bi dax switch</t>
+          <t>power bi dax vs power query</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>power bi dax vs power query</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>power bi vs power bi dax</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>power bi vs power bi dax</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>stakeholder reporting forvis mazars</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>stakeholder reporting</t>
+          <t>stakeholder reporting gmbh</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>stakeholder reporting forvis mazars</t>
+          <t>stakeholder reporting gmbh &amp; co kg</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh</t>
+          <t>stakeholder reporting hamburg</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh &amp; co kg</t>
+          <t>stakeholder reporting meaning</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>stakeholder reporting hamburg</t>
+          <t>stakeholder reporting template</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>stakeholder reporting meaning</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>stakeholder reporting template</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>top 10 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>top 5 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>top 10 power bi dax</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>top 5 power bi dax</t>
+          <t>top kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>top n power bi dax</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>top kpi dashboard</t>
+          <t>top power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>top n power bi dax</t>
+          <t>top power bi dax interview questions</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>top power bi dax functions</t>
+          <t>types of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>top power bi dax interview questions</t>
+          <t>using chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>types of dashboard design</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>using chatgpt for data analysis</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>what is a floating element in tableau dashboard design</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>what is a good dashboard design</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>what is a floating element in tableau dashboard design</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>what is a good dashboard design</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is bi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is dashboard design</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>what is bi dashboard design</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>what is dashboard design</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is kpi dashboard development</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>what is kpi dashboard</t>
+          <t>what is kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>what is kpi dashboard development</t>
+          <t>what is kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in excel</t>
+          <t>what is kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in power bi</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in tableau</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>what is power bi dashboard</t>
+          <t>what is power bi dax code</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>what is power bi dax</t>
+          <t>what is power bi dax function</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>what is power bi dax code</t>
+          <t>what is power bi dax measures</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>what is power bi dax function</t>
+          <t>what is power bi dax query</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>what is power bi dax measures</t>
+          <t>what is power bi dax studio</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>what is power bi dax query</t>
+          <t>what is power bi dax used for</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>what is power bi dax studio</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>what is power bi dax used for</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is saas dashboard design</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>what is saas dashboard design</t>
+          <t>what is the best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>what is stakeholder reporting</t>
+          <t>what is the best version of chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>what is the best chatgpt for data analysis</t>
+          <t>what is the fundamental challenge of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>what is the best version of chatgpt for data analysis</t>
+          <t>what language is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>what is the fundamental challenge of dashboard design</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>what language is power bi dax</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
-        <is>
-          <t>why power bi over excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>why power bi over tableau</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>

--- a/report.xlsx
+++ b/report.xlsx
@@ -709,12 +709,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,25 +768,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Possibly Off-Niche</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Top Competing Video</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
@@ -803,7 +808,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago (2024) and likely outdated. Structure: a direct "what's changed since 2024" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -811,23 +816,26 @@
           <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Data Engineering Course for Beginners</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1133623</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>1133651</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.8</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
@@ -844,7 +852,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Your angle: claim the space — straightforward, solid coverage of "langfuse/langfuse" has almost no competition right now.</t>
+          <t>WHITESPACE — "langfuse/langfuse" has little to no video coverage yet (only one relevant video exists: "Get Started with Langfuse - Open-Source LLM Monitoring", 79.9k views). Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,23 +860,26 @@
           <t>langfuse/langfuse</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Get Started with Langfuse - Open-Source LLM Monitoring</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>79908</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.8</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>https://github.com/langfuse/langfuse</t>
         </is>
@@ -885,7 +896,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — "coreyhaines31/marketingskills" has little to no video coverage yet. Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -893,17 +904,20 @@
           <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.8</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
@@ -920,7 +934,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("Airbyte 2.0: Enterprise Flex", 619.9k views). Your angle: claim the space — straightforward, solid coverage of "airbytehq/airbyte" has almost no competition right now.</t>
+          <t>WHITESPACE — "airbytehq/airbyte" has little to no video coverage yet (only one relevant video exists: "Airbyte 2.0: Enterprise Flex", 619.9k views). Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -928,23 +942,26 @@
           <t>airbytehq/airbyte</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Airbyte 2.0: Enterprise Flex</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>619941</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>RECURRING</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.8</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>https://github.com/airbytehq/airbyte</t>
         </is>
@@ -961,7 +978,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna" has 16.5M views, but it's from 5 years ago (2021) and likely outdated. Structure: a direct "what's changed since 2021" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -969,23 +986,26 @@
           <t>mage-ai/mage-ai</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Aye Enna Pana Mage (ආයේ එන්න පණ මාගේ) - Chamika Sirimanna</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>16542114</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>16542417</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>RECURRING</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.706</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>https://github.com/mage-ai/mage-ai</t>
         </is>
@@ -1002,7 +1022,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Avoiding circular dependency errors in DAX" has 41.9k views, but it's from 5 years ago (2021) and likely outdated. Structure: a direct "what's changed since 2021" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1010,23 +1030,26 @@
           <t>circular dependency detected power bi</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Avoiding circular dependency errors in DAX</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>41873</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>RECURRING</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
@@ -1043,7 +1066,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Cómo usar Power BI (Tutorial desde cero)" has 2.9M views, but it's from 5 years ago (2020) and likely outdated. Structure: a direct "what's changed since 2020" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1051,23 +1074,26 @@
           <t>power bi para que sirve</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Cómo usar Power BI (Tutorial desde cero)</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>2874055</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
+      <c r="G8" t="n">
+        <v>2874087</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.3</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=power+bi+para+que+sirve</t>
         </is>
@@ -1084,7 +1110,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("LangWatch LLM Optimization Studio", 89.1k views). Your angle: claim the space — straightforward, solid coverage of "langwatch/langwatch" has almost no competition right now.</t>
+          <t>WHITESPACE — "langwatch/langwatch" has little to no video coverage yet (only one relevant video exists: "LangWatch LLM Optimization Studio", 89.1k views). Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,23 +1118,26 @@
           <t>langwatch/langwatch</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>LangWatch LLM Optimization Studio</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>89121</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.19324</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>https://github.com/langwatch/langwatch</t>
         </is>
@@ -1125,7 +1154,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "spiceai/spiceai" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — "spiceai/spiceai" has little to no video coverage yet. Structure: a quick hands-on first look — install it, then specifically test (1) setup/onboarding friction, (2) output quality on a real dataset (not the demo data), and (3) how it fits into an existing stack.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1133,17 +1162,20 @@
           <t>spiceai/spiceai</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.1234</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>https://github.com/spiceai/spiceai</t>
         </is>
@@ -1160,33 +1192,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "Power BI Tutorial For Beginners | Create Your First Dashboard Now (Practice Files included)" has 3.1M views, but it's from 4 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>REVISIT — "Power BI Tutorial From Beginner to Pro ⚡ Desktop to Dashboard in 60 Minutes ⏰" has 5.8M views, but it's from 7 years ago (2019) and likely outdated. Structure: a direct "what's changed since 2019" comparison — name the specific things that are different now (new versions, deprecated features, changed best practices) rather than a generic refresh.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Power BI Tutorial For Beginners | Create Your First Dashboard Now (Practice Files included)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>3058195</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+          <t>power bi microsoft</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Power BI Tutorial From Beginner to Pro ⚡ Desktop to Dashboard in 60 Minutes ⏰</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5832760</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>EVERGREEN</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.06</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -1634,25 +1669,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2412</v>
+        <v>0.234</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1662,25 +1697,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.234</v>
+        <v>0.19324</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1725,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1699,7 +1734,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.19324</v>
+        <v>0.15584</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1708,7 +1743,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1753,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1727,7 +1762,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.15584</v>
+        <v>0.1358</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1736,7 +1771,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1781,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1755,7 +1790,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1358</v>
+        <v>0.13176</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1764,7 +1799,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1809,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1783,7 +1818,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.13176</v>
+        <v>0.1234</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1792,7 +1827,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -1802,25 +1837,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1234</v>
+        <v>0.1164</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1830,25 +1865,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1164</v>
+        <v>0.114</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1893,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1867,16 +1902,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1125</v>
+        <v>0.1048</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1921,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1895,7 +1930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1048</v>
+        <v>0.09704000000000002</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1904,7 +1939,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1949,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1923,7 +1958,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.09704000000000002</v>
+        <v>0.0964</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1932,7 +1967,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1977,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1951,7 +1986,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.0964</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1960,7 +1995,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -1970,7 +2005,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1979,7 +2014,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.07208000000000001</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1988,7 +2023,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -1998,7 +2033,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2007,7 +2042,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.07208000000000001</v>
+        <v>0.06908</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2016,7 +2051,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2061,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2035,7 +2070,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.06908</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2044,7 +2079,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2089,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2063,7 +2098,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.06696000000000001</v>
+        <v>0.06392</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2072,7 +2107,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -2082,25 +2117,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.06392</v>
+        <v>0.06</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2145,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2128,7 +2163,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2201,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>dax in power bi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2184,7 +2219,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://trends.google.com/trends/explore?q=dax+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2229,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dax in power bi</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2212,7 +2247,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+in+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=kpi+dashboard+software</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2257,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>ui dashboard design</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2240,7 +2275,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=ui+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2285,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ui dashboard design</t>
+          <t>dashboard ui</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2259,7 +2294,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.06</v>
+        <v>0.0588</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2268,7 +2303,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ui+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+ui</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2341,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dashboard ui</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2315,16 +2350,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.0588</v>
+        <v>0.05416</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+ui</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -2334,25 +2369,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.05416</v>
+        <v>0.0522</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2362,16 +2397,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>best dashboard design</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.0522</v>
+        <v>0.051</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2380,7 +2415,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2425,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>best dashboard design</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2399,16 +2434,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.051</v>
+        <v>0.05056000000000001</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=best+dashboard+design</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -2418,25 +2453,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.05056000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2481,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2455,7 +2490,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.048</v>
+        <v>0.0474</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2464,7 +2499,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2509,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data center engineering</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2492,7 +2527,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2537,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>data center engineering</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2511,7 +2546,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.0474</v>
+        <v>0.045</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2520,7 +2555,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+center+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2565,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2539,7 +2574,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.0444</v>
+        <v>0.04259999999999999</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2548,7 +2583,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2593,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2567,7 +2602,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.04259999999999999</v>
+        <v>0.0372</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2576,7 +2611,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -2586,16 +2621,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.0372</v>
+        <v>0.033</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2604,7 +2639,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2649,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2623,7 +2658,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.033</v>
+        <v>0.03179999999999999</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2632,7 +2667,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2677,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2651,7 +2686,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.03179999999999999</v>
+        <v>0.0306</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2660,7 +2695,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2705,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2688,7 +2723,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -2698,16 +2733,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0306</v>
+        <v>0.03</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2716,7 +2751,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2754,25 +2789,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.03</v>
+        <v>0.02944</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2817,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2791,7 +2826,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.02944</v>
+        <v>0.026</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2800,7 +2835,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2845,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2819,16 +2854,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.026</v>
+        <v>0.0258</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2873,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2847,16 +2882,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.0258</v>
+        <v>0.02456</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2901,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2875,16 +2910,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.02456</v>
+        <v>0.024</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2929,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.024</v>
+        <v>0.0228</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2912,7 +2947,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2950,16 +2985,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0228</v>
+        <v>0.0216</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2968,7 +3003,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -2978,7 +3013,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2987,7 +3022,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0216</v>
+        <v>0.0192</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2996,7 +3031,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3097,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3071,16 +3106,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.0192</v>
+        <v>0.019</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3125,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3099,16 +3134,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.019</v>
+        <v>0.0186</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3153,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3127,7 +3162,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0186</v>
+        <v>0.0168</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3136,7 +3171,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3181,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3155,7 +3190,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0168</v>
+        <v>0.0162</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3164,7 +3199,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3209,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3183,7 +3218,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0162</v>
+        <v>0.015</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3192,7 +3227,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3265,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3239,7 +3274,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.015</v>
+        <v>0.0144</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3248,7 +3283,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3293,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3276,7 +3311,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3321,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3304,7 +3339,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3349,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3323,16 +3358,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0144</v>
+        <v>0.01432</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3377,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>modern dashboard design</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3351,16 +3386,16 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.01432</v>
+        <v>0.0138</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3405,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>modern dashboard design</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3379,7 +3414,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0138</v>
+        <v>0.0132</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3388,7 +3423,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=modern+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3461,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>dashboard design best practices</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3444,7 +3479,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3489,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>dashboard design best practices</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3463,7 +3498,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0132</v>
+        <v>0.0126</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3472,7 +3507,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+best+practices</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3517,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3491,7 +3526,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0126</v>
+        <v>0.012</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3500,7 +3535,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3545,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3519,7 +3554,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.012</v>
+        <v>0.0114</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3528,7 +3563,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3538,12 +3573,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3556,7 +3591,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3594,16 +3629,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>bi dashboard design</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0114</v>
+        <v>0.0108</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3612,7 +3647,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3713,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>bi dashboard design</t>
+          <t>admin dashboard</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3687,7 +3722,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.0108</v>
+        <v>0.0102</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3696,7 +3731,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=bi+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3741,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>admin dashboard</t>
+          <t>power bi curso</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3724,7 +3759,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=admin+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3769,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>power bi curso</t>
+          <t>admin dashboard design</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3752,7 +3787,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+curso</t>
+          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3797,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>admin dashboard design</t>
+          <t>dashboard template</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3771,7 +3806,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.0102</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3780,7 +3815,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=admin+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+template</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3909,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>dashboard template</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3883,16 +3918,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0094</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+template</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3937,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>information dashboard design</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3911,16 +3946,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.0094</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3965,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>user dashboard design</t>
+          <t>dashboard design examples</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3948,7 +3983,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3993,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>information dashboard design</t>
+          <t>user dashboard design</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3976,7 +4011,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=information+dashboard+design</t>
+          <t>https://trends.google.com/trends/explore?q=user+dashboard+design</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4049,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>dashboard design examples</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4023,16 +4058,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.0078</v>
+        <v>0.0076</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard+design+examples</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4077,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4051,16 +4086,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0076</v>
+        <v>0.0072</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4105,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>dax query in power bi</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4088,7 +4123,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dax+query+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4133,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>dax query in power bi</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4116,7 +4151,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+query+in+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4126,16 +4161,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.0072</v>
+        <v>0.006599999999999999</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4144,7 +4179,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4189,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4172,7 +4207,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4273,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4247,16 +4282,16 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.006599999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://news.ycombinator.com/item?id=49758181</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4301,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Show HN: Open-source revenue recognition and analytics for Stripe and Metronome</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4275,16 +4310,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.006</v>
+        <v>0.00576</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49758181</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4329,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4303,7 +4338,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.00576</v>
+        <v>0.00556</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4312,7 +4347,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4357,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>dax function in power bi</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4331,16 +4366,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.00556</v>
+        <v>0.005399999999999999</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=dax+function+in+power+bi</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4413,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>dax function in power bi</t>
+          <t>surfalytics/data-projects</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4387,16 +4422,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.005399999999999999</v>
+        <v>0.00504</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+function+in+power+bi</t>
+          <t>https://github.com/surfalytics/data-projects</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4441,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>surfalytics/data-projects</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4415,7 +4450,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.00504</v>
+        <v>0.004840000000000001</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4424,7 +4459,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://github.com/surfalytics/data-projects</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4469,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4443,7 +4478,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.004840000000000001</v>
+        <v>0.004560000000000001</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4452,7 +4487,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4497,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4471,16 +4506,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.004560000000000001</v>
+        <v>0.0045</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4525,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4508,7 +4543,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4553,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4527,16 +4562,16 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.0045</v>
+        <v>0.00448</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4581,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4555,7 +4590,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.00448</v>
+        <v>0.00436</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4564,7 +4599,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4609,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4583,16 +4618,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.00436</v>
+        <v>0.0042</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4637,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4611,16 +4646,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.0042</v>
+        <v>0.00384</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4693,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4667,7 +4702,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.00384</v>
+        <v>0.0038</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4676,7 +4711,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4721,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4695,7 +4730,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0038</v>
+        <v>0.00368</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4704,7 +4739,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4749,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4723,7 +4758,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.00368</v>
+        <v>0.00364</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4732,7 +4767,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4777,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4751,16 +4786,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.00364</v>
+        <v>0.0036</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4805,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>dax functions in power bi</t>
+          <t>python for data engineering</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4788,7 +4823,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+functions+in+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4833,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4807,16 +4842,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.0036</v>
+        <v>0.00324</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4861,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>python for data engineering</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4835,16 +4870,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.0036</v>
+        <v>0.003</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python+for+data+engineering</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4889,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4863,16 +4898,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.00324</v>
+        <v>0.003</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4917,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4891,16 +4926,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4945,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4919,7 +4954,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.003</v>
+        <v>0.0024</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4928,7 +4963,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4973,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4947,7 +4982,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.0026</v>
+        <v>0.00212</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4956,7 +4991,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -4966,7 +5001,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4975,7 +5010,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.00212</v>
+        <v>0.00184</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4984,7 +5019,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -4994,25 +5029,25 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.00184</v>
+        <v>0.0018</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -5022,12 +5057,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5035,12 +5070,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5085,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5059,7 +5094,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.0018</v>
+        <v>0.0016</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5068,7 +5103,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5113,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5087,16 +5122,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.0016</v>
+        <v>0.0015</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://etlfunnel.com</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5169,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5143,16 +5178,16 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.0015</v>
+        <v>0.00148</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5197,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5171,7 +5206,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.00148</v>
+        <v>0.00136</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5180,7 +5215,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5225,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5199,16 +5234,16 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.00136</v>
+        <v>0.0012</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5253,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5236,7 +5271,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5281,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5264,7 +5299,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5309,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5292,7 +5327,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -5302,12 +5337,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5320,7 +5355,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A377"/>
+  <dimension ref="A1:A378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6412,35 +6447,35 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>data analytics google certification</t>
+          <t>data analytics internship</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>data analytics jobs remote</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
@@ -6461,56 +6496,56 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data engineering bootcamp</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>data engineering certification</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>data engineering courses</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6566,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>data pipeline design</t>
         </is>
       </c>
     </row>
@@ -6545,1685 +6580,1692 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>deepseek vs chatgpt for data analysis</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>deepseek vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>gemini vs chatgpt for data analysis</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>gemini vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>good kpi dashboard</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>good vs bad dashboard design</t>
+          <t>good kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>good vs bad dashboard design</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>grok vs chatgpt for data analysis</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>how good is chatgpt for data analysis</t>
+          <t>grok vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>how reliable is chatgpt for data analysis</t>
+          <t>how good is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how reliable is chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>how to comment power bi dax</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>how to concatenate in power bi dax</t>
+          <t>how to comment power bi dax</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in excel from scratch</t>
+          <t>how to concatenate in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>how to create a kpi dashboard in google sheets</t>
+          <t>how to create a kpi dashboard in excel from scratch</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to create a kpi dashboard in google sheets</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in excel</t>
+          <t>how to create kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in power bi</t>
+          <t>how to create kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>how to create kpi dashboard in tableau</t>
+          <t>how to create kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>how to dashboard design</t>
+          <t>how to create kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>how to dashboard design</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to data analytics</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to data engineering</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>how to design kpi dashboard</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>how to divide in power bi dax</t>
+          <t>how to design kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to divide in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>how to learn power bi dax</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to learn power bi dax</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>how to multiply in power bi dax</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>how to open power bi dax</t>
+          <t>how to multiply in power bi dax</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to open power bi dax</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to power bi</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>how to power bi dax</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to power bi dax</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>how to practice power bi dax</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>how to practice power bi dax</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>how to use chatgpt for data analysis in excel</t>
+          <t>how to use chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>how to use power bi dax</t>
+          <t>how to use chatgpt for data analysis in excel</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>how to write power bi dax</t>
+          <t>how to use power bi dax</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>if or power bi dax</t>
+          <t>how to write power bi dax</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>if or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>julius ai vs chatgpt for data analysis</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>julius vs chatgpt for data analysis</t>
+          <t>julius ai vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kpi dashboard</t>
+          <t>julius vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kpi dashboard design</t>
+          <t>kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kpi dashboard examples</t>
+          <t>kpi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kpi dashboard excel</t>
+          <t>kpi dashboard examples</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kpi dashboard ideas</t>
+          <t>kpi dashboard excel</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kpi dashboard meaning</t>
+          <t>kpi dashboard ideas</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kpi dashboard power bi</t>
+          <t>kpi dashboard meaning</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kpi dashboard software</t>
+          <t>kpi dashboard power bi</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kpi dashboard template</t>
+          <t>kpi dashboard software</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kpi dashboard template excel</t>
+          <t>kpi dashboard template</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>kpi dashboard template excel</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>llm analytics</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>llm for bi</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>llm for bi</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>or power bi</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>or power bi dax</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>or power bi measure</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>perplexity vs chatgpt for data analysis</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>perplexity vs chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi courses</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>power bi dax</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>power bi dax best practices</t>
+          <t>power bi dax</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>power bi dax cheat sheet</t>
+          <t>power bi dax best practices</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>power bi dax filter</t>
+          <t>power bi dax cheat sheet</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>power bi dax functions</t>
+          <t>power bi dax filter</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>power bi dax functions list</t>
+          <t>power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>power bi dax if statement</t>
+          <t>power bi dax functions list</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>power bi dax queries</t>
+          <t>power bi dax if statement</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>power bi dax query view</t>
+          <t>power bi dax queries</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>power bi dax switch</t>
+          <t>power bi dax query view</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>power bi dax tutorial</t>
+          <t>power bi dax switch</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>power bi dax vs power query</t>
+          <t>power bi dax tutorial</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi dax vs power query</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>power bi download</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>power bi login</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>power bi vs power bi dax</t>
+          <t>power bi training</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>power bi vs power bi dax</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>stakeholder reporting</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>stakeholder reporting forvis mazars</t>
+          <t>stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh</t>
+          <t>stakeholder reporting forvis mazars</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>stakeholder reporting gmbh &amp; co kg</t>
+          <t>stakeholder reporting gmbh</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>stakeholder reporting hamburg</t>
+          <t>stakeholder reporting gmbh &amp; co kg</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>stakeholder reporting meaning</t>
+          <t>stakeholder reporting hamburg</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>stakeholder reporting template</t>
+          <t>stakeholder reporting meaning</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>stakeholder reporting template</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>top 10 power bi dax</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>top 5 power bi dax</t>
+          <t>top 10 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>top 5 power bi dax</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>top kpi dashboard</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>top n power bi dax</t>
+          <t>top kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>top power bi dax functions</t>
+          <t>top n power bi dax</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>top power bi dax interview questions</t>
+          <t>top power bi dax functions</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>types of dashboard design</t>
+          <t>top power bi dax interview questions</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>using chatgpt for data analysis</t>
+          <t>types of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>using chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>vs data analytics</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>what is a floating element in tableau dashboard design</t>
+          <t>vs power bi</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>what is a good dashboard design</t>
+          <t>what is a floating element in tableau dashboard design</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>what is a good dashboard design</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>what is bi dashboard design</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>what is dashboard design</t>
+          <t>what is bi dashboard design</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is dashboard design</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data analytics</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>what is kpi dashboard</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>what is kpi dashboard development</t>
+          <t>what is kpi dashboard</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in excel</t>
+          <t>what is kpi dashboard development</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in power bi</t>
+          <t>what is kpi dashboard in excel</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>what is kpi dashboard in tableau</t>
+          <t>what is kpi dashboard in power bi</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is kpi dashboard in tableau</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>what is power bi dax</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>what is power bi dax code</t>
+          <t>what is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>what is power bi dax function</t>
+          <t>what is power bi dax code</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>what is power bi dax measures</t>
+          <t>what is power bi dax function</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>what is power bi dax query</t>
+          <t>what is power bi dax measures</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>what is power bi dax studio</t>
+          <t>what is power bi dax query</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>what is power bi dax used for</t>
+          <t>what is power bi dax studio</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi dax used for</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>what is saas dashboard design</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>what is stakeholder reporting</t>
+          <t>what is saas dashboard design</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>what is the best chatgpt for data analysis</t>
+          <t>what is stakeholder reporting</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>what is the best version of chatgpt for data analysis</t>
+          <t>what is the best chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>what is the fundamental challenge of dashboard design</t>
+          <t>what is the best version of chatgpt for data analysis</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>what language is power bi dax</t>
+          <t>what is the fundamental challenge of dashboard design</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>what language is power bi dax</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>
